--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -60,13 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-17T15:32:01+00:00</t>
+    <t>2023-10-31T15:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>JPSys</t>
+    <t>VA</t>
   </si>
   <si>
     <t>Contact</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31T15:37:13+00:00</t>
+    <t>2023-11-01T18:52:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for Use Case Lab Observation: Chem, hem, tox, ria, ser, ResourceType Observation</t>
+    <t>This StructureDefinition contains the maps for VistA CHEM, HEM, TOX, RIA, SER, etc. (file 63.04) to FHIR Observation</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1377,7 +1377,7 @@
     <t>704319004 |Inherent in|</t>
   </si>
   <si>
-    <t>1614: reference from CHEM, HEM, TOX, RIA, SER, etc. - ACCESSION (#63.04-.06)</t>
+    <t>+: reference from CHEM, HEM, TOX, RIA, SER, etc. - ACCESSION (#63.04-.06)</t>
   </si>
   <si>
     <t>Observation.device</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AT$79</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2778" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3377" uniqueCount="604">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-01T18:52:48+00:00</t>
+    <t>2023-11-08T21:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-observation-lab</t>
+    <t>http://va.gov/fhir/StructureDefinition/LabObservationObservation</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -659,7 +659,7 @@
     <t>Need to track the status of individual results. Some results are finalized before the whole report is finalized.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-status</t>
+    <t>http://va.gov/fhir/ValueSet/VFDiagnosticReportLabStatus</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -709,6 +709,188 @@
   </si>
   <si>
     <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category.id</t>
+  </si>
+  <si>
+    <t>Observation.category.extension</t>
+  </si>
+  <si>
+    <t>Observation.category.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>843: fixed value = laboratory</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Observation.category.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>Observation.category:Laboratory</t>
@@ -802,6 +984,30 @@
     <t>FiveWs.subject</t>
   </si>
   <si>
+    <t>Micro.AntibioticSensitivity.LRDFN
+Micro.AntibioticSensitivityComment.LRDFN
+Pathology.Autopsy.LRDFN
+Micro.BacteriologyReports.LRDFN
+Pathology.CytoOrganTissueFunction.StaffIEN
+Micro.MicroAntibioticLevel.LRDFN
+Micro.MicroAudit.LRDFN
+Micro.Microbiology.LRDFN
+Micro.MicroOrderedTest.LRDFN
+Micro.MicroSterilityResults.LRDFN
+Micro.MycobacteriologyReports.LRDFN
+Micro.Mycology.LRDFN
+Micro.MycologyReports.LRDFN
+Micro.Parasitology.LRDFN
+Micro.ParasitologyReports.LRDFN
+Micro.ParasitologyStage.LRDFN
+SStaff.SMicroOrderedTest.LRDFN
+Micro.Virology.LRDFN
+Micro.VirologyReports.LRDFN</t>
+  </si>
+  <si>
+    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (#2-63 &gt; 63-.01)</t>
+  </si>
+  <si>
     <t>Observation.focus</t>
   </si>
   <si>
@@ -1236,10 +1442,7 @@
     <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
   </si>
   <si>
-    <t>Codes identifying interpretations of observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://va.gov/fhir/ValueSet/VFLabInterpretation</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1712,6 +1915,12 @@
   </si>
   <si>
     <t>Observation.component.interpretation</t>
+  </si>
+  <si>
+    <t>Codes identifying interpretations of observations.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
   </si>
   <si>
     <t>Observation.component.referenceRange</t>
@@ -2037,7 +2246,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR68"/>
+  <dimension ref="A1:AT79"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.1171875" customWidth="true" bestFit="true"/>
@@ -2064,7 +2273,7 @@
     <col min="23" max="23" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="10.53125" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.4921875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="53.234375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="14.109375" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -2082,6 +2291,8 @@
     <col min="42" max="42" width="30.0703125" customWidth="true" bestFit="true"/>
     <col min="43" max="43" width="50.07421875" customWidth="true" bestFit="true"/>
     <col min="44" max="44" width="218.56640625" customWidth="true" bestFit="true"/>
+    <col min="45" max="45" width="50.07421875" customWidth="true" bestFit="true"/>
+    <col min="46" max="46" width="218.56640625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2209,6 +2420,12 @@
       <c r="AR1" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS1" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT1" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -2335,6 +2552,12 @@
       <c r="AR2" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS2" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT2" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
@@ -2459,6 +2682,12 @@
       <c r="AR3" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS3" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT3" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
@@ -2585,6 +2814,12 @@
       <c r="AR4" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS4" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT4" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
@@ -2711,6 +2946,12 @@
       <c r="AR5" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS5" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT5" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
@@ -2837,6 +3078,12 @@
       <c r="AR6" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS6" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT6" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
@@ -2963,6 +3210,12 @@
       <c r="AR7" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS7" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT7" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
@@ -3089,6 +3342,12 @@
       <c r="AR8" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS8" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT8" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
@@ -3217,6 +3476,12 @@
       <c r="AR9" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS9" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT9" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
@@ -3343,6 +3608,12 @@
       <c r="AR10" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS10" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT10" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
@@ -3467,6 +3738,12 @@
       <c r="AR11" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS11" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT11" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
@@ -3593,6 +3870,12 @@
       <c r="AR12" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS12" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT12" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
@@ -3721,6 +4004,12 @@
       <c r="AR13" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS13" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT13" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
@@ -3849,6 +4138,12 @@
       <c r="AR14" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS14" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT14" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
@@ -3977,6 +4272,12 @@
       <c r="AR15" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS15" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT15" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
@@ -4103,6 +4404,12 @@
       <c r="AR16" t="s" s="2">
         <v>166</v>
       </c>
+      <c r="AS16" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT16" t="s" s="2">
+        <v>166</v>
+      </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
@@ -4227,6 +4534,12 @@
       <c r="AR17" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS17" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT17" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
@@ -4353,6 +4666,12 @@
       <c r="AR18" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS18" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT18" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
@@ -4479,6 +4798,12 @@
       <c r="AR19" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS19" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT19" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
@@ -4605,6 +4930,12 @@
       <c r="AR20" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS20" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT20" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
@@ -4731,6 +5062,12 @@
       <c r="AR21" t="s" s="2">
         <v>211</v>
       </c>
+      <c r="AS21" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT21" t="s" s="2">
+        <v>211</v>
+      </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
@@ -4857,29 +5194,33 @@
       <c r="AR22" t="s" s="2">
         <v>40</v>
       </c>
+      <c r="AS22" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT22" t="s" s="2">
+        <v>40</v>
+      </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>222</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>223</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>40</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>50</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>40</v>
@@ -4888,20 +5229,16 @@
         <v>40</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>213</v>
+        <v>118</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>216</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>40</v>
       </c>
@@ -4910,7 +5247,7 @@
         <v>40</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>224</v>
+        <v>40</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>40</v>
@@ -4925,13 +5262,13 @@
         <v>40</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>217</v>
+        <v>40</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>218</v>
+        <v>40</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>40</v>
@@ -4949,19 +5286,19 @@
         <v>40</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>212</v>
+        <v>120</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>40</v>
@@ -4973,10 +5310,10 @@
         <v>40</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>220</v>
+        <v>121</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>221</v>
+        <v>40</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>40</v>
@@ -4985,51 +5322,55 @@
         <v>40</v>
       </c>
       <c r="AR23" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS23" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT23" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>226</v>
+        <v>95</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>40</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>139</v>
+        <v>96</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>227</v>
+        <v>97</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>228</v>
+        <v>123</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>40</v>
       </c>
@@ -5053,75 +5394,81 @@
         <v>40</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>231</v>
+        <v>40</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>232</v>
+        <v>40</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>40</v>
+        <v>124</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>40</v>
+        <v>125</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>225</v>
+        <v>127</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>233</v>
+        <v>40</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>234</v>
+        <v>40</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>235</v>
+        <v>40</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>236</v>
+        <v>121</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>237</v>
+        <v>40</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>238</v>
+        <v>40</v>
       </c>
       <c r="AQ24" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>239</v>
+        <v>40</v>
+      </c>
+      <c r="AS24" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT24" t="s" s="2">
+        <v>40</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5129,13 +5476,13 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>40</v>
@@ -5144,19 +5491,19 @@
         <v>51</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>40</v>
@@ -5205,13 +5552,13 @@
         <v>40</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>40</v>
@@ -5220,19 +5567,19 @@
         <v>62</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>246</v>
+        <v>40</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>249</v>
+        <v>40</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>40</v>
@@ -5241,15 +5588,21 @@
         <v>40</v>
       </c>
       <c r="AR25" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS25" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT25" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5260,7 +5613,7 @@
         <v>38</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>40</v>
@@ -5269,20 +5622,18 @@
         <v>40</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>251</v>
+        <v>117</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>252</v>
+        <v>118</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>254</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>40</v>
@@ -5331,19 +5682,19 @@
         <v>40</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>250</v>
+        <v>120</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>40</v>
@@ -5352,13 +5703,13 @@
         <v>40</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>235</v>
+        <v>40</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>255</v>
+        <v>121</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>249</v>
+        <v>40</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>40</v>
@@ -5367,26 +5718,32 @@
         <v>40</v>
       </c>
       <c r="AR26" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS26" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT26" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>256</v>
+        <v>234</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>256</v>
+        <v>234</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>257</v>
+        <v>95</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>38</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>40</v>
@@ -5395,23 +5752,21 @@
         <v>40</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>258</v>
+        <v>96</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>259</v>
+        <v>97</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>260</v>
+        <v>123</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>262</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>40</v>
       </c>
@@ -5447,46 +5802,46 @@
         <v>40</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>40</v>
+        <v>124</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>40</v>
+        <v>125</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>256</v>
+        <v>127</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>263</v>
+        <v>40</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>264</v>
+        <v>40</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>265</v>
+        <v>121</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>266</v>
+        <v>40</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>40</v>
@@ -5495,19 +5850,25 @@
         <v>40</v>
       </c>
       <c r="AR27" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS27" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT27" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>267</v>
+        <v>235</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>267</v>
+        <v>235</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>268</v>
+        <v>40</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5517,7 +5878,7 @@
         <v>50</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>40</v>
@@ -5526,19 +5887,19 @@
         <v>51</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>269</v>
+        <v>64</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>270</v>
+        <v>236</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>271</v>
+        <v>237</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>272</v>
+        <v>238</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>273</v>
+        <v>239</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>40</v>
@@ -5575,17 +5936,19 @@
         <v>40</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="AC28" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>40</v>
+      </c>
       <c r="AD28" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>126</v>
+        <v>40</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>267</v>
+        <v>240</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>38</v>
@@ -5594,25 +5957,25 @@
         <v>50</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>275</v>
+        <v>40</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>276</v>
+        <v>62</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>277</v>
+        <v>40</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>278</v>
+        <v>241</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>279</v>
+        <v>242</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>280</v>
+        <v>40</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>40</v>
@@ -5621,21 +5984,25 @@
         <v>40</v>
       </c>
       <c r="AR28" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS28" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT28" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>281</v>
+        <v>243</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="C29" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>268</v>
+        <v>40</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5645,7 +6012,7 @@
         <v>50</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>40</v>
@@ -5654,20 +6021,18 @@
         <v>51</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>283</v>
+        <v>117</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>270</v>
+        <v>244</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>271</v>
+        <v>245</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>40</v>
       </c>
@@ -5715,7 +6080,7 @@
         <v>40</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>38</v>
@@ -5724,42 +6089,48 @@
         <v>50</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>275</v>
+        <v>40</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>276</v>
+        <v>62</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>277</v>
+        <v>40</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>278</v>
+        <v>248</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>279</v>
+        <v>249</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>280</v>
+        <v>40</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>284</v>
+        <v>40</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>285</v>
+        <v>40</v>
+      </c>
+      <c r="AS29" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT29" t="s" s="2">
+        <v>40</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>286</v>
+        <v>250</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>286</v>
+        <v>250</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5782,18 +6153,18 @@
         <v>51</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>287</v>
+        <v>70</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>288</v>
+        <v>251</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>40</v>
       </c>
@@ -5841,7 +6212,7 @@
         <v>40</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>286</v>
+        <v>254</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>38</v>
@@ -5862,30 +6233,36 @@
         <v>40</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>291</v>
+        <v>255</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>292</v>
+        <v>256</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>293</v>
+        <v>40</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>294</v>
+        <v>40</v>
       </c>
       <c r="AR30" t="s" s="2">
-        <v>295</v>
+        <v>257</v>
+      </c>
+      <c r="AS30" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT30" t="s" s="2">
+        <v>257</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>296</v>
+        <v>258</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>296</v>
+        <v>258</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5896,7 +6273,7 @@
         <v>38</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>40</v>
@@ -5908,17 +6285,17 @@
         <v>51</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>297</v>
+        <v>117</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>298</v>
+        <v>259</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>299</v>
+        <v>260</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>300</v>
+        <v>261</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>40</v>
@@ -5967,13 +6344,13 @@
         <v>40</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>296</v>
+        <v>262</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>40</v>
@@ -5982,19 +6359,19 @@
         <v>62</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>301</v>
+        <v>40</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>302</v>
+        <v>263</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>303</v>
+        <v>264</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>304</v>
+        <v>40</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>40</v>
@@ -6003,15 +6380,21 @@
         <v>40</v>
       </c>
       <c r="AR31" t="s" s="2">
-        <v>305</v>
+        <v>40</v>
+      </c>
+      <c r="AS31" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT31" t="s" s="2">
+        <v>40</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>306</v>
+        <v>265</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>306</v>
+        <v>265</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6025,7 +6408,7 @@
         <v>50</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>40</v>
@@ -6034,19 +6417,19 @@
         <v>51</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>307</v>
+        <v>266</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>308</v>
+        <v>267</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>309</v>
+        <v>268</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>310</v>
+        <v>269</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>311</v>
+        <v>270</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>40</v>
@@ -6083,17 +6466,19 @@
         <v>40</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="AC32" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>40</v>
+      </c>
       <c r="AD32" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>126</v>
+        <v>40</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>306</v>
+        <v>271</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>38</v>
@@ -6102,46 +6487,50 @@
         <v>50</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>312</v>
+        <v>40</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>313</v>
+        <v>62</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>314</v>
+        <v>40</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>315</v>
+        <v>272</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>316</v>
+        <v>273</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>317</v>
+        <v>40</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR32" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS32" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT32" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>318</v>
+        <v>274</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>319</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>40</v>
       </c>
@@ -6153,7 +6542,7 @@
         <v>50</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>40</v>
@@ -6162,19 +6551,19 @@
         <v>51</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>320</v>
+        <v>117</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>308</v>
+        <v>275</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>309</v>
+        <v>276</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>310</v>
+        <v>277</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>311</v>
+        <v>278</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>40</v>
@@ -6223,7 +6612,7 @@
         <v>40</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>306</v>
+        <v>279</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>38</v>
@@ -6232,56 +6621,64 @@
         <v>50</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>312</v>
+        <v>40</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>313</v>
+        <v>62</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>314</v>
+        <v>40</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>315</v>
+        <v>280</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>316</v>
+        <v>281</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>317</v>
+        <v>40</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR33" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS33" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT33" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>321</v>
+        <v>282</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="C34" s="2"/>
+        <v>212</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>283</v>
+      </c>
       <c r="D34" t="s" s="2">
         <v>40</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>50</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>40</v>
@@ -6290,16 +6687,20 @@
         <v>40</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>118</v>
+        <v>213</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>40</v>
       </c>
@@ -6308,7 +6709,7 @@
         <v>40</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>40</v>
+        <v>284</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>40</v>
@@ -6323,13 +6724,13 @@
         <v>40</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>40</v>
+        <v>217</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>40</v>
+        <v>218</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>40</v>
@@ -6347,19 +6748,19 @@
         <v>40</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>120</v>
+        <v>212</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>40</v>
@@ -6371,10 +6772,10 @@
         <v>40</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>121</v>
+        <v>220</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>40</v>
+        <v>221</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>40</v>
@@ -6383,49 +6784,57 @@
         <v>40</v>
       </c>
       <c r="AR34" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS34" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT34" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>323</v>
+        <v>285</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>324</v>
+        <v>285</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>95</v>
+        <v>286</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>40</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>97</v>
+        <v>287</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>123</v>
+        <v>288</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>40</v>
       </c>
@@ -6449,75 +6858,81 @@
         <v>40</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>40</v>
+        <v>144</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>40</v>
+        <v>291</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>40</v>
+        <v>292</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>124</v>
+        <v>40</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>125</v>
+        <v>40</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>126</v>
+        <v>40</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>127</v>
+        <v>285</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>40</v>
+        <v>293</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>40</v>
+        <v>294</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>40</v>
+        <v>295</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>121</v>
+        <v>296</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>40</v>
+        <v>297</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>40</v>
+        <v>298</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR35" t="s" s="2">
-        <v>40</v>
+        <v>299</v>
+      </c>
+      <c r="AS35" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT35" t="s" s="2">
+        <v>299</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>326</v>
+        <v>300</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6525,13 +6940,13 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>50</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>40</v>
@@ -6540,19 +6955,19 @@
         <v>51</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>327</v>
+        <v>301</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>328</v>
+        <v>302</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>329</v>
+        <v>303</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>330</v>
+        <v>304</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>331</v>
+        <v>305</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>40</v>
@@ -6601,7 +7016,7 @@
         <v>40</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>332</v>
+        <v>300</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>38</v>
@@ -6616,36 +7031,42 @@
         <v>62</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>40</v>
+        <v>306</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>333</v>
+        <v>307</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>334</v>
+        <v>308</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>40</v>
+        <v>309</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>40</v>
+        <v>310</v>
       </c>
       <c r="AR36" t="s" s="2">
-        <v>335</v>
+        <v>311</v>
+      </c>
+      <c r="AS36" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AT36" t="s" s="2">
+        <v>311</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>336</v>
+        <v>312</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>337</v>
+        <v>312</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6656,36 +7077,34 @@
         <v>38</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>40</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="J37" t="s" s="2">
         <v>51</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>70</v>
+        <v>313</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>338</v>
+        <v>314</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>40</v>
       </c>
-      <c r="Q37" t="s" s="2">
-        <v>341</v>
-      </c>
+      <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
         <v>40</v>
       </c>
@@ -6705,13 +7124,13 @@
         <v>40</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>133</v>
+        <v>40</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>342</v>
+        <v>40</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>343</v>
+        <v>40</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>40</v>
@@ -6729,13 +7148,13 @@
         <v>40</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>344</v>
+        <v>312</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>40</v>
@@ -6750,13 +7169,13 @@
         <v>40</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>345</v>
+        <v>295</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>346</v>
+        <v>317</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>40</v>
+        <v>309</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>40</v>
@@ -6765,19 +7184,25 @@
         <v>40</v>
       </c>
       <c r="AR37" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS37" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT37" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>347</v>
+        <v>318</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>348</v>
+        <v>318</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>40</v>
+        <v>319</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6796,17 +7221,19 @@
         <v>51</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>117</v>
+        <v>320</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>349</v>
+        <v>321</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>323</v>
+      </c>
       <c r="O38" t="s" s="2">
-        <v>351</v>
+        <v>324</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>40</v>
@@ -6855,7 +7282,7 @@
         <v>40</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>352</v>
+        <v>318</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>38</v>
@@ -6870,19 +7297,19 @@
         <v>62</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>40</v>
+        <v>325</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>353</v>
+        <v>326</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>354</v>
+        <v>327</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>40</v>
+        <v>328</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>40</v>
@@ -6891,19 +7318,25 @@
         <v>40</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>355</v>
+        <v>40</v>
+      </c>
+      <c r="AS38" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT38" t="s" s="2">
+        <v>40</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>356</v>
+        <v>329</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>357</v>
+        <v>329</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>40</v>
+        <v>330</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6913,7 +7346,7 @@
         <v>50</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>40</v>
@@ -6922,17 +7355,19 @@
         <v>51</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>64</v>
+        <v>331</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>358</v>
+        <v>332</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="O39" t="s" s="2">
-        <v>360</v>
+        <v>335</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>40</v>
@@ -6969,19 +7404,17 @@
         <v>40</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>40</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="AC39" s="2"/>
       <c r="AD39" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>361</v>
+        <v>329</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>38</v>
@@ -6990,25 +7423,25 @@
         <v>50</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>362</v>
+        <v>337</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>62</v>
+        <v>338</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>40</v>
+        <v>339</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>363</v>
+        <v>341</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>40</v>
+        <v>342</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>40</v>
@@ -7017,19 +7450,27 @@
         <v>40</v>
       </c>
       <c r="AR39" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS39" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT39" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>364</v>
+        <v>343</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="C40" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>344</v>
+      </c>
       <c r="D40" t="s" s="2">
-        <v>40</v>
+        <v>330</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7039,7 +7480,7 @@
         <v>50</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>40</v>
@@ -7048,19 +7489,19 @@
         <v>51</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>70</v>
+        <v>345</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>366</v>
+        <v>332</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>367</v>
+        <v>333</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>368</v>
+        <v>334</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>369</v>
+        <v>335</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>40</v>
@@ -7109,7 +7550,7 @@
         <v>40</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>370</v>
+        <v>329</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>38</v>
@@ -7118,42 +7559,48 @@
         <v>50</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>40</v>
+        <v>337</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>62</v>
+        <v>338</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>40</v>
+        <v>339</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>371</v>
+        <v>341</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>40</v>
+        <v>342</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>40</v>
+        <v>346</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>40</v>
+        <v>347</v>
+      </c>
+      <c r="AS40" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AT40" t="s" s="2">
+        <v>347</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>372</v>
+        <v>348</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>372</v>
+        <v>348</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7167,29 +7614,27 @@
         <v>50</v>
       </c>
       <c r="H41" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="J41" t="s" s="2">
         <v>51</v>
       </c>
-      <c r="I41" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="J41" t="s" s="2">
-        <v>40</v>
-      </c>
       <c r="K41" t="s" s="2">
-        <v>139</v>
+        <v>349</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>373</v>
+        <v>350</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>374</v>
+        <v>351</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>376</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>40</v>
       </c>
@@ -7213,11 +7658,13 @@
         <v>40</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="Y41" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>40</v>
+      </c>
       <c r="Z41" t="s" s="2">
-        <v>377</v>
+        <v>40</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>40</v>
@@ -7235,7 +7682,7 @@
         <v>40</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>372</v>
+        <v>348</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>38</v>
@@ -7244,7 +7691,7 @@
         <v>50</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>378</v>
+        <v>40</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>62</v>
@@ -7256,34 +7703,40 @@
         <v>40</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>93</v>
+        <v>353</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>379</v>
+        <v>354</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>40</v>
+        <v>355</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>40</v>
+        <v>356</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>40</v>
+        <v>357</v>
+      </c>
+      <c r="AS41" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AT41" t="s" s="2">
+        <v>357</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>380</v>
+        <v>358</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>380</v>
+        <v>358</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>381</v>
+        <v>40</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7299,22 +7752,20 @@
         <v>40</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>139</v>
+        <v>359</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>382</v>
+        <v>360</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>384</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>385</v>
+        <v>362</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>40</v>
@@ -7339,13 +7790,13 @@
         <v>40</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>386</v>
+        <v>40</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>387</v>
+        <v>40</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>40</v>
@@ -7363,7 +7814,7 @@
         <v>40</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>380</v>
+        <v>358</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>38</v>
@@ -7378,36 +7829,42 @@
         <v>62</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>40</v>
+        <v>363</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>388</v>
+        <v>40</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>389</v>
+        <v>364</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>390</v>
+        <v>365</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>40</v>
+        <v>366</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>391</v>
+        <v>40</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>392</v>
+        <v>367</v>
+      </c>
+      <c r="AS42" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT42" t="s" s="2">
+        <v>367</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>393</v>
+        <v>368</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>393</v>
+        <v>368</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7418,31 +7875,31 @@
         <v>38</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>40</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>394</v>
+        <v>369</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>395</v>
+        <v>370</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>396</v>
+        <v>371</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>397</v>
+        <v>372</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>398</v>
+        <v>373</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>40</v>
@@ -7479,65 +7936,71 @@
         <v>40</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>40</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>393</v>
+        <v>368</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>40</v>
+        <v>374</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>62</v>
+        <v>375</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>40</v>
+        <v>376</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>399</v>
+        <v>377</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>400</v>
+        <v>378</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>40</v>
+        <v>379</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>401</v>
+        <v>40</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>402</v>
+        <v>40</v>
+      </c>
+      <c r="AS43" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT43" t="s" s="2">
+        <v>40</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>403</v>
+        <v>380</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="C44" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>381</v>
+      </c>
       <c r="D44" t="s" s="2">
         <v>40</v>
       </c>
@@ -7549,27 +8012,29 @@
         <v>50</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>40</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>139</v>
+        <v>382</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>404</v>
+        <v>370</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>405</v>
+        <v>371</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>372</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>373</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>40</v>
       </c>
@@ -7593,13 +8058,13 @@
         <v>40</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>407</v>
+        <v>40</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>408</v>
+        <v>40</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>409</v>
+        <v>40</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>40</v>
@@ -7617,7 +8082,7 @@
         <v>40</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>403</v>
+        <v>368</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>38</v>
@@ -7626,42 +8091,48 @@
         <v>50</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>40</v>
+        <v>374</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>62</v>
+        <v>375</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>411</v>
+        <v>377</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>412</v>
+        <v>378</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>413</v>
+        <v>379</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR44" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS44" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT44" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>414</v>
+        <v>383</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>414</v>
+        <v>384</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7684,20 +8155,16 @@
         <v>40</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>415</v>
+        <v>118</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>418</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>40</v>
       </c>
@@ -7721,13 +8188,13 @@
         <v>40</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>407</v>
+        <v>40</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>419</v>
+        <v>40</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>420</v>
+        <v>40</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>40</v>
@@ -7745,7 +8212,7 @@
         <v>40</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>414</v>
+        <v>120</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>38</v>
@@ -7757,7 +8224,7 @@
         <v>40</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>40</v>
@@ -7766,10 +8233,10 @@
         <v>40</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>421</v>
+        <v>40</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>422</v>
+        <v>121</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>40</v>
@@ -7781,26 +8248,32 @@
         <v>40</v>
       </c>
       <c r="AR45" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS45" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT45" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>423</v>
+        <v>385</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>423</v>
+        <v>386</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>38</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>40</v>
@@ -7812,16 +8285,16 @@
         <v>40</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>424</v>
+        <v>96</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>425</v>
+        <v>97</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>426</v>
+        <v>123</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>427</v>
+        <v>99</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7859,63 +8332,69 @@
         <v>40</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>40</v>
+        <v>124</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>40</v>
+        <v>125</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>423</v>
+        <v>127</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>428</v>
+        <v>40</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>429</v>
+        <v>40</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>430</v>
+        <v>121</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>431</v>
+        <v>40</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>432</v>
+        <v>40</v>
+      </c>
+      <c r="AS46" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT46" t="s" s="2">
+        <v>40</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>433</v>
+        <v>387</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>433</v>
+        <v>388</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7935,21 +8414,23 @@
         <v>40</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>434</v>
+        <v>389</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>435</v>
+        <v>390</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>436</v>
+        <v>391</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>392</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>393</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>40</v>
       </c>
@@ -7997,7 +8478,7 @@
         <v>40</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>433</v>
+        <v>394</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>38</v>
@@ -8015,33 +8496,39 @@
         <v>40</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>438</v>
+        <v>40</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>439</v>
+        <v>395</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>440</v>
+        <v>396</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>441</v>
+        <v>40</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>40</v>
+        <v>397</v>
+      </c>
+      <c r="AS47" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT47" t="s" s="2">
+        <v>397</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>442</v>
+        <v>398</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>442</v>
+        <v>399</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8052,36 +8539,36 @@
         <v>38</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>40</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>443</v>
+        <v>70</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>444</v>
+        <v>400</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>447</v>
+        <v>402</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>40</v>
       </c>
-      <c r="Q48" s="2"/>
+      <c r="Q48" t="s" s="2">
+        <v>403</v>
+      </c>
       <c r="R48" t="s" s="2">
         <v>40</v>
       </c>
@@ -8101,13 +8588,13 @@
         <v>40</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>40</v>
+        <v>133</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>40</v>
+        <v>404</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>40</v>
+        <v>405</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>40</v>
@@ -8125,19 +8612,19 @@
         <v>40</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>442</v>
+        <v>406</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>448</v>
+        <v>62</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>40</v>
@@ -8146,10 +8633,10 @@
         <v>40</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>449</v>
+        <v>407</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>450</v>
+        <v>408</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>40</v>
@@ -8161,15 +8648,21 @@
         <v>40</v>
       </c>
       <c r="AR48" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS48" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT48" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>451</v>
+        <v>409</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>451</v>
+        <v>410</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8189,19 +8682,21 @@
         <v>40</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K49" t="s" s="2">
         <v>117</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>118</v>
+        <v>411</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>119</v>
+        <v>412</v>
       </c>
       <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>413</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>40</v>
       </c>
@@ -8249,7 +8744,7 @@
         <v>40</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>120</v>
+        <v>414</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>38</v>
@@ -8261,7 +8756,7 @@
         <v>40</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>40</v>
@@ -8270,10 +8765,10 @@
         <v>40</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>40</v>
+        <v>415</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>121</v>
+        <v>416</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>40</v>
@@ -8285,26 +8780,32 @@
         <v>40</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>40</v>
+        <v>417</v>
+      </c>
+      <c r="AS49" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT49" t="s" s="2">
+        <v>417</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>452</v>
+        <v>418</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>452</v>
+        <v>419</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>38</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>40</v>
@@ -8313,21 +8814,21 @@
         <v>40</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>97</v>
+        <v>420</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>421</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" t="s" s="2">
+        <v>422</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>40</v>
       </c>
@@ -8375,19 +8876,19 @@
         <v>40</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>127</v>
+        <v>423</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>40</v>
+        <v>424</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>40</v>
@@ -8396,10 +8897,10 @@
         <v>40</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>40</v>
+        <v>415</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>121</v>
+        <v>425</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>40</v>
@@ -8411,50 +8912,56 @@
         <v>40</v>
       </c>
       <c r="AR50" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS50" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT50" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>453</v>
+        <v>426</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>453</v>
+        <v>427</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>454</v>
+        <v>40</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>38</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>40</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="J51" t="s" s="2">
         <v>51</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>455</v>
+        <v>428</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>456</v>
+        <v>429</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>99</v>
+        <v>430</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>105</v>
+        <v>431</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>40</v>
@@ -8503,19 +9010,19 @@
         <v>40</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>457</v>
+        <v>432</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>40</v>
@@ -8524,10 +9031,10 @@
         <v>40</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>40</v>
+        <v>415</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>93</v>
+        <v>433</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>40</v>
@@ -8539,15 +9046,21 @@
         <v>40</v>
       </c>
       <c r="AR51" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS51" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT51" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>458</v>
+        <v>434</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>458</v>
+        <v>434</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8561,7 +9074,7 @@
         <v>50</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>40</v>
@@ -8570,16 +9083,20 @@
         <v>40</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>459</v>
+        <v>139</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>460</v>
+        <v>435</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+        <v>436</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>438</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>40</v>
       </c>
@@ -8603,13 +9120,11 @@
         <v>40</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>40</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>40</v>
+        <v>439</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>40</v>
@@ -8627,7 +9142,7 @@
         <v>40</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>458</v>
+        <v>434</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>38</v>
@@ -8636,7 +9151,7 @@
         <v>50</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>462</v>
+        <v>440</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>62</v>
@@ -8648,10 +9163,10 @@
         <v>40</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>463</v>
+        <v>93</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>464</v>
+        <v>441</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>40</v>
@@ -8663,26 +9178,32 @@
         <v>40</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>465</v>
+        <v>40</v>
+      </c>
+      <c r="AS52" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT52" t="s" s="2">
+        <v>40</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>466</v>
+        <v>442</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>466</v>
+        <v>442</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>40</v>
+        <v>443</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>38</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>40</v>
@@ -8694,16 +9215,20 @@
         <v>40</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>459</v>
+        <v>139</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>467</v>
+        <v>444</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>445</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>447</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>40</v>
       </c>
@@ -8727,13 +9252,11 @@
         <v>40</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>40</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>40</v>
+        <v>448</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>40</v>
@@ -8751,16 +9274,16 @@
         <v>40</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>466</v>
+        <v>442</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>462</v>
+        <v>40</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>62</v>
@@ -8769,33 +9292,39 @@
         <v>40</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>40</v>
+        <v>449</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>469</v>
+        <v>451</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>40</v>
+        <v>452</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR53" t="s" s="2">
-        <v>470</v>
+        <v>453</v>
+      </c>
+      <c r="AS53" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT53" t="s" s="2">
+        <v>453</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>471</v>
+        <v>454</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>471</v>
+        <v>454</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8806,7 +9335,7 @@
         <v>38</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>40</v>
@@ -8818,19 +9347,19 @@
         <v>40</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>139</v>
+        <v>455</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>472</v>
+        <v>456</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>473</v>
+        <v>457</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>474</v>
+        <v>458</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>40</v>
@@ -8855,13 +9384,13 @@
         <v>40</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>476</v>
+        <v>40</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>477</v>
+        <v>40</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>40</v>
@@ -8879,13 +9408,13 @@
         <v>40</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>471</v>
+        <v>454</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>40</v>
@@ -8897,13 +9426,13 @@
         <v>40</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>478</v>
+        <v>40</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>479</v>
+        <v>460</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>390</v>
+        <v>461</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>40</v>
@@ -8912,18 +9441,24 @@
         <v>40</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>40</v>
+        <v>462</v>
       </c>
       <c r="AR54" t="s" s="2">
-        <v>40</v>
+        <v>463</v>
+      </c>
+      <c r="AS54" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AT54" t="s" s="2">
+        <v>463</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>480</v>
+        <v>464</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>480</v>
+        <v>464</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8934,7 +9469,7 @@
         <v>38</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>40</v>
@@ -8949,17 +9484,15 @@
         <v>139</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>481</v>
+        <v>465</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>482</v>
+        <v>466</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>484</v>
-      </c>
+        <v>467</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>40</v>
       </c>
@@ -8983,13 +9516,13 @@
         <v>40</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>407</v>
+        <v>468</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>485</v>
+        <v>469</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>486</v>
+        <v>470</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>40</v>
@@ -9007,13 +9540,13 @@
         <v>40</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>480</v>
+        <v>464</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>40</v>
@@ -9025,33 +9558,39 @@
         <v>40</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>390</v>
+        <v>473</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>40</v>
+        <v>474</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR55" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS55" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT55" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9074,17 +9613,19 @@
         <v>40</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>488</v>
+        <v>139</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>489</v>
+        <v>476</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>477</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>478</v>
+      </c>
       <c r="O56" t="s" s="2">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>40</v>
@@ -9109,13 +9650,13 @@
         <v>40</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>40</v>
+        <v>468</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>40</v>
+        <v>480</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>40</v>
+        <v>481</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>40</v>
@@ -9133,7 +9674,7 @@
         <v>40</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>38</v>
@@ -9154,10 +9695,10 @@
         <v>40</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>40</v>
+        <v>482</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>40</v>
@@ -9169,15 +9710,21 @@
         <v>40</v>
       </c>
       <c r="AR56" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS56" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT56" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9200,15 +9747,17 @@
         <v>40</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>117</v>
+        <v>485</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>487</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>488</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>40</v>
@@ -9257,7 +9806,7 @@
         <v>40</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>38</v>
@@ -9275,33 +9824,39 @@
         <v>40</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>40</v>
+        <v>489</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>463</v>
+        <v>490</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>40</v>
+        <v>492</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR57" t="s" s="2">
-        <v>40</v>
+        <v>493</v>
+      </c>
+      <c r="AS57" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT57" t="s" s="2">
+        <v>493</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9312,7 +9867,7 @@
         <v>38</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>40</v>
@@ -9321,19 +9876,19 @@
         <v>40</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9383,13 +9938,13 @@
         <v>40</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>40</v>
@@ -9401,33 +9956,39 @@
         <v>40</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>40</v>
+        <v>499</v>
       </c>
       <c r="AM58" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP58" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="AN58" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>40</v>
-      </c>
       <c r="AQ58" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR58" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS58" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT58" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9447,21 +10008,23 @@
         <v>40</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="N59" t="s" s="2">
+      <c r="O59" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>40</v>
       </c>
@@ -9509,7 +10072,7 @@
         <v>40</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>38</v>
@@ -9521,7 +10084,7 @@
         <v>40</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>62</v>
+        <v>509</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>40</v>
@@ -9530,10 +10093,10 @@
         <v>40</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>40</v>
@@ -9545,15 +10108,21 @@
         <v>40</v>
       </c>
       <c r="AR59" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS59" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT59" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9564,7 +10133,7 @@
         <v>38</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>40</v>
@@ -9573,23 +10142,19 @@
         <v>40</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>443</v>
+        <v>117</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>511</v>
+        <v>118</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>514</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>40</v>
       </c>
@@ -9637,19 +10202,19 @@
         <v>40</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>510</v>
+        <v>120</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>40</v>
@@ -9658,10 +10223,10 @@
         <v>40</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>515</v>
+        <v>40</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>516</v>
+        <v>121</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>40</v>
@@ -9673,26 +10238,32 @@
         <v>40</v>
       </c>
       <c r="AR60" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS60" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT60" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>38</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>40</v>
@@ -9704,15 +10275,17 @@
         <v>40</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>123</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>99</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>40</v>
@@ -9761,19 +10334,19 @@
         <v>40</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>40</v>
@@ -9797,19 +10370,25 @@
         <v>40</v>
       </c>
       <c r="AR61" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS61" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT61" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>95</v>
+        <v>515</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9822,24 +10401,26 @@
         <v>40</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K62" t="s" s="2">
         <v>96</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>97</v>
+        <v>516</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>123</v>
+        <v>517</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="O62" s="2"/>
+      <c r="O62" t="s" s="2">
+        <v>105</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>40</v>
       </c>
@@ -9887,7 +10468,7 @@
         <v>40</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>127</v>
+        <v>518</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>38</v>
@@ -9911,7 +10492,7 @@
         <v>40</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>40</v>
@@ -9923,6 +10504,12 @@
         <v>40</v>
       </c>
       <c r="AR62" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS62" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT62" t="s" s="2">
         <v>40</v>
       </c>
     </row>
@@ -9935,39 +10522,35 @@
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>454</v>
+        <v>40</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>38</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>40</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>96</v>
+        <v>520</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>455</v>
+        <v>521</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>105</v>
-      </c>
+        <v>522</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>40</v>
       </c>
@@ -10015,19 +10598,19 @@
         <v>40</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>457</v>
+        <v>519</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>40</v>
+        <v>523</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>40</v>
@@ -10036,10 +10619,10 @@
         <v>40</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>40</v>
+        <v>524</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>93</v>
+        <v>525</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>40</v>
@@ -10051,15 +10634,21 @@
         <v>40</v>
       </c>
       <c r="AR63" t="s" s="2">
-        <v>40</v>
+        <v>526</v>
+      </c>
+      <c r="AS63" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT63" t="s" s="2">
+        <v>526</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10067,7 +10656,7 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>50</v>
@@ -10079,23 +10668,19 @@
         <v>40</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>139</v>
+        <v>520</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>529</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>40</v>
       </c>
@@ -10119,13 +10704,13 @@
         <v>40</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>407</v>
+        <v>40</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>524</v>
+        <v>40</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>232</v>
+        <v>40</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>40</v>
@@ -10143,16 +10728,16 @@
         <v>40</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AH64" t="s" s="2">
         <v>50</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>40</v>
+        <v>523</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>62</v>
@@ -10161,16 +10746,16 @@
         <v>40</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>525</v>
+        <v>40</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>235</v>
+        <v>524</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>236</v>
+        <v>530</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>237</v>
+        <v>40</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>40</v>
@@ -10179,15 +10764,21 @@
         <v>40</v>
       </c>
       <c r="AR64" t="s" s="2">
-        <v>40</v>
+        <v>531</v>
+      </c>
+      <c r="AS64" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT64" t="s" s="2">
+        <v>531</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10207,22 +10798,22 @@
         <v>40</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>307</v>
+        <v>139</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>311</v>
+        <v>536</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>40</v>
@@ -10247,13 +10838,13 @@
         <v>40</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>40</v>
+        <v>537</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>40</v>
+        <v>538</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>40</v>
@@ -10271,7 +10862,7 @@
         <v>40</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>38</v>
@@ -10289,33 +10880,39 @@
         <v>40</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>530</v>
+        <v>539</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>315</v>
+        <v>540</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>316</v>
+        <v>451</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>317</v>
+        <v>40</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR65" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS65" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT65" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>531</v>
+        <v>541</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>531</v>
+        <v>541</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10326,7 +10923,7 @@
         <v>38</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>40</v>
@@ -10341,16 +10938,16 @@
         <v>139</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>533</v>
+        <v>543</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>534</v>
+        <v>544</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>376</v>
+        <v>545</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>40</v>
@@ -10375,13 +10972,13 @@
         <v>40</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>144</v>
+        <v>468</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>377</v>
+        <v>547</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>40</v>
@@ -10399,16 +10996,16 @@
         <v>40</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>531</v>
+        <v>541</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>536</v>
+        <v>40</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>62</v>
@@ -10417,13 +11014,13 @@
         <v>40</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>40</v>
+        <v>539</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>93</v>
+        <v>540</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>379</v>
+        <v>451</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>40</v>
@@ -10435,26 +11032,32 @@
         <v>40</v>
       </c>
       <c r="AR66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS66" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT66" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>537</v>
+        <v>548</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>537</v>
+        <v>548</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>381</v>
+        <v>40</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>38</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>40</v>
@@ -10466,19 +11069,17 @@
         <v>40</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>139</v>
+        <v>549</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>382</v>
+        <v>550</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>384</v>
-      </c>
+        <v>551</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>385</v>
+        <v>552</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>40</v>
@@ -10503,13 +11104,13 @@
         <v>40</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>386</v>
+        <v>40</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>387</v>
+        <v>40</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>40</v>
@@ -10527,13 +11128,13 @@
         <v>40</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>537</v>
+        <v>548</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>40</v>
@@ -10545,33 +11146,39 @@
         <v>40</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>388</v>
+        <v>40</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>389</v>
+        <v>40</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>390</v>
+        <v>553</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>391</v>
+        <v>40</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>40</v>
       </c>
       <c r="AR67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS67" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT67" t="s" s="2">
         <v>40</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>538</v>
+        <v>554</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>538</v>
+        <v>554</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10582,7 +11189,7 @@
         <v>38</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>40</v>
@@ -10594,20 +11201,16 @@
         <v>40</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>41</v>
+        <v>117</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>539</v>
+        <v>555</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>447</v>
-      </c>
+        <v>556</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>40</v>
       </c>
@@ -10655,13 +11258,13 @@
         <v>40</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>538</v>
+        <v>554</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>38</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>40</v>
@@ -10676,26 +11279,1496 @@
         <v>40</v>
       </c>
       <c r="AM68" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AQ68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AR68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS68" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT68" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AQ69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AR69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS69" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT69" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AQ70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AR70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS70" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT70" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="P71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AQ71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AR71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS71" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT71" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AQ72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AR72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS72" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT72" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AQ73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AR73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS73" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT73" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AQ74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AR74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS74" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT74" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="P75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AP75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AQ75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AR75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS75" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT75" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="P76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP76" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AQ76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AR76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS76" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT76" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="P77" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP77" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AQ77" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AR77" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS77" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT77" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="P78" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AL78" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="AN68" t="s" s="2">
+      <c r="AM78" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="AO68" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AQ68" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="AR68" t="s" s="2">
+      <c r="AN78" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP78" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AQ78" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AR78" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS78" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT78" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="P79" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AO79" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AP79" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AQ79" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AR79" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AS79" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="AT79" t="s" s="2">
         <v>40</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR68">
+  <autoFilter ref="A1:AT79">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10705,7 +12778,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI67">
+  <conditionalFormatting sqref="A2:AI78">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3423" uniqueCount="647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3423" uniqueCount="648">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -255,10 +255,10 @@
     <t>Mapping: SNOMED CT Attribute Binding</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
     <t>Vital Signs
@@ -941,6 +941,10 @@
   </si>
   <si>
     <t>Coding.code</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+inv-8:843: fixed value "laboratory" {null}</t>
   </si>
   <si>
     <t>C*E.1</t>
@@ -1114,6 +1118,9 @@
   </si>
   <si>
     <t>FiveWs.subject</t>
+  </si>
+  <si>
+    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (#2-63 &gt; 63-.01)</t>
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.LRDFN
@@ -1137,9 +1144,6 @@
 Micro.VirologyReports.LRDFN</t>
   </si>
   <si>
-    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (#2-63 &gt; 63-.01)</t>
-  </si>
-  <si>
     <t>Observation.focus</t>
   </si>
   <si>
@@ -1249,6 +1253,9 @@
   <si>
     <t xml:space="preserve">dateTime
 </t>
+  </si>
+  <si>
+    <t>845: source value from CHEM, HEM, TOX, RIA, SER, etc. - DATE/TIME SPECIMEN TAKEN (#63.04-.01)</t>
   </si>
   <si>
     <t>Chem.LabChem.LabChemSpecimenDateTime
@@ -1257,9 +1264,6 @@
 Chem.PatientLabChem.LabChemSpecimenDateTime</t>
   </si>
   <si>
-    <t>845: source value from CHEM, HEM, TOX, RIA, SER, etc. - DATE/TIME SPECIMEN TAKEN (#63.04-.01)</t>
-  </si>
-  <si>
     <t>Observation.issued</t>
   </si>
   <si>
@@ -1283,6 +1287,9 @@
   </si>
   <si>
     <t>FiveWs.recorded</t>
+  </si>
+  <si>
+    <t>858: source value from CHEM, HEM, TOX, RIA, SER, etc. - DATE REPORT COMPLETED (#63.04-.03)</t>
   </si>
   <si>
     <t>Chem.LabChem.LabChemCompleteDateTime
@@ -1291,9 +1298,6 @@
 Chem.PatientLabChem.LabChemCompleteDateTime</t>
   </si>
   <si>
-    <t>858: source value from CHEM, HEM, TOX, RIA, SER, etc. - DATE REPORT COMPLETED (#63.04-.03)</t>
-  </si>
-  <si>
     <t>Observation.performer</t>
   </si>
   <si>
@@ -1613,10 +1617,10 @@
     <t>subjectOf.observationEvent[code="annotation"].value</t>
   </si>
   <si>
+    <t>846: source value from CHEM, HEM, TOX, RIA, SER, etc. - COMMENT &gt; COMMENT - COMMENT (#63.04-.99 &gt; 63.041-.01)</t>
+  </si>
+  <si>
     <t>Chem.LabPanel.LabPanelComment</t>
-  </si>
-  <si>
-    <t>846: source value from CHEM, HEM, TOX, RIA, SER, etc. - COMMENT &gt; COMMENT - COMMENT (#63.04-.99 &gt; 63.041-.01)</t>
   </si>
   <si>
     <t>Observation.bodySite</t>
@@ -2418,10 +2422,10 @@
     <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="50.07421875" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="218.56640625" customWidth="true" bestFit="true"/>
-    <col min="45" max="45" width="50.07421875" customWidth="true" bestFit="true"/>
-    <col min="46" max="46" width="218.56640625" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="218.56640625" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="50.07421875" customWidth="true" bestFit="true"/>
+    <col min="45" max="45" width="218.56640625" customWidth="true" bestFit="true"/>
+    <col min="46" max="46" width="50.07421875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4668,16 +4672,16 @@
         <v>84</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>84</v>
+        <v>210</v>
       </c>
       <c r="AR17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AS17" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="AS17" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AT17" t="s" s="2">
-        <v>210</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" hidden="true">
@@ -5326,16 +5330,16 @@
         <v>84</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>84</v>
+        <v>255</v>
       </c>
       <c r="AR22" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AS22" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="AS22" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AT22" t="s" s="2">
-        <v>255</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" hidden="true">
@@ -6493,7 +6497,7 @@
         <v>84</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>106</v>
+        <v>299</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>84</v>
@@ -6502,10 +6506,10 @@
         <v>84</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>84</v>
@@ -6514,24 +6518,24 @@
         <v>84</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>84</v>
+        <v>302</v>
       </c>
       <c r="AR31" t="s" s="2">
-        <v>301</v>
+        <v>84</v>
       </c>
       <c r="AS31" t="s" s="2">
-        <v>84</v>
+        <v>302</v>
       </c>
       <c r="AT31" t="s" s="2">
-        <v>301</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6557,14 +6561,14 @@
         <v>161</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -6613,7 +6617,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6634,10 +6638,10 @@
         <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>84</v>
@@ -6660,10 +6664,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6686,19 +6690,19 @@
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6747,7 +6751,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6768,10 +6772,10 @@
         <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>84</v>
@@ -6794,10 +6798,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6823,16 +6827,16 @@
         <v>161</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6881,7 +6885,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6902,10 +6906,10 @@
         <v>84</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>84</v>
@@ -6928,13 +6932,13 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>256</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>84</v>
@@ -6978,7 +6982,7 @@
         <v>84</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>84</v>
@@ -7064,14 +7068,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -7093,16 +7097,16 @@
         <v>183</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -7130,10 +7134,10 @@
         <v>188</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>84</v>
@@ -7151,7 +7155,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>94</v>
@@ -7166,42 +7170,42 @@
         <v>106</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>84</v>
+        <v>344</v>
       </c>
       <c r="AR36" t="s" s="2">
-        <v>343</v>
+        <v>84</v>
       </c>
       <c r="AS36" t="s" s="2">
-        <v>84</v>
+        <v>344</v>
       </c>
       <c r="AT36" t="s" s="2">
-        <v>343</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7224,19 +7228,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -7285,7 +7289,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -7300,42 +7304,42 @@
         <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AR37" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="AS37" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AS37" t="s" s="2">
-        <v>354</v>
-      </c>
       <c r="AT37" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7358,16 +7362,16 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7417,7 +7421,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7438,13 +7442,13 @@
         <v>84</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>84</v>
@@ -7464,14 +7468,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7490,19 +7494,19 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -7551,7 +7555,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7566,19 +7570,19 @@
         <v>106</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>84</v>
@@ -7598,14 +7602,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7624,19 +7628,19 @@
         <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7673,7 +7677,7 @@
         <v>84</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
@@ -7683,7 +7687,7 @@
         <v>170</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7692,25 +7696,25 @@
         <v>94</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>84</v>
@@ -7730,16 +7734,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7758,19 +7762,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7819,7 +7823,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7828,48 +7832,48 @@
         <v>94</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AR41" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AS41" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="AS41" t="s" s="2">
-        <v>390</v>
-      </c>
       <c r="AT41" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7892,16 +7896,16 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7951,7 +7955,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7972,36 +7976,36 @@
         <v>84</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AR42" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AS42" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AS42" t="s" s="2">
-        <v>400</v>
-      </c>
       <c r="AT42" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8027,14 +8031,14 @@
         <v>219</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
@@ -8083,7 +8087,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -8098,42 +8102,42 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>84</v>
+        <v>411</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>410</v>
+        <v>84</v>
       </c>
       <c r="AS43" t="s" s="2">
-        <v>84</v>
+        <v>411</v>
       </c>
       <c r="AT43" t="s" s="2">
-        <v>410</v>
+        <v>84</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8156,19 +8160,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -8205,7 +8209,7 @@
         <v>84</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AC44" s="2"/>
       <c r="AD44" t="s" s="2">
@@ -8215,7 +8219,7 @@
         <v>170</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -8224,28 +8228,28 @@
         <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -8262,13 +8266,13 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>84</v>
@@ -8290,19 +8294,19 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -8351,7 +8355,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8360,28 +8364,28 @@
         <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -8398,10 +8402,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8528,10 +8532,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8660,10 +8664,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8686,19 +8690,19 @@
         <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
@@ -8747,7 +8751,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8768,10 +8772,10 @@
         <v>84</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>84</v>
@@ -8780,24 +8784,24 @@
         <v>84</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>84</v>
+        <v>441</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>440</v>
+        <v>84</v>
       </c>
       <c r="AS48" t="s" s="2">
-        <v>84</v>
+        <v>441</v>
       </c>
       <c r="AT48" t="s" s="2">
-        <v>440</v>
+        <v>84</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8823,20 +8827,20 @@
         <v>114</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q49" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="R49" t="s" s="2">
         <v>84</v>
@@ -8860,10 +8864,10 @@
         <v>177</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
@@ -8881,7 +8885,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8902,10 +8906,10 @@
         <v>84</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>84</v>
@@ -8928,10 +8932,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8957,14 +8961,14 @@
         <v>161</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -9013,7 +9017,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -9034,10 +9038,10 @@
         <v>84</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>84</v>
@@ -9046,24 +9050,24 @@
         <v>84</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>84</v>
+        <v>461</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>460</v>
+        <v>84</v>
       </c>
       <c r="AS50" t="s" s="2">
-        <v>84</v>
+        <v>461</v>
       </c>
       <c r="AT50" t="s" s="2">
-        <v>460</v>
+        <v>84</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9089,14 +9093,14 @@
         <v>108</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -9145,7 +9149,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -9154,7 +9158,7 @@
         <v>94</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>106</v>
@@ -9166,10 +9170,10 @@
         <v>84</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>84</v>
@@ -9192,10 +9196,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9221,16 +9225,16 @@
         <v>114</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -9279,7 +9283,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9300,10 +9304,10 @@
         <v>84</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>84</v>
@@ -9326,10 +9330,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9355,16 +9359,16 @@
         <v>183</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>84</v>
@@ -9393,7 +9397,7 @@
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>84</v>
@@ -9411,7 +9415,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -9420,7 +9424,7 @@
         <v>94</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>106</v>
@@ -9435,7 +9439,7 @@
         <v>137</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>84</v>
@@ -9458,14 +9462,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -9487,16 +9491,16 @@
         <v>183</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>84</v>
@@ -9525,7 +9529,7 @@
       </c>
       <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>84</v>
@@ -9543,7 +9547,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9561,39 +9565,39 @@
         <v>84</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>84</v>
+        <v>497</v>
       </c>
       <c r="AR54" t="s" s="2">
-        <v>496</v>
+        <v>84</v>
       </c>
       <c r="AS54" t="s" s="2">
-        <v>84</v>
+        <v>497</v>
       </c>
       <c r="AT54" t="s" s="2">
-        <v>496</v>
+        <v>84</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9616,19 +9620,19 @@
         <v>84</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>84</v>
@@ -9677,7 +9681,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9698,10 +9702,10 @@
         <v>84</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>84</v>
@@ -9710,24 +9714,24 @@
         <v>84</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AR55" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AS55" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="AS55" t="s" s="2">
-        <v>505</v>
-      </c>
       <c r="AT55" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9753,13 +9757,13 @@
         <v>183</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9785,13 +9789,13 @@
         <v>84</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>84</v>
@@ -9809,7 +9813,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9827,19 +9831,19 @@
         <v>84</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9856,10 +9860,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9885,16 +9889,16 @@
         <v>183</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>84</v>
@@ -9919,13 +9923,13 @@
         <v>84</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>84</v>
@@ -9943,7 +9947,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9964,10 +9968,10 @@
         <v>84</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>84</v>
@@ -9990,10 +9994,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10016,16 +10020,16 @@
         <v>84</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -10075,7 +10079,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -10093,39 +10097,39 @@
         <v>84</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>84</v>
+        <v>537</v>
       </c>
       <c r="AR58" t="s" s="2">
-        <v>536</v>
+        <v>84</v>
       </c>
       <c r="AS58" t="s" s="2">
-        <v>84</v>
+        <v>537</v>
       </c>
       <c r="AT58" t="s" s="2">
-        <v>536</v>
+        <v>84</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10148,16 +10152,16 @@
         <v>84</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -10207,7 +10211,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10225,19 +10229,19 @@
         <v>84</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -10254,10 +10258,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10280,19 +10284,19 @@
         <v>84</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -10341,7 +10345,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10353,7 +10357,7 @@
         <v>84</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>84</v>
@@ -10362,10 +10366,10 @@
         <v>84</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>84</v>
@@ -10388,10 +10392,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10518,10 +10522,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10650,14 +10654,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -10679,10 +10683,10 @@
         <v>140</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>143</v>
@@ -10737,7 +10741,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10784,10 +10788,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10810,13 +10814,13 @@
         <v>84</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10867,7 +10871,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10876,7 +10880,7 @@
         <v>94</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>106</v>
@@ -10888,10 +10892,10 @@
         <v>84</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>84</v>
@@ -10900,24 +10904,24 @@
         <v>84</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>84</v>
+        <v>570</v>
       </c>
       <c r="AR64" t="s" s="2">
-        <v>569</v>
+        <v>84</v>
       </c>
       <c r="AS64" t="s" s="2">
-        <v>84</v>
+        <v>570</v>
       </c>
       <c r="AT64" t="s" s="2">
-        <v>569</v>
+        <v>84</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10940,13 +10944,13 @@
         <v>84</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10997,7 +11001,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -11006,7 +11010,7 @@
         <v>94</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>106</v>
@@ -11018,10 +11022,10 @@
         <v>84</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>84</v>
@@ -11030,24 +11034,24 @@
         <v>84</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>84</v>
+        <v>575</v>
       </c>
       <c r="AR65" t="s" s="2">
-        <v>574</v>
+        <v>84</v>
       </c>
       <c r="AS65" t="s" s="2">
-        <v>84</v>
+        <v>575</v>
       </c>
       <c r="AT65" t="s" s="2">
-        <v>574</v>
+        <v>84</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11073,16 +11077,16 @@
         <v>183</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>84</v>
@@ -11110,10 +11114,10 @@
         <v>118</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>84</v>
@@ -11131,7 +11135,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -11149,13 +11153,13 @@
         <v>84</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>84</v>
@@ -11178,10 +11182,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11207,16 +11211,16 @@
         <v>183</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>84</v>
@@ -11241,13 +11245,13 @@
         <v>84</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>84</v>
@@ -11265,7 +11269,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -11283,13 +11287,13 @@
         <v>84</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>84</v>
@@ -11312,10 +11316,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11338,17 +11342,17 @@
         <v>84</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>84</v>
@@ -11397,7 +11401,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -11421,7 +11425,7 @@
         <v>84</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>84</v>
@@ -11444,10 +11448,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11473,10 +11477,10 @@
         <v>161</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -11527,7 +11531,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11548,10 +11552,10 @@
         <v>84</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>84</v>
@@ -11574,10 +11578,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11600,16 +11604,16 @@
         <v>95</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -11659,7 +11663,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11680,10 +11684,10 @@
         <v>84</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>84</v>
@@ -11706,10 +11710,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11732,16 +11736,16 @@
         <v>95</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -11791,7 +11795,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11812,10 +11816,10 @@
         <v>84</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>84</v>
@@ -11838,10 +11842,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11864,19 +11868,19 @@
         <v>95</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>84</v>
@@ -11925,7 +11929,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11946,10 +11950,10 @@
         <v>84</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>84</v>
@@ -11972,10 +11976,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12102,10 +12106,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12234,14 +12238,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -12263,10 +12267,10 @@
         <v>140</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>143</v>
@@ -12321,7 +12325,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12368,10 +12372,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12397,16 +12401,16 @@
         <v>183</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>84</v>
@@ -12431,13 +12435,13 @@
         <v>84</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>84</v>
@@ -12455,7 +12459,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>94</v>
@@ -12473,16 +12477,16 @@
         <v>84</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>84</v>
@@ -12502,10 +12506,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12528,19 +12532,19 @@
         <v>95</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>84</v>
@@ -12589,7 +12593,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12607,19 +12611,19 @@
         <v>84</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>84</v>
@@ -12636,10 +12640,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12665,16 +12669,16 @@
         <v>183</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>84</v>
@@ -12702,10 +12706,10 @@
         <v>188</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>84</v>
@@ -12723,7 +12727,7 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12732,7 +12736,7 @@
         <v>94</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>106</v>
@@ -12747,7 +12751,7 @@
         <v>137</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>84</v>
@@ -12770,14 +12774,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -12799,16 +12803,16 @@
         <v>183</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>84</v>
@@ -12836,28 +12840,28 @@
         <v>188</v>
       </c>
       <c r="Y79" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF79" t="s" s="2">
         <v>642</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>641</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12875,19 +12879,19 @@
         <v>84</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>84</v>
@@ -12904,10 +12908,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12933,16 +12937,16 @@
         <v>85</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>84</v>
@@ -12991,7 +12995,7 @@
         <v>84</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -13012,10 +13016,10 @@
         <v>84</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -944,7 +944,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-8:843: fixed value "laboratory" {null}</t>
+inv-9:843: fixed value = laboratory {null}</t>
   </si>
   <si>
     <t>C*E.1</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T19:04:11+00:00</t>
+    <t>2023-12-21T07:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -944,7 +944,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-9:843: fixed value = laboratory {null}</t>
+inv-10:843: fixed value = laboratory {null}</t>
   </si>
   <si>
     <t>C*E.1</t>
@@ -1417,7 +1417,7 @@
     <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
   </si>
   <si>
-    <t>857: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST (#63.04-2 through 862)</t>
+    <t>857: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST (#63.04-2+through+862)</t>
   </si>
   <si>
     <t>Observation.value[x]:valueQuantity.comparator</t>
@@ -1712,7 +1712,7 @@
     <t>704319004 |Inherent in|</t>
   </si>
   <si>
-    <t>+: reference from CHEM, HEM, TOX, RIA, SER, etc. - ACCESSION (#63.04-.06)</t>
+    <t>1656: reference from CHEM, HEM, TOX, RIA, SER, etc. - ACCESSION (#63.04-.06)</t>
   </si>
   <si>
     <t>Observation.device</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA CHEM, HEM, TOX, RIA, SER, etc. (file 63.04) to FHIR Observation</t>
+    <t>This StructureDefinition contains the maps for VistA file CHEM, HEM, TOX, RIA, SER, etc. (#63.04) to LabObservationObservation</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AT$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$69</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3423" uniqueCount="648">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2821" uniqueCount="585">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.13.0</t>
+    <t>0.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Lab Observation: Chem, hem, tox, ria, ser {Observation}</t>
+    <t>Lab Observation: Chem, hem, tox, ria, ser Observation</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-03T19:41:50+00:00</t>
+    <t>2024-01-13T13:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file CHEM, HEM, TOX, RIA, SER, etc. (#63.04) to LabObservationObservation</t>
+    <t>This StructureDefinition contains the maps for VistA file CHEM, HEM, TOX, RIA, SER, etc. (#63.04) to us-core-observation-lab</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/StructureDefinition/LabObservationObservation</t>
+    <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-observation-lab</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -841,192 +841,6 @@
   </si>
   <si>
     <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.category.id</t>
-  </si>
-  <si>
-    <t>Observation.category.extension</t>
-  </si>
-  <si>
-    <t>Observation.category.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-10:843: fixed value = laboratory {null}</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>843: fixed value = laboratory</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Observation.category.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>Observation.category:Laboratory</t>
@@ -1118,30 +932,6 @@
   </si>
   <si>
     <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (#2-63 &gt; 63-.01)</t>
-  </si>
-  <si>
-    <t>Micro.AntibioticSensitivity.LRDFN
-Micro.AntibioticSensitivityComment.LRDFN
-Pathology.Autopsy.LRDFN
-Micro.BacteriologyReports.LRDFN
-Pathology.CytoOrganTissueFunction.StaffIEN
-Micro.MicroAntibioticLevel.LRDFN
-Micro.MicroAudit.LRDFN
-Micro.Microbiology.LRDFN
-Micro.MicroOrderedTest.LRDFN
-Micro.MicroSterilityResults.LRDFN
-Micro.MycobacteriologyReports.LRDFN
-Micro.Mycology.LRDFN
-Micro.MycologyReports.LRDFN
-Micro.Parasitology.LRDFN
-Micro.ParasitologyReports.LRDFN
-Micro.ParasitologyStage.LRDFN
-SStaff.SMicroOrderedTest.LRDFN
-Micro.Virology.LRDFN
-Micro.VirologyReports.LRDFN</t>
   </si>
   <si>
     <t>Observation.focus</t>
@@ -2378,7 +2168,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AT80"/>
+  <dimension ref="A1:AR69"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.1171875" customWidth="true" bestFit="true"/>
@@ -2424,8 +2214,6 @@
     <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
     <col min="43" max="43" width="218.56640625" customWidth="true" bestFit="true"/>
     <col min="44" max="44" width="50.07421875" customWidth="true" bestFit="true"/>
-    <col min="45" max="45" width="218.56640625" customWidth="true" bestFit="true"/>
-    <col min="46" max="46" width="50.07421875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2561,12 +2349,6 @@
       <c r="AR1" t="s" s="1">
         <v>80</v>
       </c>
-      <c r="AS1" t="s" s="1">
-        <v>79</v>
-      </c>
-      <c r="AT1" t="s" s="1">
-        <v>80</v>
-      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -2693,12 +2475,6 @@
       <c r="AR2" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS2" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT2" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
@@ -2825,12 +2601,6 @@
       <c r="AR3" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS3" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT3" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
@@ -2955,12 +2725,6 @@
       <c r="AR4" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS4" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT4" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
@@ -3087,12 +2851,6 @@
       <c r="AR5" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS5" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT5" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
@@ -3219,12 +2977,6 @@
       <c r="AR6" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS6" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT6" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
@@ -3351,12 +3103,6 @@
       <c r="AR7" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS7" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT7" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
@@ -3483,12 +3229,6 @@
       <c r="AR8" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT8" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
@@ -3615,12 +3355,6 @@
       <c r="AR9" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS9" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT9" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
@@ -3749,12 +3483,6 @@
       <c r="AR10" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS10" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT10" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
@@ -3881,12 +3609,6 @@
       <c r="AR11" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT11" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
@@ -4011,12 +3733,6 @@
       <c r="AR12" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS12" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT12" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
@@ -4143,12 +3859,6 @@
       <c r="AR13" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT13" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
@@ -4277,12 +3987,6 @@
       <c r="AR14" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS14" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT14" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
@@ -4411,12 +4115,6 @@
       <c r="AR15" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT15" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
@@ -4545,12 +4243,6 @@
       <c r="AR16" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT16" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
@@ -4571,7 +4263,7 @@
         <v>94</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>84</v>
@@ -4675,12 +4367,6 @@
         <v>210</v>
       </c>
       <c r="AR17" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS17" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="AT17" t="s" s="2">
         <v>84</v>
       </c>
     </row>
@@ -4807,12 +4493,6 @@
       <c r="AR18" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS18" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT18" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
@@ -4939,12 +4619,6 @@
       <c r="AR19" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT19" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
@@ -5071,12 +4745,6 @@
       <c r="AR20" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS20" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT20" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
@@ -5203,12 +4871,6 @@
       <c r="AR21" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT21" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
@@ -5335,12 +4997,6 @@
       <c r="AR22" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS22" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="AT22" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
@@ -5467,33 +5123,29 @@
       <c r="AR23" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AS23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT23" t="s" s="2">
-        <v>84</v>
-      </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>266</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>256</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="D24" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>84</v>
@@ -5502,16 +5154,20 @@
         <v>84</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>162</v>
+        <v>257</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>84</v>
       </c>
@@ -5520,7 +5176,7 @@
         <v>84</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>84</v>
+        <v>268</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>84</v>
@@ -5535,13 +5191,13 @@
         <v>84</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>84</v>
+        <v>261</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>84</v>
+        <v>262</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>84</v>
@@ -5559,19 +5215,19 @@
         <v>84</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>164</v>
+        <v>256</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>84</v>
@@ -5583,10 +5239,10 @@
         <v>84</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>165</v>
+        <v>264</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>84</v>
+        <v>265</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>84</v>
@@ -5595,55 +5251,51 @@
         <v>84</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT24" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>139</v>
+        <v>270</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>140</v>
+        <v>183</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>141</v>
+        <v>271</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>167</v>
+        <v>272</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>84</v>
       </c>
@@ -5667,81 +5319,75 @@
         <v>84</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>84</v>
+        <v>275</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>84</v>
+        <v>276</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>169</v>
+        <v>84</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>171</v>
+        <v>269</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>84</v>
+        <v>277</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>84</v>
+        <v>278</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>84</v>
+        <v>279</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>165</v>
+        <v>280</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>84</v>
+        <v>281</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>84</v>
+        <v>282</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>84</v>
+        <v>283</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT25" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5749,13 +5395,13 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>84</v>
@@ -5764,19 +5410,19 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>84</v>
@@ -5825,13 +5471,13 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>84</v>
@@ -5840,19 +5486,19 @@
         <v>106</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>84</v>
+        <v>290</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>84</v>
+        <v>293</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>84</v>
@@ -5861,21 +5507,15 @@
         <v>84</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT26" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5886,7 +5526,7 @@
         <v>82</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>84</v>
@@ -5895,18 +5535,20 @@
         <v>84</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>161</v>
+        <v>295</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>162</v>
+        <v>296</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>84</v>
@@ -5955,19 +5597,19 @@
         <v>84</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>164</v>
+        <v>294</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>84</v>
@@ -5976,13 +5618,13 @@
         <v>84</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>84</v>
+        <v>279</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>165</v>
+        <v>299</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>84</v>
+        <v>293</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>84</v>
@@ -5991,32 +5633,26 @@
         <v>84</v>
       </c>
       <c r="AR27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT27" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>139</v>
+        <v>301</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>84</v>
@@ -6025,21 +5661,23 @@
         <v>84</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>140</v>
+        <v>302</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>141</v>
+        <v>303</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>167</v>
+        <v>304</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>305</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
       </c>
@@ -6075,46 +5713,46 @@
         <v>84</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>169</v>
+        <v>84</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>171</v>
+        <v>300</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>84</v>
+        <v>307</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>84</v>
+        <v>308</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>165</v>
+        <v>309</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>84</v>
+        <v>310</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>84</v>
@@ -6123,25 +5761,19 @@
         <v>84</v>
       </c>
       <c r="AR28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT28" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>279</v>
+        <v>311</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>84</v>
+        <v>312</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -6151,7 +5783,7 @@
         <v>94</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>84</v>
@@ -6160,19 +5792,19 @@
         <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>108</v>
+        <v>313</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>280</v>
+        <v>314</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>281</v>
+        <v>315</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>282</v>
+        <v>316</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>283</v>
+        <v>317</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>84</v>
@@ -6209,19 +5841,17 @@
         <v>84</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="AC29" s="2"/>
       <c r="AD29" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>284</v>
+        <v>311</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -6230,25 +5860,25 @@
         <v>94</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>84</v>
+        <v>319</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>106</v>
+        <v>320</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>84</v>
+        <v>321</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>285</v>
+        <v>322</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>286</v>
+        <v>323</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>84</v>
+        <v>324</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>84</v>
@@ -6257,25 +5887,21 @@
         <v>84</v>
       </c>
       <c r="AR29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT29" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>287</v>
+        <v>325</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="C30" s="2"/>
+        <v>311</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>326</v>
+      </c>
       <c r="D30" t="s" s="2">
-        <v>84</v>
+        <v>312</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -6285,7 +5911,7 @@
         <v>94</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>84</v>
@@ -6294,18 +5920,20 @@
         <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>161</v>
+        <v>327</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>288</v>
+        <v>314</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>289</v>
+        <v>315</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>316</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>84</v>
       </c>
@@ -6353,7 +5981,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -6362,48 +5990,42 @@
         <v>94</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>84</v>
+        <v>319</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>106</v>
+        <v>320</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>84</v>
+        <v>321</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>293</v>
+        <v>323</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>84</v>
+        <v>324</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>84</v>
+        <v>328</v>
       </c>
       <c r="AR30" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS30" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT30" t="s" s="2">
-        <v>84</v>
+        <v>329</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>294</v>
+        <v>330</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>294</v>
+        <v>330</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6417,7 +6039,7 @@
         <v>94</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>84</v>
@@ -6426,18 +6048,18 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>114</v>
+        <v>331</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>295</v>
+        <v>332</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>84</v>
       </c>
@@ -6485,7 +6107,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>298</v>
+        <v>330</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6497,7 +6119,7 @@
         <v>84</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>299</v>
+        <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>84</v>
@@ -6506,36 +6128,30 @@
         <v>84</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>300</v>
+        <v>335</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>301</v>
+        <v>336</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>84</v>
+        <v>337</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>302</v>
+        <v>338</v>
       </c>
       <c r="AR31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS31" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="AT31" t="s" s="2">
-        <v>84</v>
+        <v>339</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>303</v>
+        <v>340</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>303</v>
+        <v>340</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6546,10 +6162,10 @@
         <v>82</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>84</v>
@@ -6558,17 +6174,17 @@
         <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>161</v>
+        <v>219</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>304</v>
+        <v>341</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>305</v>
+        <v>342</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>306</v>
+        <v>343</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -6617,13 +6233,13 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>307</v>
+        <v>340</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>84</v>
@@ -6632,42 +6248,36 @@
         <v>106</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>84</v>
+        <v>344</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>308</v>
+        <v>345</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>309</v>
+        <v>346</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>84</v>
+        <v>347</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>84</v>
+        <v>348</v>
       </c>
       <c r="AR32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT32" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>310</v>
+        <v>349</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>310</v>
+        <v>349</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6681,7 +6291,7 @@
         <v>94</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>84</v>
@@ -6690,19 +6300,19 @@
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>311</v>
+        <v>350</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>312</v>
+        <v>351</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>313</v>
+        <v>352</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>314</v>
+        <v>353</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>315</v>
+        <v>354</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6739,19 +6349,17 @@
         <v>84</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>316</v>
+        <v>349</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6760,50 +6368,46 @@
         <v>94</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>84</v>
+        <v>355</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>106</v>
+        <v>356</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>84</v>
+        <v>357</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>317</v>
+        <v>358</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>318</v>
+        <v>359</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>84</v>
+        <v>360</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT33" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>319</v>
+        <v>361</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="C34" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="D34" t="s" s="2">
         <v>84</v>
       </c>
@@ -6815,7 +6419,7 @@
         <v>94</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>84</v>
@@ -6824,19 +6428,19 @@
         <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>161</v>
+        <v>363</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>320</v>
+        <v>351</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>321</v>
+        <v>352</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>322</v>
+        <v>353</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>323</v>
+        <v>354</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6885,7 +6489,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6894,64 +6498,56 @@
         <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>84</v>
+        <v>355</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>106</v>
+        <v>356</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>84</v>
+        <v>357</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>325</v>
+        <v>358</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>326</v>
+        <v>359</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>84</v>
+        <v>360</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT34" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>327</v>
+        <v>364</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="C35" t="s" s="2">
-        <v>328</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>84</v>
@@ -6960,20 +6556,16 @@
         <v>84</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>257</v>
+        <v>162</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>260</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>84</v>
       </c>
@@ -6982,7 +6574,7 @@
         <v>84</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>329</v>
+        <v>84</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>84</v>
@@ -6997,13 +6589,13 @@
         <v>84</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>261</v>
+        <v>84</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>262</v>
+        <v>84</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>84</v>
@@ -7021,19 +6613,19 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>256</v>
+        <v>164</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>84</v>
@@ -7045,10 +6637,10 @@
         <v>84</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>264</v>
+        <v>165</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>265</v>
+        <v>84</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>84</v>
@@ -7057,57 +6649,49 @@
         <v>84</v>
       </c>
       <c r="AR35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT35" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>330</v>
+        <v>366</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>330</v>
+        <v>367</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>331</v>
+        <v>139</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>332</v>
+        <v>141</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>333</v>
+        <v>167</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>335</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>84</v>
       </c>
@@ -7131,81 +6715,75 @@
         <v>84</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>336</v>
+        <v>84</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>337</v>
+        <v>84</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>330</v>
+        <v>171</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>338</v>
+        <v>84</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>339</v>
+        <v>84</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>340</v>
+        <v>84</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>341</v>
+        <v>165</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>342</v>
+        <v>84</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>343</v>
+        <v>84</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>344</v>
+        <v>84</v>
       </c>
       <c r="AR36" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS36" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="AT36" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>345</v>
+        <v>369</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7213,7 +6791,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>94</v>
@@ -7228,19 +6806,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>346</v>
+        <v>370</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>347</v>
+        <v>371</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>348</v>
+        <v>372</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>349</v>
+        <v>373</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>350</v>
+        <v>374</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -7289,7 +6867,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>345</v>
+        <v>375</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -7304,42 +6882,36 @@
         <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>351</v>
+        <v>84</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>352</v>
+        <v>376</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>353</v>
+        <v>377</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>354</v>
+        <v>84</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="AS37" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="AT37" t="s" s="2">
-        <v>356</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>357</v>
+        <v>380</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7350,34 +6922,36 @@
         <v>82</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J38" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>358</v>
+        <v>114</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>359</v>
+        <v>381</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>382</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" t="s" s="2">
+        <v>383</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q38" s="2"/>
+      <c r="Q38" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="R38" t="s" s="2">
         <v>84</v>
       </c>
@@ -7397,13 +6971,13 @@
         <v>84</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>84</v>
+        <v>177</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>84</v>
+        <v>385</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>84</v>
+        <v>386</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>84</v>
@@ -7421,13 +6995,13 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>357</v>
+        <v>387</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>84</v>
@@ -7442,13 +7016,13 @@
         <v>84</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>340</v>
+        <v>388</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>362</v>
+        <v>389</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>354</v>
+        <v>84</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>84</v>
@@ -7457,25 +7031,19 @@
         <v>84</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT38" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>363</v>
+        <v>390</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>363</v>
+        <v>391</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>364</v>
+        <v>84</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7485,7 +7053,7 @@
         <v>94</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>84</v>
@@ -7494,19 +7062,17 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>365</v>
+        <v>161</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>366</v>
+        <v>392</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>368</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>369</v>
+        <v>394</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -7555,7 +7121,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>363</v>
+        <v>395</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7570,46 +7136,40 @@
         <v>106</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>370</v>
+        <v>84</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>371</v>
+        <v>396</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>372</v>
+        <v>397</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>373</v>
+        <v>84</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>84</v>
+        <v>398</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS39" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT39" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>374</v>
+        <v>399</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>374</v>
+        <v>400</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>375</v>
+        <v>84</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7619,7 +7179,7 @@
         <v>94</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>84</v>
@@ -7628,19 +7188,17 @@
         <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>376</v>
+        <v>108</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>377</v>
+        <v>401</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>379</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>380</v>
+        <v>403</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7677,17 +7235,19 @@
         <v>84</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AC40" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>374</v>
+        <v>404</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7696,25 +7256,25 @@
         <v>94</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>382</v>
+        <v>405</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>383</v>
+        <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>384</v>
+        <v>84</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>386</v>
+        <v>406</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>387</v>
+        <v>84</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>84</v>
@@ -7723,27 +7283,19 @@
         <v>84</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT40" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>388</v>
+        <v>407</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="C41" t="s" s="2">
-        <v>389</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>375</v>
+        <v>84</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7753,7 +7305,7 @@
         <v>94</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>84</v>
@@ -7762,19 +7314,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>390</v>
+        <v>114</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>377</v>
+        <v>409</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>378</v>
+        <v>410</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>379</v>
+        <v>411</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>380</v>
+        <v>412</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7823,7 +7375,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>374</v>
+        <v>413</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7832,48 +7384,42 @@
         <v>94</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>382</v>
+        <v>84</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>383</v>
+        <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>384</v>
+        <v>84</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>386</v>
+        <v>414</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>387</v>
+        <v>84</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>391</v>
+        <v>84</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="AS41" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="AT41" t="s" s="2">
-        <v>392</v>
+        <v>84</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>393</v>
+        <v>415</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>393</v>
+        <v>415</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7887,27 +7433,29 @@
         <v>94</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>394</v>
+        <v>183</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>395</v>
+        <v>416</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>396</v>
+        <v>417</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>418</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>419</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>84</v>
       </c>
@@ -7931,13 +7479,11 @@
         <v>84</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>84</v>
+        <v>420</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>84</v>
@@ -7955,7 +7501,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>393</v>
+        <v>415</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7964,7 +7510,7 @@
         <v>94</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>84</v>
+        <v>421</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>106</v>
@@ -7976,40 +7522,34 @@
         <v>84</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>398</v>
+        <v>137</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>399</v>
+        <v>422</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>400</v>
+        <v>84</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>401</v>
+        <v>84</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="AS42" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="AT42" t="s" s="2">
-        <v>402</v>
+        <v>84</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>84</v>
+        <v>424</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -8019,26 +7559,28 @@
         <v>83</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>219</v>
+        <v>183</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>404</v>
+        <v>425</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>426</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>427</v>
+      </c>
       <c r="O43" t="s" s="2">
-        <v>406</v>
+        <v>428</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
@@ -8063,13 +7605,11 @@
         <v>84</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
-        <v>84</v>
+        <v>429</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>84</v>
@@ -8087,7 +7627,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -8102,42 +7642,36 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>407</v>
+        <v>84</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>84</v>
+        <v>430</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>408</v>
+        <v>431</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>409</v>
+        <v>432</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>410</v>
+        <v>84</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>84</v>
+        <v>433</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>411</v>
+        <v>434</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS43" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="AT43" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>412</v>
+        <v>435</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>412</v>
+        <v>435</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8148,7 +7682,7 @@
         <v>82</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>95</v>
@@ -8157,22 +7691,22 @@
         <v>84</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>413</v>
+        <v>436</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>414</v>
+        <v>437</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>415</v>
+        <v>438</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>416</v>
+        <v>439</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>417</v>
+        <v>440</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -8209,71 +7743,65 @@
         <v>84</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AC44" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>412</v>
+        <v>435</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>418</v>
+        <v>84</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>419</v>
+        <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>420</v>
+        <v>84</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>421</v>
+        <v>441</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>422</v>
+        <v>442</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>423</v>
+        <v>84</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>84</v>
+        <v>443</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT44" t="s" s="2">
-        <v>84</v>
+        <v>444</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>424</v>
+        <v>445</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="C45" t="s" s="2">
-        <v>425</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>84</v>
       </c>
@@ -8285,29 +7813,27 @@
         <v>94</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>426</v>
+        <v>183</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>414</v>
+        <v>446</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>415</v>
+        <v>447</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>84</v>
       </c>
@@ -8331,13 +7857,13 @@
         <v>84</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>84</v>
+        <v>449</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>84</v>
+        <v>450</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>84</v>
+        <v>451</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>84</v>
@@ -8355,7 +7881,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>412</v>
+        <v>445</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8364,48 +7890,42 @@
         <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>418</v>
+        <v>84</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>419</v>
+        <v>106</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>420</v>
+        <v>452</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>421</v>
+        <v>453</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>422</v>
+        <v>454</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>423</v>
+        <v>455</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS45" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT45" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>427</v>
+        <v>456</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>428</v>
+        <v>456</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8428,16 +7948,20 @@
         <v>84</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>162</v>
+        <v>457</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>458</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>460</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
       </c>
@@ -8461,13 +7985,13 @@
         <v>84</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>84</v>
+        <v>449</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>84</v>
+        <v>461</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>84</v>
+        <v>462</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>84</v>
@@ -8485,7 +8009,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>164</v>
+        <v>456</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8497,7 +8021,7 @@
         <v>84</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>84</v>
@@ -8506,10 +8030,10 @@
         <v>84</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>84</v>
+        <v>463</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>165</v>
+        <v>464</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>84</v>
@@ -8521,35 +8045,29 @@
         <v>84</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT46" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>429</v>
+        <v>465</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>430</v>
+        <v>465</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>84</v>
@@ -8558,16 +8076,16 @@
         <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>140</v>
+        <v>466</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>141</v>
+        <v>467</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>167</v>
+        <v>468</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>143</v>
+        <v>469</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8605,69 +8123,63 @@
         <v>84</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>169</v>
+        <v>84</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>171</v>
+        <v>465</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>84</v>
+        <v>470</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>84</v>
+        <v>471</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>165</v>
+        <v>472</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>84</v>
+        <v>473</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>84</v>
+        <v>474</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT47" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>431</v>
+        <v>475</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>432</v>
+        <v>475</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8687,23 +8199,21 @@
         <v>84</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>433</v>
+        <v>476</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>434</v>
+        <v>477</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>435</v>
+        <v>478</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>437</v>
-      </c>
+        <v>479</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>84</v>
       </c>
@@ -8751,7 +8261,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>438</v>
+        <v>475</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8769,39 +8279,33 @@
         <v>84</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>84</v>
+        <v>480</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>439</v>
+        <v>481</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>440</v>
+        <v>482</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>84</v>
+        <v>483</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>441</v>
+        <v>84</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS48" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="AT48" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>442</v>
+        <v>484</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>443</v>
+        <v>484</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8812,36 +8316,36 @@
         <v>82</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>114</v>
+        <v>485</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>444</v>
+        <v>486</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>487</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>488</v>
+      </c>
       <c r="O49" t="s" s="2">
-        <v>446</v>
+        <v>489</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q49" t="s" s="2">
-        <v>447</v>
-      </c>
+      <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
         <v>84</v>
       </c>
@@ -8861,13 +8365,13 @@
         <v>84</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>177</v>
+        <v>84</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>448</v>
+        <v>84</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>449</v>
+        <v>84</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
@@ -8885,19 +8389,19 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>450</v>
+        <v>484</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>106</v>
+        <v>490</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>84</v>
@@ -8906,10 +8410,10 @@
         <v>84</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>451</v>
+        <v>491</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>452</v>
+        <v>492</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>84</v>
@@ -8921,21 +8425,15 @@
         <v>84</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT49" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>453</v>
+        <v>493</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>454</v>
+        <v>493</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8955,21 +8453,19 @@
         <v>84</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
         <v>161</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>455</v>
+        <v>162</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>456</v>
+        <v>163</v>
       </c>
       <c r="N50" s="2"/>
-      <c r="O50" t="s" s="2">
-        <v>457</v>
-      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>84</v>
       </c>
@@ -9017,7 +8513,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>458</v>
+        <v>164</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -9029,7 +8525,7 @@
         <v>84</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>84</v>
@@ -9038,10 +8534,10 @@
         <v>84</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>459</v>
+        <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>460</v>
+        <v>165</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>84</v>
@@ -9050,35 +8546,29 @@
         <v>84</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>461</v>
+        <v>84</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS50" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="AT50" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>462</v>
+        <v>494</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>463</v>
+        <v>494</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>84</v>
@@ -9087,21 +8577,21 @@
         <v>84</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>464</v>
+        <v>141</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" t="s" s="2">
-        <v>466</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>84</v>
       </c>
@@ -9149,19 +8639,19 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>467</v>
+        <v>171</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>468</v>
+        <v>84</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>84</v>
@@ -9170,10 +8660,10 @@
         <v>84</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>459</v>
+        <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>469</v>
+        <v>165</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>84</v>
@@ -9185,56 +8675,50 @@
         <v>84</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT51" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>470</v>
+        <v>495</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>471</v>
+        <v>495</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>84</v>
+        <v>496</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J52" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>472</v>
+        <v>497</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>473</v>
+        <v>498</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>474</v>
+        <v>143</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>475</v>
+        <v>149</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -9283,19 +8767,19 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>476</v>
+        <v>499</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>84</v>
@@ -9304,10 +8788,10 @@
         <v>84</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>459</v>
+        <v>84</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>477</v>
+        <v>137</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>84</v>
@@ -9319,21 +8803,15 @@
         <v>84</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT52" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>478</v>
+        <v>500</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>478</v>
+        <v>500</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9356,20 +8834,16 @@
         <v>84</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>183</v>
+        <v>501</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>479</v>
+        <v>502</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>482</v>
-      </c>
+        <v>503</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>84</v>
       </c>
@@ -9393,11 +8867,13 @@
         <v>84</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Y53" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z53" t="s" s="2">
-        <v>483</v>
+        <v>84</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>84</v>
@@ -9415,7 +8891,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>478</v>
+        <v>500</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -9424,7 +8900,7 @@
         <v>94</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>484</v>
+        <v>504</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>106</v>
@@ -9436,10 +8912,10 @@
         <v>84</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>137</v>
+        <v>505</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>485</v>
+        <v>506</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>84</v>
@@ -9448,38 +8924,32 @@
         <v>84</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>84</v>
+        <v>507</v>
       </c>
       <c r="AR53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT53" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>486</v>
+        <v>508</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>486</v>
+        <v>508</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>487</v>
+        <v>84</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>84</v>
@@ -9488,20 +8958,16 @@
         <v>84</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>183</v>
+        <v>501</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>488</v>
+        <v>509</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>491</v>
-      </c>
+        <v>510</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>84</v>
       </c>
@@ -9525,11 +8991,13 @@
         <v>84</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y54" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z54" t="s" s="2">
-        <v>492</v>
+        <v>84</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>84</v>
@@ -9547,16 +9015,16 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>486</v>
+        <v>508</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>84</v>
+        <v>504</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>106</v>
@@ -9565,39 +9033,33 @@
         <v>84</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>493</v>
+        <v>84</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>494</v>
+        <v>505</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>495</v>
+        <v>511</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>496</v>
+        <v>84</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>497</v>
+        <v>512</v>
       </c>
       <c r="AR54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS54" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="AT54" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>498</v>
+        <v>513</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>498</v>
+        <v>513</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9608,7 +9070,7 @@
         <v>82</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>84</v>
@@ -9620,19 +9082,19 @@
         <v>84</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>499</v>
+        <v>183</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>501</v>
+        <v>515</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>502</v>
+        <v>516</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>503</v>
+        <v>517</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>84</v>
@@ -9657,13 +9119,13 @@
         <v>84</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>84</v>
+        <v>518</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>84</v>
+        <v>519</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>84</v>
@@ -9681,13 +9143,13 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>498</v>
+        <v>513</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>84</v>
@@ -9699,13 +9161,13 @@
         <v>84</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>84</v>
+        <v>520</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>504</v>
+        <v>521</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>505</v>
+        <v>432</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>84</v>
@@ -9714,24 +9176,18 @@
         <v>84</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>506</v>
+        <v>84</v>
       </c>
       <c r="AR55" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="AS55" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="AT55" t="s" s="2">
-        <v>507</v>
+        <v>84</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9742,7 +9198,7 @@
         <v>82</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>84</v>
@@ -9757,15 +9213,17 @@
         <v>183</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>510</v>
+        <v>524</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>525</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>526</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>84</v>
       </c>
@@ -9789,13 +9247,13 @@
         <v>84</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>512</v>
+        <v>449</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>513</v>
+        <v>527</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>514</v>
+        <v>528</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>84</v>
@@ -9813,13 +9271,13 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>84</v>
@@ -9831,39 +9289,33 @@
         <v>84</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>517</v>
+        <v>432</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>518</v>
+        <v>84</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT56" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9886,19 +9338,17 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>183</v>
+        <v>530</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>520</v>
+        <v>531</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>522</v>
-      </c>
+        <v>532</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>523</v>
+        <v>533</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>84</v>
@@ -9923,13 +9373,13 @@
         <v>84</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>512</v>
+        <v>84</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>524</v>
+        <v>84</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>525</v>
+        <v>84</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>84</v>
@@ -9947,7 +9397,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9968,10 +9418,10 @@
         <v>84</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>526</v>
+        <v>84</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>84</v>
@@ -9983,21 +9433,15 @@
         <v>84</v>
       </c>
       <c r="AR57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT57" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10020,17 +9464,15 @@
         <v>84</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>529</v>
+        <v>161</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>532</v>
-      </c>
+        <v>537</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -10079,7 +9521,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -10097,39 +9539,33 @@
         <v>84</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>533</v>
+        <v>84</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>534</v>
+        <v>505</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>536</v>
+        <v>84</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>537</v>
+        <v>84</v>
       </c>
       <c r="AR58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS58" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="AT58" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10140,7 +9576,7 @@
         <v>82</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>84</v>
@@ -10149,19 +9585,19 @@
         <v>84</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -10211,13 +9647,13 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>84</v>
@@ -10229,7 +9665,7 @@
         <v>84</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>543</v>
+        <v>84</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>544</v>
@@ -10241,27 +9677,21 @@
         <v>84</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>546</v>
+        <v>84</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT59" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10281,23 +9711,21 @@
         <v>84</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="N60" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>552</v>
-      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>84</v>
       </c>
@@ -10345,7 +9773,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10357,7 +9785,7 @@
         <v>84</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>553</v>
+        <v>106</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>84</v>
@@ -10366,10 +9794,10 @@
         <v>84</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>554</v>
+        <v>544</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>84</v>
@@ -10381,21 +9809,15 @@
         <v>84</v>
       </c>
       <c r="AR60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT60" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10406,7 +9828,7 @@
         <v>82</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>84</v>
@@ -10415,19 +9837,23 @@
         <v>84</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>161</v>
+        <v>485</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>162</v>
+        <v>553</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+        <v>554</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>556</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>84</v>
       </c>
@@ -10475,19 +9901,19 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>164</v>
+        <v>552</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>84</v>
@@ -10496,10 +9922,10 @@
         <v>84</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>84</v>
+        <v>557</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>165</v>
+        <v>558</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>84</v>
@@ -10511,32 +9937,26 @@
         <v>84</v>
       </c>
       <c r="AR61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT61" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>84</v>
@@ -10548,17 +9968,15 @@
         <v>84</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>84</v>
@@ -10607,19 +10025,19 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>84</v>
@@ -10643,25 +10061,19 @@
         <v>84</v>
       </c>
       <c r="AR62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT62" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>559</v>
+        <v>139</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -10674,26 +10086,24 @@
         <v>84</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K63" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>560</v>
+        <v>141</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>561</v>
+        <v>167</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O63" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>84</v>
       </c>
@@ -10741,7 +10151,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>562</v>
+        <v>171</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10765,7 +10175,7 @@
         <v>84</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>84</v>
@@ -10777,53 +10187,51 @@
         <v>84</v>
       </c>
       <c r="AR63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT63" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>84</v>
+        <v>496</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>564</v>
+        <v>140</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>565</v>
+        <v>497</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
+        <v>498</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
       </c>
@@ -10871,19 +10279,19 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>563</v>
+        <v>499</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>567</v>
+        <v>84</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>84</v>
@@ -10892,10 +10300,10 @@
         <v>84</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>568</v>
+        <v>84</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>569</v>
+        <v>137</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>84</v>
@@ -10904,24 +10312,18 @@
         <v>84</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>570</v>
+        <v>84</v>
       </c>
       <c r="AR64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS64" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="AT64" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10929,7 +10331,7 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>94</v>
@@ -10941,19 +10343,23 @@
         <v>84</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="L65" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
+      <c r="N65" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>84</v>
       </c>
@@ -10977,13 +10383,13 @@
         <v>84</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>84</v>
+        <v>449</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>84</v>
+        <v>566</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>84</v>
+        <v>276</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>84</v>
@@ -11001,16 +10407,16 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH65" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>567</v>
+        <v>84</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>106</v>
@@ -11019,39 +10425,33 @@
         <v>84</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>84</v>
+        <v>567</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>568</v>
+        <v>279</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>574</v>
+        <v>280</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>84</v>
+        <v>281</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>575</v>
+        <v>84</v>
       </c>
       <c r="AR65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS65" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="AT65" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11071,22 +10471,22 @@
         <v>84</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>183</v>
+        <v>350</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>580</v>
+        <v>354</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>84</v>
@@ -11111,13 +10511,13 @@
         <v>84</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>581</v>
+        <v>84</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>582</v>
+        <v>84</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>84</v>
@@ -11135,7 +10535,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -11153,39 +10553,33 @@
         <v>84</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>583</v>
+        <v>572</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>584</v>
+        <v>358</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>495</v>
+        <v>359</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>84</v>
+        <v>360</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT66" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>585</v>
+        <v>573</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>585</v>
+        <v>573</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11196,7 +10590,7 @@
         <v>82</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>84</v>
@@ -11211,16 +10605,16 @@
         <v>183</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>586</v>
+        <v>574</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>587</v>
+        <v>575</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>588</v>
+        <v>576</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>589</v>
+        <v>419</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>84</v>
@@ -11245,13 +10639,13 @@
         <v>84</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>512</v>
+        <v>188</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>590</v>
+        <v>577</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>591</v>
+        <v>420</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>84</v>
@@ -11269,16 +10663,16 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>585</v>
+        <v>573</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>84</v>
+        <v>578</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>106</v>
@@ -11287,13 +10681,13 @@
         <v>84</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>583</v>
+        <v>84</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>584</v>
+        <v>137</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>495</v>
+        <v>422</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>84</v>
@@ -11305,32 +10699,26 @@
         <v>84</v>
       </c>
       <c r="AR67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT67" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>592</v>
+        <v>579</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>592</v>
+        <v>579</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>84</v>
+        <v>424</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>84</v>
@@ -11342,17 +10730,19 @@
         <v>84</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>593</v>
+        <v>183</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>594</v>
+        <v>425</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>426</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>427</v>
+      </c>
       <c r="O68" t="s" s="2">
-        <v>596</v>
+        <v>428</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>84</v>
@@ -11377,13 +10767,13 @@
         <v>84</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>84</v>
+        <v>580</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>84</v>
+        <v>581</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>84</v>
@@ -11401,13 +10791,13 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>592</v>
+        <v>579</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>84</v>
@@ -11419,39 +10809,33 @@
         <v>84</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>84</v>
+        <v>430</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>84</v>
+        <v>431</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>597</v>
+        <v>432</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>84</v>
+        <v>433</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT68" t="s" s="2">
         <v>84</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>598</v>
+        <v>582</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>598</v>
+        <v>582</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11462,7 +10846,7 @@
         <v>82</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>84</v>
@@ -11474,16 +10858,20 @@
         <v>84</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>599</v>
+        <v>583</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
+        <v>584</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>489</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>84</v>
       </c>
@@ -11531,13 +10919,13 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>598</v>
+        <v>582</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>84</v>
@@ -11552,10 +10940,10 @@
         <v>84</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>568</v>
+        <v>491</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>601</v>
+        <v>492</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>84</v>
@@ -11567,1481 +10955,11 @@
         <v>84</v>
       </c>
       <c r="AR69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT69" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="70" hidden="true">
-      <c r="A70" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="B70" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="C70" s="2"/>
-      <c r="D70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E70" s="2"/>
-      <c r="F70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J70" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K70" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="L70" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="O70" s="2"/>
-      <c r="P70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q70" s="2"/>
-      <c r="R70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="AG70" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ70" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT70" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="71" hidden="true">
-      <c r="A71" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="C71" s="2"/>
-      <c r="D71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E71" s="2"/>
-      <c r="F71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K71" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="O71" s="2"/>
-      <c r="P71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q71" s="2"/>
-      <c r="R71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ71" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT71" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="72" hidden="true">
-      <c r="A72" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="P72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q72" s="2"/>
-      <c r="R72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT72" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="73" hidden="true">
-      <c r="A73" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E73" s="2"/>
-      <c r="F73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
-      <c r="P73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q73" s="2"/>
-      <c r="R73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT73" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="74" hidden="true">
-      <c r="A74" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="E74" s="2"/>
-      <c r="F74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K74" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O74" s="2"/>
-      <c r="P74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q74" s="2"/>
-      <c r="R74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT74" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="75" hidden="true">
-      <c r="A75" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="E75" s="2"/>
-      <c r="F75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="P75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q75" s="2"/>
-      <c r="R75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT75" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="76" hidden="true">
-      <c r="A76" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E76" s="2"/>
-      <c r="F76" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="G76" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K76" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="P76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q76" s="2"/>
-      <c r="R76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT76" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="77" hidden="true">
-      <c r="A77" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E77" s="2"/>
-      <c r="F77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K77" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="P77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q77" s="2"/>
-      <c r="R77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="AG77" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH77" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ77" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP77" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AQ77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT77" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="78" hidden="true">
-      <c r="A78" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="C78" s="2"/>
-      <c r="D78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E78" s="2"/>
-      <c r="F78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G78" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K78" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="P78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q78" s="2"/>
-      <c r="R78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X78" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="AG78" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH78" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI78" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="AJ78" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="AO78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT78" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="79" hidden="true">
-      <c r="A79" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="C79" s="2"/>
-      <c r="D79" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="E79" s="2"/>
-      <c r="F79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G79" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H79" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I79" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J79" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K79" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="L79" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="P79" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q79" s="2"/>
-      <c r="R79" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S79" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T79" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U79" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V79" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W79" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X79" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="AG79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH79" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI79" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK79" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="AO79" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP79" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="AQ79" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR79" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS79" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT79" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="80" hidden="true">
-      <c r="A80" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="C80" s="2"/>
-      <c r="D80" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E80" s="2"/>
-      <c r="F80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H80" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I80" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J80" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K80" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L80" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="P80" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q80" s="2"/>
-      <c r="R80" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S80" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T80" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U80" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V80" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W80" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X80" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="AG80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK80" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="AO80" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP80" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ80" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR80" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AS80" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AT80" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AT80">
+  <autoFilter ref="A1:AR69">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -13051,7 +10969,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI79">
+  <conditionalFormatting sqref="A2:AI68">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$73</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2821" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2982" uniqueCount="606">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -900,7 +900,65 @@
     <t>116680003 |Is a|</t>
   </si>
   <si>
-    <t>853: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE (#63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-95.03)</t>
+    <t>Observation.code.id</t>
+  </si>
+  <si>
+    <t>Observation.code.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>853: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (#63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-95.03 &gt; 95.03-)</t>
+  </si>
+  <si>
+    <t>Observation.code.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>Observation.subject</t>
@@ -1091,6 +1149,10 @@
     <t>Observation.performer</t>
   </si>
   <si>
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
+</t>
+  </si>
+  <si>
     <t>Who is responsible for the observation</t>
   </si>
   <si>
@@ -1112,7 +1174,7 @@
     <t>FiveWs.actor</t>
   </si>
   <si>
-    <t>847: reference from CHEM, HEM, TOX, RIA, SER, etc. - ACCESSIONING INSTITUTION (#63.04-.112)</t>
+    <t>1676: reference from CHEM, HEM, TOX, RIA, SER, etc. - VERIFY PERSON (#63.04-.04)</t>
   </si>
   <si>
     <t>Observation.value[x]</t>
@@ -1503,6 +1565,10 @@
   </si>
   <si>
     <t>1656: reference from CHEM, HEM, TOX, RIA, SER, etc. - ACCESSION (#63.04-.06)</t>
+  </si>
+  <si>
+    <t>Chem.LabChem.ShortAccessionNumber
+Chem.PatientLabChem.ShortAccessionNumber</t>
   </si>
   <si>
     <t>Observation.device</t>
@@ -2168,7 +2234,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR69"/>
+  <dimension ref="A1:AR73"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.1171875" customWidth="true" bestFit="true"/>
@@ -2212,7 +2278,7 @@
     <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="218.56640625" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="239.078125" customWidth="true" bestFit="true"/>
     <col min="44" max="44" width="50.07421875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -5376,7 +5442,7 @@
         <v>282</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>283</v>
+        <v>84</v>
       </c>
       <c r="AR25" t="s" s="2">
         <v>84</v>
@@ -5384,10 +5450,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5395,35 +5461,31 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>94</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>285</v>
+        <v>161</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>286</v>
+        <v>162</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>289</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>84</v>
       </c>
@@ -5471,7 +5533,7 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>284</v>
+        <v>164</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -5483,22 +5545,22 @@
         <v>84</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>290</v>
+        <v>84</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>291</v>
+        <v>84</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>292</v>
+        <v>165</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>293</v>
+        <v>84</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>84</v>
@@ -5512,14 +5574,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5535,19 +5597,19 @@
         <v>84</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>295</v>
+        <v>140</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>296</v>
+        <v>141</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>297</v>
+        <v>167</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>298</v>
+        <v>143</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5585,19 +5647,19 @@
         <v>84</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>294</v>
+        <v>171</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>82</v>
@@ -5609,7 +5671,7 @@
         <v>84</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>84</v>
@@ -5618,13 +5680,13 @@
         <v>84</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>279</v>
+        <v>84</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>299</v>
+        <v>165</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>293</v>
+        <v>84</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>84</v>
@@ -5638,24 +5700,24 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>301</v>
+        <v>84</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>84</v>
@@ -5664,19 +5726,19 @@
         <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>306</v>
+        <v>290</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -5725,13 +5787,13 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>84</v>
@@ -5740,25 +5802,25 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>307</v>
+        <v>84</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>309</v>
+        <v>293</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>310</v>
+        <v>84</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>84</v>
+        <v>294</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>84</v>
@@ -5766,14 +5828,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>312</v>
+        <v>84</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5783,7 +5845,7 @@
         <v>94</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>84</v>
@@ -5792,19 +5854,19 @@
         <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>313</v>
+        <v>161</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>314</v>
+        <v>296</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>315</v>
+        <v>297</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>316</v>
+        <v>298</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>317</v>
+        <v>299</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>84</v>
@@ -5841,17 +5903,19 @@
         <v>84</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="AC29" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD29" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5860,25 +5924,25 @@
         <v>94</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>319</v>
+        <v>84</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>320</v>
+        <v>106</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>321</v>
+        <v>84</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>322</v>
+        <v>301</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>323</v>
+        <v>302</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>324</v>
+        <v>84</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>84</v>
@@ -5892,20 +5956,18 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>325</v>
+        <v>303</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="C30" t="s" s="2">
-        <v>326</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>312</v>
+        <v>84</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>94</v>
@@ -5920,19 +5982,19 @@
         <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>327</v>
+        <v>304</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>84</v>
@@ -5981,7 +6043,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>82</v>
@@ -5990,42 +6052,42 @@
         <v>94</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>319</v>
+        <v>84</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>320</v>
+        <v>106</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ30" t="s" s="2">
-        <v>328</v>
+        <v>84</v>
       </c>
       <c r="AR30" t="s" s="2">
-        <v>329</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6036,10 +6098,10 @@
         <v>82</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>84</v>
@@ -6048,16 +6110,16 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>333</v>
+        <v>316</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6107,13 +6169,13 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>84</v>
@@ -6128,44 +6190,44 @@
         <v>84</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>335</v>
+        <v>279</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>336</v>
+        <v>318</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>337</v>
+        <v>312</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>338</v>
+        <v>84</v>
       </c>
       <c r="AR31" t="s" s="2">
-        <v>339</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>340</v>
+        <v>319</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>340</v>
+        <v>319</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>84</v>
+        <v>320</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>84</v>
@@ -6174,17 +6236,19 @@
         <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>219</v>
+        <v>321</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>341</v>
+        <v>322</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>323</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>324</v>
+      </c>
       <c r="O32" t="s" s="2">
-        <v>343</v>
+        <v>325</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -6233,13 +6297,13 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>340</v>
+        <v>319</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>84</v>
@@ -6248,25 +6312,25 @@
         <v>106</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>344</v>
+        <v>326</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>346</v>
+        <v>328</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>347</v>
+        <v>329</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>348</v>
+        <v>84</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>84</v>
@@ -6274,14 +6338,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>349</v>
+        <v>330</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>349</v>
+        <v>330</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>84</v>
+        <v>331</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -6300,19 +6364,19 @@
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>350</v>
+        <v>332</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>351</v>
+        <v>333</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>352</v>
+        <v>334</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>353</v>
+        <v>335</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>354</v>
+        <v>336</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6349,7 +6413,7 @@
         <v>84</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>318</v>
+        <v>337</v>
       </c>
       <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
@@ -6359,7 +6423,7 @@
         <v>170</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>349</v>
+        <v>330</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6368,28 +6432,28 @@
         <v>94</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>84</v>
+        <v>340</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>357</v>
+        <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>359</v>
+        <v>342</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>84</v>
+        <v>343</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>360</v>
+        <v>84</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
@@ -6400,16 +6464,16 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>349</v>
+        <v>330</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="D34" t="s" s="2">
-        <v>84</v>
+        <v>331</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6428,19 +6492,19 @@
         <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>363</v>
+        <v>346</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>351</v>
+        <v>333</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>352</v>
+        <v>334</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>353</v>
+        <v>335</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>354</v>
+        <v>336</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6489,7 +6553,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>349</v>
+        <v>330</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6498,42 +6562,42 @@
         <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>84</v>
+        <v>340</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>357</v>
+        <v>84</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>359</v>
+        <v>342</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>84</v>
+        <v>343</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>360</v>
+        <v>84</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>84</v>
+        <v>347</v>
       </c>
       <c r="AR34" t="s" s="2">
-        <v>84</v>
+        <v>348</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>365</v>
+        <v>349</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6547,24 +6611,26 @@
         <v>94</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>161</v>
+        <v>350</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>162</v>
+        <v>351</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>353</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -6613,7 +6679,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>164</v>
+        <v>349</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6625,7 +6691,7 @@
         <v>84</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>84</v>
@@ -6634,34 +6700,34 @@
         <v>84</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>84</v>
+        <v>354</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>165</v>
+        <v>355</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>84</v>
+        <v>356</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>84</v>
+        <v>357</v>
       </c>
       <c r="AR35" t="s" s="2">
-        <v>84</v>
+        <v>358</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6671,27 +6737,27 @@
         <v>83</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>140</v>
+        <v>360</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>141</v>
+        <v>361</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>362</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
       </c>
@@ -6727,19 +6793,19 @@
         <v>84</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>169</v>
+        <v>84</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>171</v>
+        <v>359</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6751,28 +6817,28 @@
         <v>84</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>84</v>
+        <v>364</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>84</v>
+        <v>365</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>165</v>
+        <v>366</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>84</v>
+        <v>367</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>84</v>
+        <v>368</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>84</v>
@@ -6780,7 +6846,7 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>369</v>
@@ -6855,19 +6921,17 @@
         <v>84</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="AC37" s="2"/>
       <c r="AD37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6876,31 +6940,31 @@
         <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>84</v>
+        <v>375</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>106</v>
+        <v>376</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>84</v>
+        <v>377</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>84</v>
+        <v>380</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>378</v>
+        <v>84</v>
       </c>
       <c r="AR37" t="s" s="2">
         <v>84</v>
@@ -6908,12 +6972,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="C38" s="2"/>
+        <v>369</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>382</v>
+      </c>
       <c r="D38" t="s" s="2">
         <v>84</v>
       </c>
@@ -6925,33 +6991,33 @@
         <v>94</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J38" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>114</v>
+        <v>383</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>372</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>373</v>
+      </c>
       <c r="O38" t="s" s="2">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q38" t="s" s="2">
-        <v>384</v>
-      </c>
+      <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
         <v>84</v>
       </c>
@@ -6971,13 +7037,13 @@
         <v>84</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>177</v>
+        <v>84</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>385</v>
+        <v>84</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>386</v>
+        <v>84</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>84</v>
@@ -6995,7 +7061,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>387</v>
+        <v>369</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7004,28 +7070,28 @@
         <v>94</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>84</v>
+        <v>375</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>106</v>
+        <v>376</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>84</v>
+        <v>377</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>84</v>
+        <v>380</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
@@ -7036,10 +7102,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7053,27 +7119,25 @@
         <v>94</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
         <v>161</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>392</v>
+        <v>162</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>393</v>
+        <v>163</v>
       </c>
       <c r="N39" s="2"/>
-      <c r="O39" t="s" s="2">
-        <v>394</v>
-      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>84</v>
       </c>
@@ -7121,7 +7185,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>395</v>
+        <v>164</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7133,7 +7197,7 @@
         <v>84</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>84</v>
@@ -7142,10 +7206,10 @@
         <v>84</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>396</v>
+        <v>84</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>397</v>
+        <v>165</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>84</v>
@@ -7154,7 +7218,7 @@
         <v>84</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>398</v>
+        <v>84</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>84</v>
@@ -7162,21 +7226,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>399</v>
+        <v>386</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>400</v>
+        <v>387</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>84</v>
@@ -7185,21 +7249,21 @@
         <v>84</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>401</v>
+        <v>141</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" t="s" s="2">
-        <v>403</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>84</v>
       </c>
@@ -7235,31 +7299,31 @@
         <v>84</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>404</v>
+        <v>171</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>405</v>
+        <v>84</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>84</v>
@@ -7268,10 +7332,10 @@
         <v>84</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>396</v>
+        <v>84</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>406</v>
+        <v>165</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>84</v>
@@ -7288,10 +7352,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>407</v>
+        <v>388</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>408</v>
+        <v>389</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7305,7 +7369,7 @@
         <v>94</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>84</v>
@@ -7314,19 +7378,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>114</v>
+        <v>390</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>409</v>
+        <v>391</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>410</v>
+        <v>392</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>411</v>
+        <v>393</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>412</v>
+        <v>394</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7375,7 +7439,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>413</v>
+        <v>395</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7399,7 +7463,7 @@
         <v>396</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>84</v>
@@ -7408,7 +7472,7 @@
         <v>84</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>84</v>
+        <v>398</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>84</v>
@@ -7416,10 +7480,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>415</v>
+        <v>399</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>415</v>
+        <v>400</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7433,33 +7497,33 @@
         <v>94</v>
       </c>
       <c r="H42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I42" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="I42" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="J42" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>183</v>
+        <v>114</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>416</v>
+        <v>401</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>418</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>419</v>
+        <v>403</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q42" s="2"/>
+      <c r="Q42" t="s" s="2">
+        <v>404</v>
+      </c>
       <c r="R42" t="s" s="2">
         <v>84</v>
       </c>
@@ -7479,11 +7543,13 @@
         <v>84</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Y42" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>405</v>
+      </c>
       <c r="Z42" t="s" s="2">
-        <v>420</v>
+        <v>406</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>84</v>
@@ -7501,7 +7567,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7510,7 +7576,7 @@
         <v>94</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>421</v>
+        <v>84</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>106</v>
@@ -7522,10 +7588,10 @@
         <v>84</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>137</v>
+        <v>408</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>84</v>
@@ -7542,21 +7608,21 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>424</v>
+        <v>84</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>95</v>
@@ -7565,22 +7631,20 @@
         <v>84</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>427</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
@@ -7605,11 +7669,13 @@
         <v>84</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y43" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z43" t="s" s="2">
-        <v>429</v>
+        <v>84</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>84</v>
@@ -7627,13 +7693,13 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>84</v>
@@ -7645,22 +7711,22 @@
         <v>84</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>430</v>
+        <v>84</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>432</v>
+        <v>417</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>433</v>
+        <v>84</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>434</v>
+        <v>418</v>
       </c>
       <c r="AR43" t="s" s="2">
         <v>84</v>
@@ -7668,10 +7734,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>435</v>
+        <v>419</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7682,31 +7748,29 @@
         <v>82</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J44" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="I44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="K44" t="s" s="2">
-        <v>436</v>
+        <v>108</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>437</v>
+        <v>421</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>439</v>
-      </c>
+        <v>422</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>440</v>
+        <v>423</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -7755,16 +7819,16 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>84</v>
+        <v>425</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>106</v>
@@ -7776,10 +7840,10 @@
         <v>84</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>441</v>
+        <v>416</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>442</v>
+        <v>426</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>84</v>
@@ -7788,18 +7852,18 @@
         <v>84</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>443</v>
+        <v>84</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>444</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>445</v>
+        <v>427</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>445</v>
+        <v>428</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7819,21 +7883,23 @@
         <v>84</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>183</v>
+        <v>114</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>446</v>
+        <v>429</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>447</v>
+        <v>430</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>431</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>432</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
       </c>
@@ -7857,13 +7923,13 @@
         <v>84</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>449</v>
+        <v>84</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>450</v>
+        <v>84</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>451</v>
+        <v>84</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>84</v>
@@ -7881,7 +7947,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7899,19 +7965,19 @@
         <v>84</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>452</v>
+        <v>84</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>453</v>
+        <v>416</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>454</v>
+        <v>434</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>455</v>
+        <v>84</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -7922,10 +7988,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>456</v>
+        <v>435</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>456</v>
+        <v>435</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7939,7 +8005,7 @@
         <v>94</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>84</v>
@@ -7951,16 +8017,16 @@
         <v>183</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>457</v>
+        <v>436</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>458</v>
+        <v>437</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>459</v>
+        <v>438</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>460</v>
+        <v>439</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -7985,13 +8051,11 @@
         <v>84</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>461</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>462</v>
+        <v>440</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>84</v>
@@ -8009,7 +8073,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>456</v>
+        <v>435</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8018,7 +8082,7 @@
         <v>94</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>84</v>
+        <v>441</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>106</v>
@@ -8030,10 +8094,10 @@
         <v>84</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>463</v>
+        <v>137</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>464</v>
+        <v>442</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>84</v>
@@ -8050,21 +8114,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>465</v>
+        <v>443</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>465</v>
+        <v>443</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>84</v>
+        <v>444</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>95</v>
@@ -8076,18 +8140,20 @@
         <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>466</v>
+        <v>183</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>467</v>
+        <v>445</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>468</v>
+        <v>446</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>448</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>84</v>
       </c>
@@ -8111,13 +8177,11 @@
         <v>84</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>84</v>
+        <v>449</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>84</v>
@@ -8135,13 +8199,13 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>465</v>
+        <v>443</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>84</v>
@@ -8153,22 +8217,22 @@
         <v>84</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>470</v>
+        <v>450</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>471</v>
+        <v>451</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>472</v>
+        <v>452</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>473</v>
+        <v>453</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>474</v>
+        <v>454</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>84</v>
@@ -8176,10 +8240,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>475</v>
+        <v>455</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>475</v>
+        <v>455</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8190,10 +8254,10 @@
         <v>82</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>84</v>
@@ -8202,18 +8266,20 @@
         <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>476</v>
+        <v>456</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>477</v>
+        <v>457</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>478</v>
+        <v>458</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>459</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>460</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
       </c>
@@ -8261,13 +8327,13 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>475</v>
+        <v>455</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>84</v>
@@ -8279,33 +8345,33 @@
         <v>84</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>480</v>
+        <v>84</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>481</v>
+        <v>461</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>482</v>
+        <v>462</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>483</v>
+        <v>84</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>84</v>
+        <v>463</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>84</v>
+        <v>464</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>484</v>
+        <v>465</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>484</v>
+        <v>465</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8316,7 +8382,7 @@
         <v>82</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>84</v>
@@ -8328,20 +8394,18 @@
         <v>84</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>485</v>
+        <v>183</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>486</v>
+        <v>466</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>487</v>
+        <v>467</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>489</v>
-      </c>
+        <v>468</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>84</v>
       </c>
@@ -8365,13 +8429,13 @@
         <v>84</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>84</v>
+        <v>469</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>84</v>
+        <v>470</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>84</v>
+        <v>471</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
@@ -8389,37 +8453,37 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>484</v>
+        <v>465</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>490</v>
+        <v>106</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>84</v>
+        <v>472</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>491</v>
+        <v>473</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>492</v>
+        <v>474</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>84</v>
+        <v>475</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8430,10 +8494,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>493</v>
+        <v>476</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>493</v>
+        <v>476</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8456,16 +8520,20 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>162</v>
+        <v>477</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+        <v>478</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>480</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
       </c>
@@ -8489,13 +8557,13 @@
         <v>84</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>84</v>
+        <v>469</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>84</v>
+        <v>481</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>84</v>
+        <v>482</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>84</v>
@@ -8513,7 +8581,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>164</v>
+        <v>476</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8525,7 +8593,7 @@
         <v>84</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>84</v>
@@ -8534,10 +8602,10 @@
         <v>84</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>84</v>
+        <v>483</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>165</v>
+        <v>484</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>84</v>
@@ -8554,24 +8622,24 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>84</v>
@@ -8580,16 +8648,16 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>140</v>
+        <v>486</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>141</v>
+        <v>487</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>167</v>
+        <v>488</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>143</v>
+        <v>489</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8639,87 +8707,85 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>171</v>
+        <v>485</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>84</v>
+        <v>490</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>84</v>
+        <v>491</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>165</v>
+        <v>492</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>84</v>
+        <v>493</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>84</v>
+        <v>494</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>84</v>
+        <v>495</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>496</v>
+        <v>84</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>140</v>
+        <v>497</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>84</v>
       </c>
@@ -8767,37 +8833,37 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>84</v>
+        <v>501</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>84</v>
+        <v>502</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>137</v>
+        <v>503</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>84</v>
+        <v>504</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -8808,10 +8874,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8822,10 +8888,10 @@
         <v>82</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>84</v>
@@ -8834,16 +8900,20 @@
         <v>84</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>508</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>510</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>84</v>
       </c>
@@ -8891,19 +8961,19 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>504</v>
+        <v>84</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>106</v>
+        <v>511</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>84</v>
@@ -8912,10 +8982,10 @@
         <v>84</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>84</v>
@@ -8924,7 +8994,7 @@
         <v>84</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>507</v>
+        <v>84</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>84</v>
@@ -8932,10 +9002,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8949,7 +9019,7 @@
         <v>94</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>84</v>
@@ -8958,13 +9028,13 @@
         <v>84</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>501</v>
+        <v>161</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>509</v>
+        <v>162</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>510</v>
+        <v>163</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -9015,7 +9085,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>508</v>
+        <v>164</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9024,10 +9094,10 @@
         <v>94</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>504</v>
+        <v>84</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>84</v>
@@ -9036,10 +9106,10 @@
         <v>84</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>505</v>
+        <v>84</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>511</v>
+        <v>165</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>84</v>
@@ -9048,7 +9118,7 @@
         <v>84</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>512</v>
+        <v>84</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>84</v>
@@ -9056,21 +9126,21 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>84</v>
@@ -9082,20 +9152,18 @@
         <v>84</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>514</v>
+        <v>141</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>515</v>
+        <v>167</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>517</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>84</v>
       </c>
@@ -9119,13 +9187,13 @@
         <v>84</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>518</v>
+        <v>84</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>519</v>
+        <v>84</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>84</v>
@@ -9143,31 +9211,31 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>513</v>
+        <v>171</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>520</v>
+        <v>84</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>521</v>
+        <v>84</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>432</v>
+        <v>165</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>84</v>
@@ -9184,14 +9252,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>84</v>
+        <v>517</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -9204,25 +9272,25 @@
         <v>84</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>525</v>
+        <v>143</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>526</v>
+        <v>149</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>84</v>
@@ -9247,13 +9315,13 @@
         <v>84</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>449</v>
+        <v>84</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>527</v>
+        <v>84</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>528</v>
+        <v>84</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>84</v>
@@ -9271,7 +9339,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9283,19 +9351,19 @@
         <v>84</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>520</v>
+        <v>84</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>521</v>
+        <v>84</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>432</v>
+        <v>137</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>84</v>
@@ -9312,10 +9380,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9329,7 +9397,7 @@
         <v>94</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>84</v>
@@ -9338,18 +9406,16 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="N57" s="2"/>
-      <c r="O57" t="s" s="2">
-        <v>533</v>
-      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>84</v>
       </c>
@@ -9397,7 +9463,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9406,7 +9472,7 @@
         <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>84</v>
+        <v>525</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>106</v>
@@ -9418,10 +9484,10 @@
         <v>84</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>84</v>
+        <v>526</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>84</v>
@@ -9430,7 +9496,7 @@
         <v>84</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>84</v>
+        <v>528</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>84</v>
@@ -9438,10 +9504,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9455,7 +9521,7 @@
         <v>94</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>84</v>
@@ -9464,13 +9530,13 @@
         <v>84</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>161</v>
+        <v>522</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9521,7 +9587,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9530,7 +9596,7 @@
         <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>84</v>
+        <v>525</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>106</v>
@@ -9542,10 +9608,10 @@
         <v>84</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>505</v>
+        <v>526</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>84</v>
@@ -9554,7 +9620,7 @@
         <v>84</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>84</v>
+        <v>533</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>84</v>
@@ -9562,10 +9628,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9576,7 +9642,7 @@
         <v>82</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>84</v>
@@ -9585,21 +9651,23 @@
         <v>84</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>540</v>
+        <v>183</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>537</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>538</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
       </c>
@@ -9623,13 +9691,13 @@
         <v>84</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>84</v>
+        <v>539</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>84</v>
+        <v>540</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>84</v>
@@ -9647,13 +9715,13 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>84</v>
@@ -9665,13 +9733,13 @@
         <v>84</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>84</v>
+        <v>541</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>545</v>
+        <v>452</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>84</v>
@@ -9688,10 +9756,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9711,21 +9779,23 @@
         <v>84</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="O60" t="s" s="2">
         <v>547</v>
       </c>
-      <c r="L60" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>84</v>
       </c>
@@ -9749,13 +9819,13 @@
         <v>84</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>84</v>
+        <v>469</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>84</v>
+        <v>548</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>84</v>
+        <v>549</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>84</v>
@@ -9773,7 +9843,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9791,13 +9861,13 @@
         <v>84</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>84</v>
+        <v>541</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>551</v>
+        <v>452</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>84</v>
@@ -9814,10 +9884,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9828,7 +9898,7 @@
         <v>82</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>84</v>
@@ -9837,22 +9907,20 @@
         <v>84</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>485</v>
+        <v>551</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" s="2"/>
+      <c r="O61" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>84</v>
@@ -9901,13 +9969,13 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>84</v>
@@ -9922,10 +9990,10 @@
         <v>84</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>557</v>
+        <v>84</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>84</v>
@@ -9942,10 +10010,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9971,10 +10039,10 @@
         <v>161</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>162</v>
+        <v>557</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>163</v>
+        <v>558</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10025,7 +10093,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>164</v>
+        <v>556</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10037,7 +10105,7 @@
         <v>84</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>84</v>
@@ -10046,10 +10114,10 @@
         <v>84</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>84</v>
+        <v>526</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>165</v>
+        <v>559</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>84</v>
@@ -10073,7 +10141,7 @@
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -10089,19 +10157,19 @@
         <v>84</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>140</v>
+        <v>561</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>141</v>
+        <v>562</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>167</v>
+        <v>563</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>143</v>
+        <v>564</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10151,7 +10219,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>171</v>
+        <v>560</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10163,7 +10231,7 @@
         <v>84</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>84</v>
@@ -10172,10 +10240,10 @@
         <v>84</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>84</v>
+        <v>565</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>165</v>
+        <v>566</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>84</v>
@@ -10192,14 +10260,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>496</v>
+        <v>84</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -10212,26 +10280,24 @@
         <v>84</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J64" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>140</v>
+        <v>568</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>497</v>
+        <v>569</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>498</v>
+        <v>570</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>571</v>
+      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>84</v>
       </c>
@@ -10279,7 +10345,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>499</v>
+        <v>567</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10291,7 +10357,7 @@
         <v>84</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>84</v>
@@ -10300,10 +10366,10 @@
         <v>84</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>84</v>
+        <v>565</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>137</v>
+        <v>572</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>84</v>
@@ -10320,10 +10386,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>562</v>
+        <v>573</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>562</v>
+        <v>573</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10331,10 +10397,10 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>84</v>
@@ -10346,19 +10412,19 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>183</v>
+        <v>506</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>563</v>
+        <v>574</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>564</v>
+        <v>575</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>565</v>
+        <v>576</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>274</v>
+        <v>577</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>84</v>
@@ -10383,13 +10449,13 @@
         <v>84</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>449</v>
+        <v>84</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>566</v>
+        <v>84</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>276</v>
+        <v>84</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>84</v>
@@ -10407,13 +10473,13 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>562</v>
+        <v>573</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>84</v>
@@ -10425,16 +10491,16 @@
         <v>84</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>567</v>
+        <v>84</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>279</v>
+        <v>578</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>280</v>
+        <v>579</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>281</v>
+        <v>84</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>84</v>
@@ -10448,10 +10514,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>568</v>
+        <v>580</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>568</v>
+        <v>580</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10471,23 +10537,19 @@
         <v>84</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>350</v>
+        <v>161</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>569</v>
+        <v>162</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>84</v>
       </c>
@@ -10535,7 +10597,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>568</v>
+        <v>164</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10547,25 +10609,25 @@
         <v>84</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>572</v>
+        <v>84</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>358</v>
+        <v>84</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>359</v>
+        <v>165</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>360</v>
+        <v>84</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>84</v>
@@ -10576,21 +10638,21 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>84</v>
@@ -10602,20 +10664,18 @@
         <v>84</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>574</v>
+        <v>141</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>575</v>
+        <v>167</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>419</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>84</v>
       </c>
@@ -10639,13 +10699,13 @@
         <v>84</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>577</v>
+        <v>84</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>420</v>
+        <v>84</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>84</v>
@@ -10663,19 +10723,19 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>573</v>
+        <v>171</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>578</v>
+        <v>84</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>84</v>
@@ -10684,10 +10744,10 @@
         <v>84</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>422</v>
+        <v>165</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>84</v>
@@ -10704,14 +10764,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>424</v>
+        <v>517</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10724,25 +10784,25 @@
         <v>84</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>425</v>
+        <v>518</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>426</v>
+        <v>519</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>427</v>
+        <v>143</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>428</v>
+        <v>149</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>84</v>
@@ -10767,13 +10827,13 @@
         <v>84</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>580</v>
+        <v>84</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>581</v>
+        <v>84</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>84</v>
@@ -10791,7 +10851,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>579</v>
+        <v>520</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -10803,25 +10863,25 @@
         <v>84</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>430</v>
+        <v>84</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>431</v>
+        <v>84</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>432</v>
+        <v>137</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>433</v>
+        <v>84</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>84</v>
@@ -10832,10 +10892,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10843,10 +10903,10 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>84</v>
@@ -10855,22 +10915,22 @@
         <v>84</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>85</v>
+        <v>183</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>488</v>
+        <v>586</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>489</v>
+        <v>274</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>84</v>
@@ -10895,13 +10955,13 @@
         <v>84</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>84</v>
+        <v>469</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>84</v>
+        <v>587</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>84</v>
+        <v>276</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>84</v>
@@ -10919,13 +10979,13 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>84</v>
@@ -10937,16 +10997,16 @@
         <v>84</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>84</v>
+        <v>588</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>491</v>
+        <v>279</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>492</v>
+        <v>280</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>84</v>
+        <v>281</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>84</v>
@@ -10955,11 +11015,523 @@
         <v>84</v>
       </c>
       <c r="AR69" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="P70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AQ70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR70" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="P71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR71" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="P72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AQ72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR72" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="P73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR73" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR69">
+  <autoFilter ref="A1:AR73">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10969,7 +11541,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI68">
+  <conditionalFormatting sqref="A2:AI72">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3263" uniqueCount="653">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3263" uniqueCount="656">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -831,28 +831,6 @@
   </si>
   <si>
     <t>Used for filtering what observations are retrieved and displayed.</t>
-  </si>
-  <si>
-    <t>Codes for high level observation categories.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.category:Laboratory</t>
-  </si>
-  <si>
-    <t>Laboratory</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -863,6 +841,31 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
+    <t>Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>843: fixed value = http://terminology.hl7.org/CodeSystem/observation-category#laboratory</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category:Laboratory</t>
+  </si>
+  <si>
+    <t>Laboratory</t>
+  </si>
+  <si>
     <t>Observation.code</t>
   </si>
   <si>
@@ -1117,6 +1120,12 @@
   </si>
   <si>
     <t>Observations have no value if you don't know who or what they're about.</t>
+  </si>
+  <si>
+    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
+  </si>
+  <si>
+    <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -2408,7 +2417,7 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="253.0703125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="183.43359375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
@@ -5249,7 +5258,7 @@
         <v>84</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>84</v>
+        <v>263</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>84</v>
@@ -5267,16 +5276,16 @@
         <v>118</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -5301,7 +5310,7 @@
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>84</v>
+        <v>267</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>84</v>
@@ -5316,10 +5325,10 @@
         <v>84</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AR23" t="s" s="2">
         <v>84</v>
@@ -5327,13 +5336,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>258</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>84</v>
@@ -5377,7 +5386,7 @@
         <v>84</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>84</v>
@@ -5395,10 +5404,10 @@
         <v>118</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>84</v>
@@ -5446,10 +5455,10 @@
         <v>84</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AR24" t="s" s="2">
         <v>84</v>
@@ -5457,14 +5466,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5486,16 +5495,16 @@
         <v>183</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>84</v>
@@ -5523,10 +5532,10 @@
         <v>188</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>84</v>
@@ -5544,7 +5553,7 @@
         <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>94</v>
@@ -5565,30 +5574,30 @@
         <v>84</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5709,10 +5718,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5835,10 +5844,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5861,19 +5870,19 @@
         <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>84</v>
@@ -5922,7 +5931,7 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -5937,7 +5946,7 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>84</v>
@@ -5949,10 +5958,10 @@
         <v>84</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>84</v>
@@ -5963,10 +5972,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6087,10 +6096,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6213,10 +6222,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6242,16 +6251,16 @@
         <v>108</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>84</v>
@@ -6261,7 +6270,7 @@
         <v>84</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="T31" t="s" s="2">
         <v>84</v>
@@ -6300,7 +6309,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6315,7 +6324,7 @@
         <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>84</v>
@@ -6327,10 +6336,10 @@
         <v>84</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>84</v>
@@ -6341,10 +6350,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6370,13 +6379,13 @@
         <v>161</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6426,7 +6435,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6453,10 +6462,10 @@
         <v>84</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>84</v>
@@ -6467,10 +6476,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6496,14 +6505,14 @@
         <v>114</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6552,7 +6561,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6567,7 +6576,7 @@
         <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>84</v>
@@ -6579,10 +6588,10 @@
         <v>84</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
@@ -6593,10 +6602,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6622,14 +6631,14 @@
         <v>161</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6678,7 +6687,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6693,7 +6702,7 @@
         <v>106</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>84</v>
@@ -6705,10 +6714,10 @@
         <v>84</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
@@ -6719,10 +6728,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6745,19 +6754,19 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -6806,7 +6815,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6833,10 +6842,10 @@
         <v>84</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
@@ -6847,10 +6856,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6876,16 +6885,16 @@
         <v>161</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -6934,7 +6943,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6961,10 +6970,10 @@
         <v>84</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
@@ -6975,10 +6984,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7001,19 +7010,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -7062,7 +7071,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -7077,25 +7086,25 @@
         <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>84</v>
+        <v>356</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>84</v>
+        <v>357</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AR37" t="s" s="2">
         <v>84</v>
@@ -7103,10 +7112,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7129,16 +7138,16 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7188,7 +7197,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7215,13 +7224,13 @@
         <v>84</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AR38" t="s" s="2">
         <v>84</v>
@@ -7229,14 +7238,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7255,19 +7264,19 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -7316,7 +7325,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7337,19 +7346,19 @@
         <v>84</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>84</v>
@@ -7357,14 +7366,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7383,19 +7392,19 @@
         <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7432,7 +7441,7 @@
         <v>84</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
@@ -7442,7 +7451,7 @@
         <v>170</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7451,10 +7460,10 @@
         <v>94</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>84</v>
@@ -7463,19 +7472,19 @@
         <v>84</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>84</v>
@@ -7483,16 +7492,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7511,19 +7520,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7572,7 +7581,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7581,31 +7590,31 @@
         <v>94</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>84</v>
@@ -7613,10 +7622,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7639,16 +7648,16 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7698,7 +7707,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7713,10 +7722,10 @@
         <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>84</v>
@@ -7725,13 +7734,13 @@
         <v>84</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>84</v>
@@ -7739,10 +7748,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7765,17 +7774,17 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
@@ -7824,7 +7833,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7839,25 +7848,25 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="AR43" t="s" s="2">
         <v>84</v>
@@ -7865,10 +7874,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7891,19 +7900,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -7940,7 +7949,7 @@
         <v>84</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AC44" s="2"/>
       <c r="AD44" t="s" s="2">
@@ -7950,7 +7959,7 @@
         <v>170</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7959,10 +7968,10 @@
         <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>84</v>
@@ -7974,30 +7983,30 @@
         <v>84</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>84</v>
@@ -8019,19 +8028,19 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -8080,7 +8089,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8089,10 +8098,10 @@
         <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>84</v>
@@ -8104,27 +8113,27 @@
         <v>84</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8245,10 +8254,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8371,10 +8380,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8397,19 +8406,19 @@
         <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>84</v>
@@ -8458,7 +8467,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8473,7 +8482,7 @@
         <v>106</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>84</v>
@@ -8485,10 +8494,10 @@
         <v>84</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -8499,10 +8508,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8528,20 +8537,20 @@
         <v>114</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q49" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="R49" t="s" s="2">
         <v>84</v>
@@ -8565,10 +8574,10 @@
         <v>177</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
@@ -8586,7 +8595,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8613,10 +8622,10 @@
         <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8627,10 +8636,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8656,14 +8665,14 @@
         <v>161</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -8712,7 +8721,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8727,7 +8736,7 @@
         <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>84</v>
@@ -8739,10 +8748,10 @@
         <v>84</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -8753,10 +8762,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8782,14 +8791,14 @@
         <v>108</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -8838,7 +8847,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8847,7 +8856,7 @@
         <v>94</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>106</v>
@@ -8865,10 +8874,10 @@
         <v>84</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -8879,10 +8888,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8908,16 +8917,16 @@
         <v>114</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -8966,7 +8975,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8993,10 +9002,10 @@
         <v>84</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -9007,10 +9016,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9036,16 +9045,16 @@
         <v>183</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>84</v>
@@ -9074,7 +9083,7 @@
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>84</v>
@@ -9092,7 +9101,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -9101,7 +9110,7 @@
         <v>94</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>106</v>
@@ -9122,7 +9131,7 @@
         <v>137</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -9133,14 +9142,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -9162,16 +9171,16 @@
         <v>183</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>84</v>
@@ -9200,7 +9209,7 @@
       </c>
       <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>84</v>
@@ -9218,7 +9227,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9233,7 +9242,7 @@
         <v>106</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>84</v>
@@ -9242,27 +9251,27 @@
         <v>84</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR54" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9285,19 +9294,19 @@
         <v>84</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>84</v>
@@ -9346,7 +9355,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9361,10 +9370,10 @@
         <v>106</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>84</v>
@@ -9373,10 +9382,10 @@
         <v>84</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9387,10 +9396,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9416,13 +9425,13 @@
         <v>183</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9448,13 +9457,13 @@
         <v>84</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>84</v>
@@ -9472,7 +9481,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9496,27 +9505,27 @@
         <v>84</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR56" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9542,16 +9551,16 @@
         <v>183</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>84</v>
@@ -9576,13 +9585,13 @@
         <v>84</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>84</v>
@@ -9600,7 +9609,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9627,10 +9636,10 @@
         <v>84</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9641,10 +9650,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9667,16 +9676,16 @@
         <v>84</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9726,7 +9735,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9741,36 +9750,36 @@
         <v>106</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR58" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9793,16 +9802,16 @@
         <v>84</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9852,7 +9861,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9876,27 +9885,27 @@
         <v>84</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9919,19 +9928,19 @@
         <v>84</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -9980,7 +9989,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9992,7 +10001,7 @@
         <v>84</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>84</v>
@@ -10007,10 +10016,10 @@
         <v>84</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -10021,10 +10030,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10145,10 +10154,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10271,14 +10280,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -10300,10 +10309,10 @@
         <v>140</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>143</v>
@@ -10358,7 +10367,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10399,10 +10408,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10425,13 +10434,13 @@
         <v>84</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10482,7 +10491,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10491,13 +10500,13 @@
         <v>94</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>84</v>
@@ -10509,10 +10518,10 @@
         <v>84</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
@@ -10523,10 +10532,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10549,13 +10558,13 @@
         <v>84</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10606,7 +10615,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -10615,13 +10624,13 @@
         <v>94</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>84</v>
@@ -10633,10 +10642,10 @@
         <v>84</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>
@@ -10647,10 +10656,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10676,16 +10685,16 @@
         <v>183</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>84</v>
@@ -10713,10 +10722,10 @@
         <v>118</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>84</v>
@@ -10734,7 +10743,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10758,13 +10767,13 @@
         <v>84</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>84</v>
@@ -10775,10 +10784,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10804,16 +10813,16 @@
         <v>183</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>84</v>
@@ -10838,13 +10847,13 @@
         <v>84</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>84</v>
@@ -10862,7 +10871,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -10886,13 +10895,13 @@
         <v>84</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>84</v>
@@ -10903,10 +10912,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10929,17 +10938,17 @@
         <v>84</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>84</v>
@@ -10988,7 +10997,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -11018,7 +11027,7 @@
         <v>84</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>84</v>
@@ -11029,10 +11038,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11058,10 +11067,10 @@
         <v>161</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -11112,7 +11121,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11139,10 +11148,10 @@
         <v>84</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
@@ -11153,10 +11162,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11179,16 +11188,16 @@
         <v>95</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -11238,7 +11247,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11265,10 +11274,10 @@
         <v>84</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
@@ -11279,10 +11288,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11305,16 +11314,16 @@
         <v>95</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -11364,7 +11373,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11391,10 +11400,10 @@
         <v>84</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>
@@ -11405,10 +11414,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11431,19 +11440,19 @@
         <v>95</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>84</v>
@@ -11492,7 +11501,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11519,10 +11528,10 @@
         <v>84</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>
@@ -11533,10 +11542,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11657,10 +11666,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11783,14 +11792,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -11812,10 +11821,10 @@
         <v>140</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>143</v>
@@ -11870,7 +11879,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -11911,10 +11920,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11940,16 +11949,16 @@
         <v>183</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>84</v>
@@ -11974,13 +11983,13 @@
         <v>84</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>84</v>
@@ -11998,7 +12007,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>94</v>
@@ -12022,16 +12031,16 @@
         <v>84</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AQ76" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AR76" t="s" s="2">
         <v>84</v>
@@ -12039,10 +12048,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12065,19 +12074,19 @@
         <v>95</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>84</v>
@@ -12126,7 +12135,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12150,27 +12159,27 @@
         <v>84</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR77" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12196,16 +12205,16 @@
         <v>183</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>84</v>
@@ -12233,10 +12242,10 @@
         <v>188</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>84</v>
@@ -12254,7 +12263,7 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12263,7 +12272,7 @@
         <v>94</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>106</v>
@@ -12284,7 +12293,7 @@
         <v>137</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>84</v>
@@ -12295,14 +12304,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -12324,16 +12333,16 @@
         <v>183</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>84</v>
@@ -12361,10 +12370,10 @@
         <v>188</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>84</v>
@@ -12382,7 +12391,7 @@
         <v>84</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12406,27 +12415,27 @@
         <v>84</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR79" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12452,16 +12461,16 @@
         <v>85</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>84</v>
@@ -12510,7 +12519,7 @@
         <v>84</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -12537,10 +12546,10 @@
         <v>84</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="AQ80" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1106,7 +1106,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>
@@ -1291,7 +1291,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Organization|http://va.gov/fhir/StructureDefinition/Practitioner)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -937,7 +937,7 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
-    <t>853: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-95.03 &gt; 95.3-)</t>
+    <t>853: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-)</t>
   </si>
   <si>
     <t>C*E.1-8, C*E.10-22</t>
@@ -1018,7 +1018,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>853-2: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC - CODE (63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-95.03 &gt; 95.3-.01)</t>
+    <t>853-2: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC - CODE (63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-.01)</t>
   </si>
   <si>
     <t>C*E.1</t>
@@ -1042,7 +1042,7 @@
     <t>Coding.display</t>
   </si>
   <si>
-    <t>853-3: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC - COMPONENT (63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-95.03 &gt; 95.3-1)</t>
+    <t>853-3: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC - COMPONENT (63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-1)</t>
   </si>
   <si>
     <t>C*E.2 - but note this is not well followed</t>
@@ -2416,7 +2416,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="253.0703125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="251.90234375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="247.40625" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1106,7 +1106,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3263" uniqueCount="656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3263" uniqueCount="657">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1547,6 +1547,9 @@
   <si>
     <t>obs-6
 us-core-2</t>
+  </si>
+  <si>
+    <t>null: target not supported</t>
   </si>
   <si>
     <t>value.nullFlavor</t>
@@ -9116,7 +9119,7 @@
         <v>106</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>84</v>
+        <v>492</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>84</v>
@@ -9131,7 +9134,7 @@
         <v>137</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -9142,14 +9145,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -9171,16 +9174,16 @@
         <v>183</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>84</v>
@@ -9209,7 +9212,7 @@
       </c>
       <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>84</v>
@@ -9227,7 +9230,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9242,7 +9245,7 @@
         <v>106</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>84</v>
@@ -9251,27 +9254,27 @@
         <v>84</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR54" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9294,19 +9297,19 @@
         <v>84</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>84</v>
@@ -9355,7 +9358,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9370,10 +9373,10 @@
         <v>106</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>84</v>
@@ -9382,10 +9385,10 @@
         <v>84</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9396,10 +9399,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9425,13 +9428,13 @@
         <v>183</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9457,13 +9460,13 @@
         <v>84</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>84</v>
@@ -9481,7 +9484,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9505,27 +9508,27 @@
         <v>84</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR56" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9551,16 +9554,16 @@
         <v>183</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>84</v>
@@ -9585,13 +9588,13 @@
         <v>84</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>84</v>
@@ -9609,7 +9612,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9636,10 +9639,10 @@
         <v>84</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9650,10 +9653,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9676,16 +9679,16 @@
         <v>84</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9735,7 +9738,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9750,36 +9753,36 @@
         <v>106</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR58" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9802,16 +9805,16 @@
         <v>84</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9861,7 +9864,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9885,27 +9888,27 @@
         <v>84</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9928,19 +9931,19 @@
         <v>84</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -9989,7 +9992,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10001,7 +10004,7 @@
         <v>84</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>84</v>
@@ -10016,10 +10019,10 @@
         <v>84</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -10030,10 +10033,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10154,10 +10157,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10280,14 +10283,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -10309,10 +10312,10 @@
         <v>140</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>143</v>
@@ -10367,7 +10370,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10408,10 +10411,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10434,13 +10437,13 @@
         <v>84</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10491,7 +10494,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10500,13 +10503,13 @@
         <v>94</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>84</v>
@@ -10518,10 +10521,10 @@
         <v>84</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
@@ -10532,10 +10535,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10558,13 +10561,13 @@
         <v>84</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10615,7 +10618,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -10624,13 +10627,13 @@
         <v>94</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>84</v>
@@ -10642,10 +10645,10 @@
         <v>84</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>
@@ -10656,10 +10659,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10685,16 +10688,16 @@
         <v>183</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>84</v>
@@ -10722,10 +10725,10 @@
         <v>118</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>84</v>
@@ -10743,7 +10746,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -10767,13 +10770,13 @@
         <v>84</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>84</v>
@@ -10784,10 +10787,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10813,16 +10816,16 @@
         <v>183</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>84</v>
@@ -10847,13 +10850,13 @@
         <v>84</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>84</v>
@@ -10871,7 +10874,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -10895,13 +10898,13 @@
         <v>84</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>84</v>
@@ -10912,10 +10915,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10938,17 +10941,17 @@
         <v>84</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>84</v>
@@ -10997,7 +11000,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -11027,7 +11030,7 @@
         <v>84</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>84</v>
@@ -11038,10 +11041,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11067,10 +11070,10 @@
         <v>161</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -11121,7 +11124,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11148,10 +11151,10 @@
         <v>84</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
@@ -11162,10 +11165,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11188,16 +11191,16 @@
         <v>95</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -11247,7 +11250,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11274,10 +11277,10 @@
         <v>84</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
@@ -11288,10 +11291,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11314,16 +11317,16 @@
         <v>95</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -11373,7 +11376,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11400,10 +11403,10 @@
         <v>84</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>
@@ -11414,10 +11417,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11440,19 +11443,19 @@
         <v>95</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>84</v>
@@ -11501,7 +11504,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11528,10 +11531,10 @@
         <v>84</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>
@@ -11542,10 +11545,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11666,10 +11669,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11792,14 +11795,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -11821,10 +11824,10 @@
         <v>140</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>143</v>
@@ -11879,7 +11882,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -11920,10 +11923,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11949,13 +11952,13 @@
         <v>183</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="O76" t="s" s="2">
         <v>277</v>
@@ -11983,10 +11986,10 @@
         <v>84</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="Z76" t="s" s="2">
         <v>279</v>
@@ -12007,7 +12010,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>94</v>
@@ -12031,7 +12034,7 @@
         <v>84</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>282</v>
@@ -12048,10 +12051,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12077,13 +12080,13 @@
         <v>420</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="O77" t="s" s="2">
         <v>424</v>
@@ -12135,7 +12138,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12159,7 +12162,7 @@
         <v>84</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>428</v>
@@ -12176,10 +12179,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12205,13 +12208,13 @@
         <v>183</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="O78" t="s" s="2">
         <v>489</v>
@@ -12242,7 +12245,7 @@
         <v>188</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="Z78" t="s" s="2">
         <v>490</v>
@@ -12263,7 +12266,7 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12272,7 +12275,7 @@
         <v>94</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>106</v>
@@ -12293,7 +12296,7 @@
         <v>137</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>84</v>
@@ -12304,14 +12307,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -12333,16 +12336,16 @@
         <v>183</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>84</v>
@@ -12370,28 +12373,28 @@
         <v>188</v>
       </c>
       <c r="Y79" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF79" t="s" s="2">
         <v>651</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>650</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12415,27 +12418,27 @@
         <v>84</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR79" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12461,16 +12464,16 @@
         <v>85</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>84</v>
@@ -12519,7 +12522,7 @@
         <v>84</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -12546,10 +12549,10 @@
         <v>84</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AQ80" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1549,7 +1549,7 @@
 us-core-2</t>
   </si>
   <si>
-    <t>null: target not supported</t>
+    <t>2031: target not supported</t>
   </si>
   <si>
     <t>value.nullFlavor</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -797,7 +797,7 @@
     <t>Need to track the status of individual results. Some results are finalized before the whole report is finalized.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFLabObservationStatus</t>
+    <t>http://va.gov/fhir/ValueSet/LabObservationStatus</t>
   </si>
   <si>
     <t>860: terminologyMaps using VF_LabObservationStatus on CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - DISPOSITION (63.04-.35 &gt; 63.07-10)</t>
@@ -1574,7 +1574,7 @@
     <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFLabInterpretation</t>
+    <t>http://va.gov/fhir/ValueSet/LabInterpretation</t>
   </si>
   <si>
     <t>852: terminologyMaps using VF_LabInterpretation on CHEM, HEM, TOX, RIA, SER, etc. - testnames (63.04-2+through+862)</t>
@@ -2409,7 +2409,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.97265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.4921875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3343" uniqueCount="659">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3343" uniqueCount="664">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1131,7 +1131,8 @@
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
-    <t>demographics.lrdfn</t>
+    <t>demographics.lrdfn
+accession.collected</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1263,6 +1264,9 @@
     <t>Chem.LabChem.LabChemSpecimenDateTime,Chem.LabPanel.LabChemSpecimenDateTime,Chem.OrderedLabPanel.LabChemSpecimenDateTime,Chem.PatientLabChem.LabChemSpecimenDateTime</t>
   </si>
   <si>
+    <t>lab.collected</t>
+  </si>
+  <si>
     <t>Observation.issued</t>
   </si>
   <si>
@@ -1285,6 +1289,9 @@
     <t>Chem.LabChem.LabChemCompleteDateTime,Chem.LabPanel.LabChemCompleteDateTime,Chem.OrderedLabPanel.LabChemCompleteDateTime,Chem.PatientLabChem.LabChemCompleteDateTime</t>
   </si>
   <si>
+    <t>lab.resulted,lab.status</t>
+  </si>
+  <si>
     <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
   </si>
   <si>
@@ -1316,6 +1323,9 @@
     <t>Chem.LabChem.AccessionInstitutionIEN,Chem.PatientLabChem.AccessionInstitutionIEN</t>
   </si>
   <si>
+    <t>lab.facility</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -1623,6 +1633,9 @@
     <t>Chem.LabPanel.LabPanelComment</t>
   </si>
   <si>
+    <t>lab.comment</t>
+  </si>
+  <si>
     <t>NTE.3 (partner NTE to OBX, or sometimes another (child?) OBX)</t>
   </si>
   <si>
@@ -1710,6 +1723,9 @@
   </si>
   <si>
     <t>Chem.LabChem.ShortAccessionNumber,Chem.PatientLabChem.ShortAccessionNumber</t>
+  </si>
+  <si>
+    <t>lab.groupName</t>
   </si>
   <si>
     <t>&lt; 123038009 |Specimen|</t>
@@ -7732,7 +7748,7 @@
         <v>399</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>85</v>
+        <v>400</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>391</v>
@@ -7755,10 +7771,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7781,16 +7797,16 @@
         <v>96</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7840,7 +7856,7 @@
         <v>85</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>83</v>
@@ -7855,13 +7871,13 @@
         <v>107</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>85</v>
+        <v>408</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>85</v>
@@ -7870,13 +7886,13 @@
         <v>85</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AS42" t="s" s="2">
         <v>85</v>
@@ -7884,10 +7900,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7910,17 +7926,17 @@
         <v>96</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>85</v>
@@ -7969,7 +7985,7 @@
         <v>85</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>83</v>
@@ -7984,28 +8000,28 @@
         <v>107</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>85</v>
+        <v>419</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="AS43" t="s" s="2">
         <v>85</v>
@@ -8013,10 +8029,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8039,19 +8055,19 @@
         <v>96</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>85</v>
@@ -8098,7 +8114,7 @@
         <v>171</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>83</v>
@@ -8107,10 +8123,10 @@
         <v>95</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>85</v>
@@ -8125,30 +8141,30 @@
         <v>85</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AR44" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS44" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>85</v>
@@ -8170,19 +8186,19 @@
         <v>96</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>85</v>
@@ -8231,7 +8247,7 @@
         <v>85</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
@@ -8240,10 +8256,10 @@
         <v>95</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>85</v>
@@ -8258,27 +8274,27 @@
         <v>85</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AR45" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS45" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8402,10 +8418,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8531,10 +8547,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8557,19 +8573,19 @@
         <v>96</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>85</v>
@@ -8618,7 +8634,7 @@
         <v>85</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
@@ -8633,7 +8649,7 @@
         <v>107</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>85</v>
@@ -8648,10 +8664,10 @@
         <v>85</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>85</v>
@@ -8662,10 +8678,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8691,20 +8707,20 @@
         <v>115</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q49" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="R49" t="s" s="2">
         <v>85</v>
@@ -8728,10 +8744,10 @@
         <v>178</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>85</v>
@@ -8749,7 +8765,7 @@
         <v>85</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
@@ -8779,10 +8795,10 @@
         <v>85</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>85</v>
@@ -8793,10 +8809,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8822,14 +8838,14 @@
         <v>162</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>85</v>
@@ -8878,7 +8894,7 @@
         <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -8893,7 +8909,7 @@
         <v>107</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>85</v>
@@ -8908,10 +8924,10 @@
         <v>85</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>85</v>
@@ -8922,10 +8938,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8951,14 +8967,14 @@
         <v>109</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>85</v>
@@ -9007,7 +9023,7 @@
         <v>85</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -9016,7 +9032,7 @@
         <v>95</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>107</v>
@@ -9037,10 +9053,10 @@
         <v>85</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>85</v>
@@ -9051,10 +9067,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9080,16 +9096,16 @@
         <v>115</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>85</v>
@@ -9138,7 +9154,7 @@
         <v>85</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
@@ -9168,10 +9184,10 @@
         <v>85</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>85</v>
@@ -9182,10 +9198,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9211,16 +9227,16 @@
         <v>184</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>85</v>
@@ -9249,7 +9265,7 @@
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>85</v>
@@ -9267,7 +9283,7 @@
         <v>85</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -9276,13 +9292,13 @@
         <v>95</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>85</v>
@@ -9300,7 +9316,7 @@
         <v>138</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>85</v>
@@ -9311,14 +9327,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -9340,16 +9356,16 @@
         <v>184</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>85</v>
@@ -9378,7 +9394,7 @@
       </c>
       <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>85</v>
@@ -9396,7 +9412,7 @@
         <v>85</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -9411,7 +9427,7 @@
         <v>107</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>85</v>
@@ -9423,27 +9439,27 @@
         <v>85</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS54" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9466,19 +9482,19 @@
         <v>85</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>85</v>
@@ -9527,7 +9543,7 @@
         <v>85</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -9542,13 +9558,13 @@
         <v>107</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>85</v>
+        <v>519</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>85</v>
@@ -9557,10 +9573,10 @@
         <v>85</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>85</v>
@@ -9571,10 +9587,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9600,13 +9616,13 @@
         <v>184</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9632,31 +9648,31 @@
         <v>85</v>
       </c>
       <c r="X56" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF56" t="s" s="2">
         <v>522</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="Z56" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>518</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
@@ -9683,27 +9699,27 @@
         <v>85</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS56" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9729,16 +9745,16 @@
         <v>184</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>85</v>
@@ -9763,13 +9779,13 @@
         <v>85</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>85</v>
@@ -9787,7 +9803,7 @@
         <v>85</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
@@ -9817,10 +9833,10 @@
         <v>85</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>85</v>
@@ -9831,10 +9847,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9857,16 +9873,16 @@
         <v>85</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9916,7 +9932,7 @@
         <v>85</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
@@ -9931,39 +9947,39 @@
         <v>107</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>85</v>
+        <v>549</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS58" t="s" s="2">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9986,16 +10002,16 @@
         <v>85</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -10045,7 +10061,7 @@
         <v>85</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
@@ -10072,27 +10088,27 @@
         <v>85</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS59" t="s" s="2">
-        <v>557</v>
+        <v>562</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10115,19 +10131,19 @@
         <v>85</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>85</v>
@@ -10176,7 +10192,7 @@
         <v>85</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
@@ -10188,7 +10204,7 @@
         <v>85</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>85</v>
@@ -10206,10 +10222,10 @@
         <v>85</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>85</v>
@@ -10220,10 +10236,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10347,10 +10363,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10476,14 +10492,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -10505,10 +10521,10 @@
         <v>141</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>144</v>
@@ -10563,7 +10579,7 @@
         <v>85</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -10607,10 +10623,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10633,13 +10649,13 @@
         <v>85</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10690,7 +10706,7 @@
         <v>85</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
@@ -10699,13 +10715,13 @@
         <v>95</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>85</v>
@@ -10720,10 +10736,10 @@
         <v>85</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>85</v>
@@ -10734,10 +10750,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10760,13 +10776,13 @@
         <v>85</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -10817,7 +10833,7 @@
         <v>85</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>83</v>
@@ -10826,31 +10842,31 @@
         <v>95</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP65" t="s" s="2">
         <v>585</v>
       </c>
-      <c r="AL65" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>580</v>
-      </c>
       <c r="AQ65" t="s" s="2">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="AR65" t="s" s="2">
         <v>85</v>
@@ -10861,10 +10877,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10890,16 +10906,16 @@
         <v>184</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>85</v>
@@ -10927,28 +10943,28 @@
         <v>119</v>
       </c>
       <c r="Y66" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF66" t="s" s="2">
         <v>592</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>587</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>83</v>
@@ -10975,13 +10991,13 @@
         <v>85</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="AR66" t="s" s="2">
         <v>85</v>
@@ -10992,10 +11008,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11021,16 +11037,16 @@
         <v>184</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>85</v>
@@ -11055,31 +11071,31 @@
         <v>85</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="Y67" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF67" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>596</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>83</v>
@@ -11106,13 +11122,13 @@
         <v>85</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="AR67" t="s" s="2">
         <v>85</v>
@@ -11123,10 +11139,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11149,17 +11165,17 @@
         <v>85</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>85</v>
@@ -11208,7 +11224,7 @@
         <v>85</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>83</v>
@@ -11241,7 +11257,7 @@
         <v>85</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>85</v>
@@ -11252,10 +11268,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11281,10 +11297,10 @@
         <v>162</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -11335,7 +11351,7 @@
         <v>85</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
@@ -11365,10 +11381,10 @@
         <v>85</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>85</v>
@@ -11379,10 +11395,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11405,16 +11421,16 @@
         <v>96</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -11464,7 +11480,7 @@
         <v>85</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>83</v>
@@ -11494,10 +11510,10 @@
         <v>85</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="AQ70" t="s" s="2">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="AR70" t="s" s="2">
         <v>85</v>
@@ -11508,10 +11524,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11534,16 +11550,16 @@
         <v>96</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -11593,7 +11609,7 @@
         <v>85</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>83</v>
@@ -11623,10 +11639,10 @@
         <v>85</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="AR71" t="s" s="2">
         <v>85</v>
@@ -11637,10 +11653,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11663,19 +11679,19 @@
         <v>96</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>85</v>
@@ -11724,7 +11740,7 @@
         <v>85</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>83</v>
@@ -11754,10 +11770,10 @@
         <v>85</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="AR72" t="s" s="2">
         <v>85</v>
@@ -11768,10 +11784,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11895,10 +11911,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12024,14 +12040,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -12053,10 +12069,10 @@
         <v>141</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>144</v>
@@ -12111,7 +12127,7 @@
         <v>85</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>83</v>
@@ -12155,10 +12171,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12184,13 +12200,13 @@
         <v>184</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="O76" t="s" s="2">
         <v>278</v>
@@ -12218,10 +12234,10 @@
         <v>85</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="Z76" t="s" s="2">
         <v>280</v>
@@ -12242,7 +12258,7 @@
         <v>85</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>95</v>
@@ -12269,7 +12285,7 @@
         <v>85</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>283</v>
@@ -12286,10 +12302,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12312,19 +12328,19 @@
         <v>96</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>643</v>
+        <v>648</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>85</v>
@@ -12373,7 +12389,7 @@
         <v>85</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>83</v>
@@ -12400,27 +12416,27 @@
         <v>85</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="AQ77" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AR77" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS77" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12446,16 +12462,16 @@
         <v>184</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>85</v>
@@ -12483,10 +12499,10 @@
         <v>189</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>85</v>
@@ -12504,7 +12520,7 @@
         <v>85</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>83</v>
@@ -12513,7 +12529,7 @@
         <v>95</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>107</v>
@@ -12537,7 +12553,7 @@
         <v>138</v>
       </c>
       <c r="AQ78" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AR78" t="s" s="2">
         <v>85</v>
@@ -12548,14 +12564,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -12577,16 +12593,16 @@
         <v>184</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>85</v>
@@ -12614,10 +12630,10 @@
         <v>189</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>85</v>
@@ -12635,7 +12651,7 @@
         <v>85</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>83</v>
@@ -12662,27 +12678,27 @@
         <v>85</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="AQ79" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="AR79" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS79" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12708,16 +12724,16 @@
         <v>86</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>85</v>
@@ -12766,7 +12782,7 @@
         <v>85</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>83</v>
@@ -12796,10 +12812,10 @@
         <v>85</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="AQ80" t="s" s="2">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="AR80" t="s" s="2">
         <v>85</v>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -243,7 +243,7 @@
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
+    <t>Mapping: Summary Document Architecure (SDA)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>
@@ -2443,7 +2443,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="251.90234375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="247.40625" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1131,8 +1131,7 @@
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
-    <t>demographics.lrdfn
-accession.collected</t>
+    <t>Patient.PatientExtension.VeteranLrdfn</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1264,7 +1263,7 @@
     <t>Chem.LabChem.LabChemSpecimenDateTime,Chem.LabPanel.LabChemSpecimenDateTime,Chem.OrderedLabPanel.LabChemSpecimenDateTime,Chem.PatientLabChem.LabChemSpecimenDateTime</t>
   </si>
   <si>
-    <t>lab.collected</t>
+    <t>LabOrder.LabTestItem.Description,LabOrder.Organization.Description</t>
   </si>
   <si>
     <t>Observation.issued</t>
@@ -1289,7 +1288,7 @@
     <t>Chem.LabChem.LabChemCompleteDateTime,Chem.LabPanel.LabChemCompleteDateTime,Chem.OrderedLabPanel.LabChemCompleteDateTime,Chem.PatientLabChem.LabChemCompleteDateTime</t>
   </si>
   <si>
-    <t>lab.resulted,lab.status</t>
+    <t>LabOrder.Result.ResultStatus,LabOrder.Result.ResultTime,LabOrder.LabResultItem.TestItemStatus</t>
   </si>
   <si>
     <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
@@ -1323,7 +1322,7 @@
     <t>Chem.LabChem.AccessionInstitutionIEN,Chem.PatientLabChem.AccessionInstitutionIEN</t>
   </si>
   <si>
-    <t>lab.facility</t>
+    <t>LabOrder.Result.VerifiedBy</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1633,7 +1632,7 @@
     <t>Chem.LabPanel.LabPanelComment</t>
   </si>
   <si>
-    <t>lab.comment</t>
+    <t>LabOrder.Result.Comments</t>
   </si>
   <si>
     <t>NTE.3 (partner NTE to OBX, or sometimes another (child?) OBX)</t>
@@ -1725,7 +1724,7 @@
     <t>Chem.LabChem.ShortAccessionNumber,Chem.PatientLabChem.ShortAccessionNumber</t>
   </si>
   <si>
-    <t>lab.groupName</t>
+    <t>LabOrder.ResultExtension.GroupName</t>
   </si>
   <si>
     <t>&lt; 123038009 |Specimen|</t>
@@ -2443,7 +2442,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="251.90234375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="91.8984375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="247.40625" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1131,7 +1131,7 @@
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
-    <t>Patient.PatientExtension.VeteranLrdfn</t>
+    <t>Patient.Extension[PatientExtension].VeteranLrdfn</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1263,7 +1263,7 @@
     <t>Chem.LabChem.LabChemSpecimenDateTime,Chem.LabPanel.LabChemSpecimenDateTime,Chem.OrderedLabPanel.LabChemSpecimenDateTime,Chem.PatientLabChem.LabChemSpecimenDateTime</t>
   </si>
   <si>
-    <t>LabOrder.LabTestItem.Description,LabOrder.Organization.Description</t>
+    <t>LabOrder.TestItemCode[LabTestItem].Description,LabOrder.PerformedAt[Organization].Description</t>
   </si>
   <si>
     <t>Observation.issued</t>
@@ -1288,7 +1288,7 @@
     <t>Chem.LabChem.LabChemCompleteDateTime,Chem.LabPanel.LabChemCompleteDateTime,Chem.OrderedLabPanel.LabChemCompleteDateTime,Chem.PatientLabChem.LabChemCompleteDateTime</t>
   </si>
   <si>
-    <t>LabOrder.Result.ResultStatus,LabOrder.Result.ResultTime,LabOrder.LabResultItem.TestItemStatus</t>
+    <t>LabOrder.Result.ResultStatus,LabOrder.Result.ResultTime,LabOrder.ResultItem[LabResultItem].TestItemStatus</t>
   </si>
   <si>
     <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
@@ -1724,7 +1724,7 @@
     <t>Chem.LabChem.ShortAccessionNumber,Chem.PatientLabChem.ShortAccessionNumber</t>
   </si>
   <si>
-    <t>LabOrder.ResultExtension.GroupName</t>
+    <t>LabOrder.Extension[ResultExtension].GroupName</t>
   </si>
   <si>
     <t>&lt; 123038009 |Specimen|</t>
@@ -2442,7 +2442,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="251.90234375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="91.8984375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="103.25" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="247.40625" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$82</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3343" uniqueCount="664">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3426" uniqueCount="672">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file CHEM, HEM, TOX, RIA, SER, etc. (63.04) to us-core-observation-lab</t>
+    <t>This StructureDefinition contains the maps for VistA file CHEM, HEM, TOX, RIA, SER, etc. (63.04) to us-core-observation-lab.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1303,7 +1303,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Organization|http://va.gov/fhir/StructureDefinition/Practitioner)
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
 </t>
   </si>
   <si>
@@ -1316,25 +1316,51 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
+    <t>Event.performer.actor</t>
+  </si>
+  <si>
+    <t>OBX.15 / (Practitioner)  OBX-16,  PRT-5:PRT-4='RO' /  (Device)  OBX-18 , PRT-10:PRT-4='EQUIP' / (Organization)  OBX-23,  PRT-8:PRT-4='PO'</t>
+  </si>
+  <si>
+    <t>participation[typeCode=PRF]</t>
+  </si>
+  <si>
+    <t>FiveWs.actor</t>
+  </si>
+  <si>
+    <t>Observation.performer:va-at</t>
+  </si>
+  <si>
+    <t>va-at</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Organization)
+</t>
+  </si>
+  <si>
+    <t>847: reference from CHEM, HEM, TOX, RIA, SER, etc. - ACCESSIONING INSTITUTION (63.04-.112)</t>
+  </si>
+  <si>
+    <t>Chem.LabChem.AccessionInstitutionIEN,Chem.PatientLabChem.AccessionInstitutionIEN</t>
+  </si>
+  <si>
+    <t>LabOrder.Result.EnteredAt</t>
+  </si>
+  <si>
+    <t>Observation.performer:va-by</t>
+  </si>
+  <si>
+    <t>va-by</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Practitioner)
+</t>
+  </si>
+  <si>
     <t>1676: reference from CHEM, HEM, TOX, RIA, SER, etc. - VERIFY PERSON (63.04-.04)</t>
   </si>
   <si>
-    <t>Chem.LabChem.AccessionInstitutionIEN,Chem.PatientLabChem.AccessionInstitutionIEN</t>
-  </si>
-  <si>
     <t>LabOrder.Result.VerifiedBy</t>
-  </si>
-  <si>
-    <t>Event.performer.actor</t>
-  </si>
-  <si>
-    <t>OBX.15 / (Practitioner)  OBX-16,  PRT-5:PRT-4='RO' /  (Device)  OBX-18 , PRT-10:PRT-4='EQUIP' / (Organization)  OBX-23,  PRT-8:PRT-4='PO'</t>
-  </si>
-  <si>
-    <t>participation[typeCode=PRF]</t>
-  </si>
-  <si>
-    <t>FiveWs.actor</t>
   </si>
   <si>
     <t>Observation.value[x]</t>
@@ -2402,7 +2428,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AS80"/>
+  <dimension ref="A1:AS82"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.1171875" customWidth="true" bestFit="true"/>
@@ -7916,7 +7942,7 @@
         <v>84</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>85</v>
@@ -7972,16 +7998,14 @@
         <v>85</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>85</v>
+        <v>171</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>412</v>
@@ -7999,28 +8023,28 @@
         <v>107</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AO43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP43" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AQ43" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="AN43" t="s" s="2">
+      <c r="AR43" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="AQ43" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="AR43" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="AS43" t="s" s="2">
         <v>85</v>
@@ -8028,12 +8052,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="C44" s="2"/>
+        <v>412</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>422</v>
+      </c>
       <c r="D44" t="s" s="2">
         <v>85</v>
       </c>
@@ -8054,19 +8080,17 @@
         <v>96</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>428</v>
-      </c>
+        <v>415</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>85</v>
@@ -8103,67 +8127,69 @@
         <v>85</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="AC44" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="AD44" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>171</v>
+        <v>85</v>
       </c>
       <c r="AF44" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK44" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="AG44" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="AL44" t="s" s="2">
-        <v>85</v>
+        <v>425</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>85</v>
+        <v>426</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>85</v>
+        <v>417</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>432</v>
+        <v>85</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>433</v>
+        <v>418</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>434</v>
+        <v>419</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>85</v>
+        <v>420</v>
       </c>
       <c r="AS44" t="s" s="2">
-        <v>435</v>
+        <v>85</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>85</v>
@@ -8185,19 +8211,17 @@
         <v>96</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>428</v>
-      </c>
+        <v>415</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>85</v>
@@ -8246,54 +8270,54 @@
         <v>85</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI45" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK45" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="AJ45" t="s" s="2">
+      <c r="AL45" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AK45" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="AN45" t="s" s="2">
-        <v>85</v>
+        <v>417</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>432</v>
+        <v>85</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>433</v>
+        <v>418</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>434</v>
+        <v>419</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>85</v>
+        <v>420</v>
       </c>
       <c r="AS45" t="s" s="2">
-        <v>435</v>
+        <v>85</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8307,25 +8331,29 @@
         <v>95</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>162</v>
+        <v>433</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>163</v>
+        <v>434</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>437</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>85</v>
       </c>
@@ -8361,19 +8389,17 @@
         <v>85</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="AC46" s="2"/>
       <c r="AD46" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>85</v>
+        <v>171</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>165</v>
+        <v>432</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>83</v>
@@ -8382,10 +8408,10 @@
         <v>95</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>85</v>
+        <v>438</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>85</v>
+        <v>439</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>85</v>
@@ -8400,61 +8426,65 @@
         <v>85</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>85</v>
+        <v>440</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>85</v>
+        <v>441</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>166</v>
+        <v>442</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS46" t="s" s="2">
-        <v>85</v>
+        <v>443</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="C47" s="2"/>
+        <v>432</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>445</v>
+      </c>
       <c r="D47" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>141</v>
+        <v>446</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>142</v>
+        <v>434</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>168</v>
+        <v>435</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>436</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>437</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>85</v>
       </c>
@@ -8490,31 +8520,31 @@
         <v>85</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>169</v>
+        <v>85</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>171</v>
+        <v>85</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>172</v>
+        <v>432</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>85</v>
+        <v>438</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>146</v>
+        <v>439</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>85</v>
@@ -8529,27 +8559,27 @@
         <v>85</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>85</v>
+        <v>440</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>85</v>
+        <v>441</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>166</v>
+        <v>442</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS47" t="s" s="2">
-        <v>85</v>
+        <v>443</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8563,29 +8593,25 @@
         <v>95</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>445</v>
+        <v>162</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>446</v>
+        <v>163</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>449</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>85</v>
       </c>
@@ -8633,7 +8659,7 @@
         <v>85</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>450</v>
+        <v>165</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
@@ -8645,10 +8671,10 @@
         <v>85</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>451</v>
+        <v>85</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>85</v>
@@ -8663,10 +8689,10 @@
         <v>85</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>452</v>
+        <v>85</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>453</v>
+        <v>166</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>85</v>
@@ -8677,50 +8703,48 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>456</v>
+        <v>142</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" t="s" s="2">
-        <v>458</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="Q49" t="s" s="2">
-        <v>459</v>
-      </c>
+      <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
         <v>85</v>
       </c>
@@ -8740,43 +8764,43 @@
         <v>85</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>178</v>
+        <v>85</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>460</v>
+        <v>85</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>461</v>
+        <v>85</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>85</v>
+        <v>169</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>85</v>
+        <v>171</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>462</v>
+        <v>172</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>85</v>
@@ -8794,10 +8818,10 @@
         <v>85</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>463</v>
+        <v>85</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>464</v>
+        <v>166</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>85</v>
@@ -8808,10 +8832,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>465</v>
+        <v>451</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>466</v>
+        <v>452</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8834,17 +8858,19 @@
         <v>96</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>162</v>
+        <v>453</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>455</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>456</v>
+      </c>
       <c r="O50" t="s" s="2">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>85</v>
@@ -8893,7 +8919,7 @@
         <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -8908,7 +8934,7 @@
         <v>107</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>85</v>
@@ -8923,10 +8949,10 @@
         <v>85</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>85</v>
@@ -8937,10 +8963,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8957,28 +8983,30 @@
         <v>85</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J51" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="Q51" s="2"/>
+      <c r="Q51" t="s" s="2">
+        <v>467</v>
+      </c>
       <c r="R51" t="s" s="2">
         <v>85</v>
       </c>
@@ -8998,13 +9026,13 @@
         <v>85</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>85</v>
+        <v>178</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>85</v>
+        <v>468</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>85</v>
+        <v>469</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>85</v>
@@ -9022,7 +9050,7 @@
         <v>85</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -9031,7 +9059,7 @@
         <v>95</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>480</v>
+        <v>85</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>107</v>
@@ -9052,10 +9080,10 @@
         <v>85</v>
       </c>
       <c r="AP51" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AQ51" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="AQ51" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>85</v>
@@ -9066,10 +9094,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9083,7 +9111,7 @@
         <v>95</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>85</v>
@@ -9092,19 +9120,17 @@
         <v>96</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>115</v>
+        <v>162</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>486</v>
-      </c>
+        <v>476</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>85</v>
@@ -9153,7 +9179,7 @@
         <v>85</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
@@ -9168,7 +9194,7 @@
         <v>107</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>85</v>
+        <v>479</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>85</v>
@@ -9183,10 +9209,10 @@
         <v>85</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>85</v>
@@ -9197,10 +9223,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9214,28 +9240,26 @@
         <v>95</v>
       </c>
       <c r="H53" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J53" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="I53" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="K53" t="s" s="2">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>493</v>
-      </c>
+        <v>485</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>85</v>
@@ -9260,11 +9284,13 @@
         <v>85</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="Y53" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="Z53" t="s" s="2">
-        <v>495</v>
+        <v>85</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>85</v>
@@ -9282,7 +9308,7 @@
         <v>85</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -9291,13 +9317,13 @@
         <v>95</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>497</v>
+        <v>85</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>85</v>
@@ -9312,10 +9338,10 @@
         <v>85</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>138</v>
+        <v>480</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>85</v>
@@ -9326,45 +9352,45 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H54" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J54" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="I54" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J54" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="K54" t="s" s="2">
-        <v>184</v>
+        <v>115</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>85</v>
@@ -9389,11 +9415,13 @@
         <v>85</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="Y54" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="Z54" t="s" s="2">
-        <v>505</v>
+        <v>85</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>85</v>
@@ -9411,13 +9439,13 @@
         <v>85</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>85</v>
@@ -9426,7 +9454,7 @@
         <v>107</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>506</v>
+        <v>85</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>85</v>
@@ -9438,27 +9466,27 @@
         <v>85</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>507</v>
+        <v>85</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>508</v>
+        <v>480</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS54" t="s" s="2">
-        <v>510</v>
+        <v>85</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>511</v>
+        <v>498</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>511</v>
+        <v>498</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9469,7 +9497,7 @@
         <v>83</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>96</v>
@@ -9481,19 +9509,19 @@
         <v>85</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>512</v>
+        <v>184</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>513</v>
+        <v>499</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>514</v>
+        <v>500</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>515</v>
+        <v>501</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>516</v>
+        <v>502</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>85</v>
@@ -9518,13 +9546,11 @@
         <v>85</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>85</v>
+        <v>503</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>85</v>
@@ -9542,28 +9568,28 @@
         <v>85</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>511</v>
+        <v>498</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>85</v>
+        <v>504</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>518</v>
+        <v>85</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>519</v>
+        <v>85</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>85</v>
@@ -9572,10 +9598,10 @@
         <v>85</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>520</v>
+        <v>138</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>521</v>
+        <v>506</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>85</v>
@@ -9586,24 +9612,24 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>522</v>
+        <v>507</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>522</v>
+        <v>507</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>85</v>
+        <v>508</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>85</v>
@@ -9615,15 +9641,17 @@
         <v>184</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>523</v>
+        <v>509</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>524</v>
+        <v>510</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>511</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>512</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>85</v>
       </c>
@@ -9647,13 +9675,11 @@
         <v>85</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>527</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>528</v>
+        <v>513</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>85</v>
@@ -9671,13 +9697,13 @@
         <v>85</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>522</v>
+        <v>507</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>85</v>
@@ -9686,7 +9712,7 @@
         <v>107</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>85</v>
+        <v>514</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>85</v>
@@ -9698,27 +9724,27 @@
         <v>85</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>529</v>
+        <v>515</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>530</v>
+        <v>516</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>531</v>
+        <v>517</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS56" t="s" s="2">
-        <v>532</v>
+        <v>518</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>533</v>
+        <v>519</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>533</v>
+        <v>519</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9729,10 +9755,10 @@
         <v>83</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>85</v>
@@ -9741,19 +9767,19 @@
         <v>85</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>184</v>
+        <v>520</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>534</v>
+        <v>521</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>537</v>
+        <v>524</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>85</v>
@@ -9778,13 +9804,13 @@
         <v>85</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>526</v>
+        <v>85</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>538</v>
+        <v>85</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>539</v>
+        <v>85</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>85</v>
@@ -9802,13 +9828,13 @@
         <v>85</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>533</v>
+        <v>519</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>85</v>
@@ -9817,13 +9843,13 @@
         <v>107</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>85</v>
+        <v>525</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>85</v>
+        <v>526</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>85</v>
+        <v>527</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>85</v>
@@ -9832,10 +9858,10 @@
         <v>85</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>540</v>
+        <v>528</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>85</v>
@@ -9846,10 +9872,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9863,7 +9889,7 @@
         <v>95</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>85</v>
@@ -9872,16 +9898,16 @@
         <v>85</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>543</v>
+        <v>184</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>544</v>
+        <v>531</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>545</v>
+        <v>532</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>546</v>
+        <v>533</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9907,13 +9933,13 @@
         <v>85</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>85</v>
+        <v>534</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>85</v>
+        <v>535</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>85</v>
+        <v>536</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>85</v>
@@ -9931,7 +9957,7 @@
         <v>85</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
@@ -9946,39 +9972,39 @@
         <v>107</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>547</v>
+        <v>85</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>548</v>
+        <v>85</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>549</v>
+        <v>85</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>550</v>
+        <v>537</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>551</v>
+        <v>538</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>552</v>
+        <v>539</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS58" t="s" s="2">
-        <v>553</v>
+        <v>540</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>554</v>
+        <v>541</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>554</v>
+        <v>541</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10001,18 +10027,20 @@
         <v>85</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>555</v>
+        <v>184</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>557</v>
+        <v>543</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>544</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>545</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>85</v>
       </c>
@@ -10036,13 +10064,13 @@
         <v>85</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>85</v>
+        <v>534</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>85</v>
+        <v>546</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>85</v>
+        <v>547</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>85</v>
@@ -10060,7 +10088,7 @@
         <v>85</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>554</v>
+        <v>541</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
@@ -10087,27 +10115,27 @@
         <v>85</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>559</v>
+        <v>85</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>560</v>
+        <v>548</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>561</v>
+        <v>549</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS59" t="s" s="2">
-        <v>562</v>
+        <v>85</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>563</v>
+        <v>550</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>563</v>
+        <v>550</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10118,10 +10146,10 @@
         <v>83</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>85</v>
@@ -10130,20 +10158,18 @@
         <v>85</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>564</v>
+        <v>551</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>568</v>
-      </c>
+        <v>554</v>
+      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>85</v>
       </c>
@@ -10191,54 +10217,54 @@
         <v>85</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>563</v>
+        <v>550</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>569</v>
+        <v>107</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>85</v>
+        <v>555</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>85</v>
+        <v>556</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>85</v>
+        <v>557</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>85</v>
+        <v>558</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>570</v>
+        <v>559</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS60" t="s" s="2">
-        <v>85</v>
+        <v>561</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10261,15 +10287,17 @@
         <v>85</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>162</v>
+        <v>563</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>163</v>
+        <v>564</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>565</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>566</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>85</v>
@@ -10318,7 +10346,7 @@
         <v>85</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>165</v>
+        <v>562</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
@@ -10330,7 +10358,7 @@
         <v>85</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>85</v>
@@ -10345,31 +10373,31 @@
         <v>85</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>85</v>
+        <v>567</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>85</v>
+        <v>568</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>166</v>
+        <v>569</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS61" t="s" s="2">
-        <v>85</v>
+        <v>570</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -10388,18 +10416,20 @@
         <v>85</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>141</v>
+        <v>572</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>142</v>
+        <v>573</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>168</v>
+        <v>574</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>575</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>576</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>85</v>
       </c>
@@ -10447,7 +10477,7 @@
         <v>85</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>172</v>
+        <v>571</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
@@ -10459,7 +10489,7 @@
         <v>85</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>146</v>
+        <v>577</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>85</v>
@@ -10477,10 +10507,10 @@
         <v>85</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>85</v>
+        <v>578</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>166</v>
+        <v>579</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>85</v>
@@ -10491,46 +10521,42 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>575</v>
+        <v>85</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>576</v>
+        <v>163</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>85</v>
       </c>
@@ -10578,19 +10604,19 @@
         <v>85</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>578</v>
+        <v>165</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>85</v>
@@ -10611,7 +10637,7 @@
         <v>85</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>85</v>
@@ -10622,24 +10648,24 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>85</v>
@@ -10648,15 +10674,17 @@
         <v>85</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>580</v>
+        <v>141</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>581</v>
+        <v>142</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>85</v>
@@ -10705,22 +10733,22 @@
         <v>85</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>579</v>
+        <v>172</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>583</v>
+        <v>85</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>584</v>
+        <v>85</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>85</v>
@@ -10735,10 +10763,10 @@
         <v>85</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>585</v>
+        <v>85</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>586</v>
+        <v>166</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>85</v>
@@ -10749,42 +10777,46 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>85</v>
+        <v>583</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H65" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I65" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="I65" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="J65" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>580</v>
+        <v>141</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
+        <v>585</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>85</v>
       </c>
@@ -10832,22 +10864,22 @@
         <v>85</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>583</v>
+        <v>85</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>590</v>
+        <v>85</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>85</v>
@@ -10862,10 +10894,10 @@
         <v>85</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>585</v>
+        <v>85</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>591</v>
+        <v>138</v>
       </c>
       <c r="AR65" t="s" s="2">
         <v>85</v>
@@ -10876,10 +10908,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10893,7 +10925,7 @@
         <v>95</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>85</v>
@@ -10902,20 +10934,16 @@
         <v>85</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>184</v>
+        <v>588</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>596</v>
-      </c>
+        <v>590</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>85</v>
       </c>
@@ -10939,13 +10967,13 @@
         <v>85</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>597</v>
+        <v>85</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>598</v>
+        <v>85</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>85</v>
@@ -10963,7 +10991,7 @@
         <v>85</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>83</v>
@@ -10972,13 +11000,13 @@
         <v>95</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>85</v>
+        <v>591</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>85</v>
+        <v>592</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>85</v>
@@ -10990,13 +11018,13 @@
         <v>85</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>599</v>
+        <v>85</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>509</v>
+        <v>594</v>
       </c>
       <c r="AR66" t="s" s="2">
         <v>85</v>
@@ -11007,10 +11035,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11021,10 +11049,10 @@
         <v>83</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>85</v>
@@ -11033,20 +11061,16 @@
         <v>85</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>184</v>
+        <v>588</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>605</v>
-      </c>
+        <v>597</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>85</v>
       </c>
@@ -11070,13 +11094,13 @@
         <v>85</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>526</v>
+        <v>85</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>606</v>
+        <v>85</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>607</v>
+        <v>85</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>85</v>
@@ -11094,22 +11118,22 @@
         <v>85</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>85</v>
+        <v>591</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>85</v>
+        <v>598</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>85</v>
@@ -11121,13 +11145,13 @@
         <v>85</v>
       </c>
       <c r="AO67" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="AQ67" t="s" s="2">
         <v>599</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="AQ67" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="AR67" t="s" s="2">
         <v>85</v>
@@ -11138,10 +11162,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11164,17 +11188,19 @@
         <v>85</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>609</v>
+        <v>184</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>602</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>603</v>
+      </c>
       <c r="O68" t="s" s="2">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>85</v>
@@ -11199,13 +11225,13 @@
         <v>85</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>85</v>
+        <v>605</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>85</v>
+        <v>606</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>85</v>
@@ -11223,7 +11249,7 @@
         <v>85</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>83</v>
@@ -11250,13 +11276,13 @@
         <v>85</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>85</v>
+        <v>607</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>85</v>
+        <v>608</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>613</v>
+        <v>517</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>85</v>
@@ -11267,10 +11293,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11281,7 +11307,7 @@
         <v>83</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>85</v>
@@ -11293,16 +11319,20 @@
         <v>85</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
+        <v>611</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>613</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>85</v>
       </c>
@@ -11326,13 +11356,13 @@
         <v>85</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>85</v>
+        <v>534</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>85</v>
+        <v>614</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>85</v>
+        <v>615</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>85</v>
@@ -11350,13 +11380,13 @@
         <v>85</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>85</v>
@@ -11377,13 +11407,13 @@
         <v>85</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>85</v>
+        <v>607</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>585</v>
+        <v>608</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>617</v>
+        <v>517</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>85</v>
@@ -11394,10 +11424,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11408,7 +11438,7 @@
         <v>83</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>85</v>
@@ -11417,21 +11447,21 @@
         <v>85</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>619</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="N70" s="2"/>
+      <c r="O70" t="s" s="2">
         <v>620</v>
       </c>
-      <c r="M70" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>85</v>
       </c>
@@ -11479,13 +11509,13 @@
         <v>85</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>85</v>
@@ -11509,10 +11539,10 @@
         <v>85</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>623</v>
+        <v>85</v>
       </c>
       <c r="AQ70" t="s" s="2">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="AR70" t="s" s="2">
         <v>85</v>
@@ -11523,10 +11553,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11537,7 +11567,7 @@
         <v>83</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>85</v>
@@ -11546,20 +11576,18 @@
         <v>85</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>626</v>
+        <v>162</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>629</v>
-      </c>
+        <v>624</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>85</v>
@@ -11608,13 +11636,13 @@
         <v>85</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>85</v>
@@ -11638,10 +11666,10 @@
         <v>85</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>623</v>
+        <v>593</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="AR71" t="s" s="2">
         <v>85</v>
@@ -11652,10 +11680,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11678,20 +11706,18 @@
         <v>96</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>564</v>
+        <v>627</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>635</v>
-      </c>
+        <v>630</v>
+      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>85</v>
       </c>
@@ -11739,7 +11765,7 @@
         <v>85</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>83</v>
@@ -11769,10 +11795,10 @@
         <v>85</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="AR72" t="s" s="2">
         <v>85</v>
@@ -11783,10 +11809,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11797,7 +11823,7 @@
         <v>83</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>85</v>
@@ -11806,18 +11832,20 @@
         <v>85</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>162</v>
+        <v>634</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>163</v>
+        <v>635</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>636</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>637</v>
+      </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>85</v>
@@ -11866,19 +11894,19 @@
         <v>85</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>165</v>
+        <v>633</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>85</v>
@@ -11896,10 +11924,10 @@
         <v>85</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>85</v>
+        <v>631</v>
       </c>
       <c r="AQ73" t="s" s="2">
-        <v>166</v>
+        <v>638</v>
       </c>
       <c r="AR73" t="s" s="2">
         <v>85</v>
@@ -11917,7 +11945,7 @@
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11933,21 +11961,23 @@
         <v>85</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>141</v>
+        <v>572</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>142</v>
+        <v>640</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>168</v>
+        <v>641</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O74" s="2"/>
+        <v>642</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>643</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>85</v>
       </c>
@@ -11995,7 +12025,7 @@
         <v>85</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>172</v>
+        <v>639</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>83</v>
@@ -12007,7 +12037,7 @@
         <v>85</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>85</v>
@@ -12025,10 +12055,10 @@
         <v>85</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>85</v>
+        <v>644</v>
       </c>
       <c r="AQ74" t="s" s="2">
-        <v>166</v>
+        <v>645</v>
       </c>
       <c r="AR74" t="s" s="2">
         <v>85</v>
@@ -12039,46 +12069,42 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>575</v>
+        <v>85</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>576</v>
+        <v>163</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>85</v>
       </c>
@@ -12126,19 +12152,19 @@
         <v>85</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>578</v>
+        <v>165</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>85</v>
@@ -12159,7 +12185,7 @@
         <v>85</v>
       </c>
       <c r="AQ75" t="s" s="2">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="AR75" t="s" s="2">
         <v>85</v>
@@ -12170,21 +12196,21 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>85</v>
@@ -12193,23 +12219,21 @@
         <v>85</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>184</v>
+        <v>141</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>642</v>
+        <v>142</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>643</v>
+        <v>168</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>278</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>85</v>
       </c>
@@ -12233,13 +12257,13 @@
         <v>85</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>526</v>
+        <v>85</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>645</v>
+        <v>85</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>280</v>
+        <v>85</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>85</v>
@@ -12257,19 +12281,19 @@
         <v>85</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>641</v>
+        <v>172</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>85</v>
@@ -12284,16 +12308,16 @@
         <v>85</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>646</v>
+        <v>85</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>283</v>
+        <v>85</v>
       </c>
       <c r="AQ76" t="s" s="2">
-        <v>284</v>
+        <v>166</v>
       </c>
       <c r="AR76" t="s" s="2">
-        <v>285</v>
+        <v>85</v>
       </c>
       <c r="AS76" t="s" s="2">
         <v>85</v>
@@ -12301,45 +12325,45 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>85</v>
+        <v>583</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J77" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>425</v>
+        <v>141</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>648</v>
+        <v>584</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>649</v>
+        <v>585</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>650</v>
+        <v>144</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>429</v>
+        <v>150</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>85</v>
@@ -12388,19 +12412,19 @@
         <v>85</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>647</v>
+        <v>586</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>85</v>
@@ -12415,27 +12439,27 @@
         <v>85</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>651</v>
+        <v>85</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>433</v>
+        <v>85</v>
       </c>
       <c r="AQ77" t="s" s="2">
-        <v>434</v>
+        <v>138</v>
       </c>
       <c r="AR77" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS77" t="s" s="2">
-        <v>435</v>
+        <v>85</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12443,7 +12467,7 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G78" t="s" s="2">
         <v>95</v>
@@ -12455,22 +12479,22 @@
         <v>85</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K78" t="s" s="2">
         <v>184</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>494</v>
+        <v>278</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>85</v>
@@ -12495,13 +12519,13 @@
         <v>85</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>189</v>
+        <v>534</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>495</v>
+        <v>280</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>85</v>
@@ -12519,16 +12543,16 @@
         <v>85</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH78" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>657</v>
+        <v>85</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>107</v>
@@ -12546,16 +12570,16 @@
         <v>85</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>85</v>
+        <v>654</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>138</v>
+        <v>283</v>
       </c>
       <c r="AQ78" t="s" s="2">
-        <v>498</v>
+        <v>284</v>
       </c>
       <c r="AR78" t="s" s="2">
-        <v>85</v>
+        <v>285</v>
       </c>
       <c r="AS78" t="s" s="2">
         <v>85</v>
@@ -12563,21 +12587,21 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>85</v>
@@ -12586,22 +12610,22 @@
         <v>85</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>184</v>
+        <v>433</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>501</v>
+        <v>656</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>502</v>
+        <v>657</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>503</v>
+        <v>658</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>504</v>
+        <v>437</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>85</v>
@@ -12626,13 +12650,13 @@
         <v>85</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>189</v>
+        <v>85</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>659</v>
+        <v>85</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>660</v>
+        <v>85</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>85</v>
@@ -12650,13 +12674,13 @@
         <v>85</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>85</v>
@@ -12677,27 +12701,27 @@
         <v>85</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>507</v>
+        <v>659</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>508</v>
+        <v>441</v>
       </c>
       <c r="AQ79" t="s" s="2">
-        <v>509</v>
+        <v>442</v>
       </c>
       <c r="AR79" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS79" t="s" s="2">
-        <v>510</v>
+        <v>443</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12708,7 +12732,7 @@
         <v>83</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>85</v>
@@ -12720,19 +12744,19 @@
         <v>85</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>86</v>
+        <v>184</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>662</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>663</v>
       </c>
-      <c r="N80" t="s" s="2">
-        <v>567</v>
-      </c>
       <c r="O80" t="s" s="2">
-        <v>568</v>
+        <v>502</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>85</v>
@@ -12757,13 +12781,13 @@
         <v>85</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>85</v>
+        <v>664</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>85</v>
+        <v>503</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>85</v>
@@ -12781,16 +12805,16 @@
         <v>85</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>85</v>
+        <v>665</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>107</v>
@@ -12811,20 +12835,282 @@
         <v>85</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>570</v>
+        <v>138</v>
       </c>
       <c r="AQ80" t="s" s="2">
-        <v>571</v>
+        <v>506</v>
       </c>
       <c r="AR80" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS80" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="P81" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO81" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AP81" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="AQ81" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AR81" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS81" t="s" s="2">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="82" hidden="true">
+      <c r="A82" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="P82" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO82" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP82" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AQ82" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="AR82" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS82" t="s" s="2">
         <v>85</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS80">
+  <autoFilter ref="A1:AS82">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12834,7 +13120,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI79">
+  <conditionalFormatting sqref="A2:AI81">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$84</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3426" uniqueCount="672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3512" uniqueCount="679">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1316,6 +1316,10 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:$this}
+</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -1565,6 +1569,24 @@
   </si>
   <si>
     <t>PQ.code, MO.currency, PQ.translation.code</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>2054: target not supported</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueString</t>
+  </si>
+  <si>
+    <t>valueString</t>
+  </si>
+  <si>
+    <t>2055: target not supported</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -2428,12 +2450,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AS82"/>
+  <dimension ref="A1:AS84"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.1171875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="17.96484375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -7998,7 +8020,7 @@
         <v>85</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>267</v>
+        <v>417</v>
       </c>
       <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
@@ -8032,19 +8054,19 @@
         <v>85</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AS43" t="s" s="2">
         <v>85</v>
@@ -8052,13 +8074,13 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>412</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>85</v>
@@ -8080,7 +8102,7 @@
         <v>96</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L44" t="s" s="2">
         <v>414</v>
@@ -8154,28 +8176,28 @@
         <v>107</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AS44" t="s" s="2">
         <v>85</v>
@@ -8183,13 +8205,13 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>412</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>85</v>
@@ -8211,7 +8233,7 @@
         <v>96</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L45" t="s" s="2">
         <v>414</v>
@@ -8285,28 +8307,28 @@
         <v>107</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AS45" t="s" s="2">
         <v>85</v>
@@ -8314,10 +8336,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8340,19 +8362,19 @@
         <v>96</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>85</v>
@@ -8399,7 +8421,7 @@
         <v>171</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>83</v>
@@ -8408,10 +8430,10 @@
         <v>95</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>85</v>
@@ -8426,30 +8448,30 @@
         <v>85</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS46" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>85</v>
@@ -8471,19 +8493,19 @@
         <v>96</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>85</v>
@@ -8532,7 +8554,7 @@
         <v>85</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
@@ -8541,10 +8563,10 @@
         <v>95</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>85</v>
@@ -8559,27 +8581,27 @@
         <v>85</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS47" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8703,10 +8725,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8832,10 +8854,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8858,19 +8880,19 @@
         <v>96</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>85</v>
@@ -8919,7 +8941,7 @@
         <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -8934,7 +8956,7 @@
         <v>107</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>85</v>
@@ -8949,10 +8971,10 @@
         <v>85</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>85</v>
@@ -8963,10 +8985,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8992,20 +9014,20 @@
         <v>115</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q51" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="R51" t="s" s="2">
         <v>85</v>
@@ -9029,10 +9051,10 @@
         <v>178</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>85</v>
@@ -9050,7 +9072,7 @@
         <v>85</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -9080,10 +9102,10 @@
         <v>85</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>85</v>
@@ -9094,10 +9116,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9123,14 +9145,14 @@
         <v>162</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>85</v>
@@ -9179,7 +9201,7 @@
         <v>85</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
@@ -9194,7 +9216,7 @@
         <v>107</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>85</v>
@@ -9209,10 +9231,10 @@
         <v>85</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>85</v>
@@ -9223,10 +9245,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9252,14 +9274,14 @@
         <v>109</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>85</v>
@@ -9308,7 +9330,7 @@
         <v>85</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -9317,7 +9339,7 @@
         <v>95</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>107</v>
@@ -9338,10 +9360,10 @@
         <v>85</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>85</v>
@@ -9352,10 +9374,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9381,16 +9403,16 @@
         <v>115</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>85</v>
@@ -9439,7 +9461,7 @@
         <v>85</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -9469,10 +9491,10 @@
         <v>85</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>85</v>
@@ -9483,12 +9505,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="C55" s="2"/>
+        <v>433</v>
+      </c>
+      <c r="C55" t="s" s="2">
+        <v>500</v>
+      </c>
       <c r="D55" t="s" s="2">
         <v>85</v>
       </c>
@@ -9506,22 +9530,22 @@
         <v>85</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K55" t="s" s="2">
         <v>184</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>499</v>
+        <v>435</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>500</v>
+        <v>436</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>501</v>
+        <v>437</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>502</v>
+        <v>438</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>85</v>
@@ -9546,11 +9570,13 @@
         <v>85</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="Y55" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="Z55" t="s" s="2">
-        <v>503</v>
+        <v>85</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>85</v>
@@ -9568,7 +9594,7 @@
         <v>85</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>498</v>
+        <v>433</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -9577,13 +9603,13 @@
         <v>95</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>504</v>
+        <v>439</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>107</v>
+        <v>440</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>85</v>
@@ -9595,38 +9621,40 @@
         <v>85</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>85</v>
+        <v>441</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>138</v>
+        <v>442</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>506</v>
+        <v>443</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS55" t="s" s="2">
-        <v>85</v>
+        <v>444</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="C56" s="2"/>
+        <v>433</v>
+      </c>
+      <c r="C56" t="s" s="2">
+        <v>503</v>
+      </c>
       <c r="D56" t="s" s="2">
-        <v>508</v>
+        <v>85</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>96</v>
@@ -9635,22 +9663,22 @@
         <v>85</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>509</v>
+        <v>435</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>510</v>
+        <v>436</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>511</v>
+        <v>437</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>512</v>
+        <v>438</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>85</v>
@@ -9675,11 +9703,13 @@
         <v>85</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="Y56" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="Z56" t="s" s="2">
-        <v>513</v>
+        <v>85</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>85</v>
@@ -9697,22 +9727,22 @@
         <v>85</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>507</v>
+        <v>433</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>85</v>
+        <v>439</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>107</v>
+        <v>440</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>85</v>
@@ -9724,27 +9754,27 @@
         <v>85</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>515</v>
+        <v>441</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>516</v>
+        <v>442</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>517</v>
+        <v>443</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS56" t="s" s="2">
-        <v>518</v>
+        <v>444</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>519</v>
+        <v>505</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>519</v>
+        <v>505</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9755,7 +9785,7 @@
         <v>83</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>96</v>
@@ -9767,19 +9797,19 @@
         <v>85</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>520</v>
+        <v>184</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>521</v>
+        <v>506</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>522</v>
+        <v>507</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>523</v>
+        <v>508</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>524</v>
+        <v>509</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>85</v>
@@ -9804,13 +9834,11 @@
         <v>85</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>85</v>
+        <v>510</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>85</v>
@@ -9828,28 +9856,28 @@
         <v>85</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>519</v>
+        <v>505</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>85</v>
+        <v>511</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>525</v>
+        <v>512</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>526</v>
+        <v>85</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>527</v>
+        <v>85</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>85</v>
@@ -9858,10 +9886,10 @@
         <v>85</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>528</v>
+        <v>138</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>529</v>
+        <v>513</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>85</v>
@@ -9872,24 +9900,24 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>530</v>
+        <v>514</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>530</v>
+        <v>514</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>85</v>
+        <v>515</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>85</v>
@@ -9901,15 +9929,17 @@
         <v>184</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>531</v>
+        <v>516</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>532</v>
+        <v>517</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="O58" s="2"/>
+        <v>518</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>519</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>85</v>
       </c>
@@ -9933,13 +9963,11 @@
         <v>85</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>535</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="Y58" s="2"/>
       <c r="Z58" t="s" s="2">
-        <v>536</v>
+        <v>520</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>85</v>
@@ -9957,13 +9985,13 @@
         <v>85</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>530</v>
+        <v>514</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>85</v>
@@ -9972,7 +10000,7 @@
         <v>107</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>85</v>
+        <v>521</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>85</v>
@@ -9984,27 +10012,27 @@
         <v>85</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>537</v>
+        <v>522</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>539</v>
+        <v>524</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS58" t="s" s="2">
-        <v>540</v>
+        <v>525</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>541</v>
+        <v>526</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>541</v>
+        <v>526</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10015,10 +10043,10 @@
         <v>83</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>85</v>
@@ -10027,19 +10055,19 @@
         <v>85</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>184</v>
+        <v>527</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>542</v>
+        <v>528</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>543</v>
+        <v>529</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>544</v>
+        <v>530</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>545</v>
+        <v>531</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>85</v>
@@ -10064,13 +10092,13 @@
         <v>85</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>534</v>
+        <v>85</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>546</v>
+        <v>85</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>547</v>
+        <v>85</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>85</v>
@@ -10088,13 +10116,13 @@
         <v>85</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>541</v>
+        <v>526</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>85</v>
@@ -10103,13 +10131,13 @@
         <v>107</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>85</v>
+        <v>532</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>85</v>
+        <v>533</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>85</v>
+        <v>534</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>85</v>
@@ -10118,10 +10146,10 @@
         <v>85</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>548</v>
+        <v>535</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>549</v>
+        <v>536</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>85</v>
@@ -10132,10 +10160,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>550</v>
+        <v>537</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>550</v>
+        <v>537</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10149,7 +10177,7 @@
         <v>95</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>85</v>
@@ -10158,16 +10186,16 @@
         <v>85</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>551</v>
+        <v>184</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>552</v>
+        <v>538</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>553</v>
+        <v>539</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>554</v>
+        <v>540</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -10193,13 +10221,13 @@
         <v>85</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>85</v>
+        <v>541</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>85</v>
+        <v>542</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>85</v>
+        <v>543</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>85</v>
@@ -10217,7 +10245,7 @@
         <v>85</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>550</v>
+        <v>537</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
@@ -10232,39 +10260,39 @@
         <v>107</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>555</v>
+        <v>85</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>556</v>
+        <v>85</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>557</v>
+        <v>85</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>559</v>
+        <v>545</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>560</v>
+        <v>546</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS60" t="s" s="2">
-        <v>561</v>
+        <v>547</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>562</v>
+        <v>548</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>562</v>
+        <v>548</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10287,18 +10315,20 @@
         <v>85</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>563</v>
+        <v>184</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>564</v>
+        <v>549</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>565</v>
+        <v>550</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="O61" s="2"/>
+        <v>551</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>552</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>85</v>
       </c>
@@ -10322,13 +10352,13 @@
         <v>85</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>85</v>
+        <v>541</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>85</v>
+        <v>553</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>85</v>
+        <v>554</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>85</v>
@@ -10346,7 +10376,7 @@
         <v>85</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>562</v>
+        <v>548</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
@@ -10373,27 +10403,27 @@
         <v>85</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>567</v>
+        <v>85</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>568</v>
+        <v>555</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>569</v>
+        <v>556</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS61" t="s" s="2">
-        <v>570</v>
+        <v>85</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>571</v>
+        <v>557</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>571</v>
+        <v>557</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10404,10 +10434,10 @@
         <v>83</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>85</v>
@@ -10416,20 +10446,18 @@
         <v>85</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>572</v>
+        <v>558</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>573</v>
+        <v>559</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>576</v>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>85</v>
       </c>
@@ -10477,54 +10505,54 @@
         <v>85</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>571</v>
+        <v>557</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>577</v>
+        <v>107</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>85</v>
+        <v>562</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>85</v>
+        <v>563</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>85</v>
+        <v>564</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>85</v>
+        <v>565</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS62" t="s" s="2">
-        <v>85</v>
+        <v>568</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>580</v>
+        <v>569</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>580</v>
+        <v>569</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10547,15 +10575,17 @@
         <v>85</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>162</v>
+        <v>570</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>163</v>
+        <v>571</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>572</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>573</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>85</v>
@@ -10604,7 +10634,7 @@
         <v>85</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>165</v>
+        <v>569</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -10616,7 +10646,7 @@
         <v>85</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>85</v>
@@ -10631,31 +10661,31 @@
         <v>85</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>85</v>
+        <v>574</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>85</v>
+        <v>575</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>166</v>
+        <v>576</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS63" t="s" s="2">
-        <v>85</v>
+        <v>577</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -10674,18 +10704,20 @@
         <v>85</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>141</v>
+        <v>579</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>142</v>
+        <v>580</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>168</v>
+        <v>581</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O64" s="2"/>
+        <v>582</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>583</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>85</v>
       </c>
@@ -10733,7 +10765,7 @@
         <v>85</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>172</v>
+        <v>578</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
@@ -10745,7 +10777,7 @@
         <v>85</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>146</v>
+        <v>584</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>85</v>
@@ -10763,10 +10795,10 @@
         <v>85</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>85</v>
+        <v>585</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>166</v>
+        <v>586</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>85</v>
@@ -10777,46 +10809,42 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>583</v>
+        <v>85</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>584</v>
+        <v>163</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>85</v>
       </c>
@@ -10864,19 +10892,19 @@
         <v>85</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>586</v>
+        <v>165</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>85</v>
@@ -10897,7 +10925,7 @@
         <v>85</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="AR65" t="s" s="2">
         <v>85</v>
@@ -10908,24 +10936,24 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>85</v>
@@ -10934,15 +10962,17 @@
         <v>85</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>588</v>
+        <v>141</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>589</v>
+        <v>142</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>85</v>
@@ -10991,22 +11021,22 @@
         <v>85</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>587</v>
+        <v>172</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>591</v>
+        <v>85</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>592</v>
+        <v>85</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>85</v>
@@ -11021,10 +11051,10 @@
         <v>85</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>593</v>
+        <v>85</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>594</v>
+        <v>166</v>
       </c>
       <c r="AR66" t="s" s="2">
         <v>85</v>
@@ -11035,42 +11065,46 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>85</v>
+        <v>590</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H67" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I67" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="I67" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="J67" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>588</v>
+        <v>141</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
+        <v>592</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>85</v>
       </c>
@@ -11118,22 +11152,22 @@
         <v>85</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>591</v>
+        <v>85</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>598</v>
+        <v>85</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>85</v>
@@ -11148,10 +11182,10 @@
         <v>85</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>593</v>
+        <v>85</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>599</v>
+        <v>138</v>
       </c>
       <c r="AR67" t="s" s="2">
         <v>85</v>
@@ -11162,10 +11196,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11179,7 +11213,7 @@
         <v>95</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>85</v>
@@ -11188,20 +11222,16 @@
         <v>85</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>184</v>
+        <v>595</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>604</v>
-      </c>
+        <v>597</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>85</v>
       </c>
@@ -11225,13 +11255,13 @@
         <v>85</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>605</v>
+        <v>85</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>606</v>
+        <v>85</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>85</v>
@@ -11249,7 +11279,7 @@
         <v>85</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>83</v>
@@ -11258,13 +11288,13 @@
         <v>95</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>85</v>
+        <v>598</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>85</v>
+        <v>599</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>85</v>
@@ -11276,13 +11306,13 @@
         <v>85</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>607</v>
+        <v>85</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>517</v>
+        <v>601</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>85</v>
@@ -11293,10 +11323,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11307,10 +11337,10 @@
         <v>83</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>85</v>
@@ -11319,20 +11349,16 @@
         <v>85</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>184</v>
+        <v>595</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>613</v>
-      </c>
+        <v>604</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>85</v>
       </c>
@@ -11356,13 +11382,13 @@
         <v>85</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>534</v>
+        <v>85</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>614</v>
+        <v>85</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>615</v>
+        <v>85</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>85</v>
@@ -11380,22 +11406,22 @@
         <v>85</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>85</v>
+        <v>598</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>85</v>
+        <v>605</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>85</v>
@@ -11407,13 +11433,13 @@
         <v>85</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>607</v>
+        <v>85</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>517</v>
+        <v>606</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>85</v>
@@ -11424,10 +11450,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11450,17 +11476,19 @@
         <v>85</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>617</v>
+        <v>184</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>618</v>
+        <v>608</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>609</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>610</v>
+      </c>
       <c r="O70" t="s" s="2">
-        <v>620</v>
+        <v>611</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>85</v>
@@ -11485,13 +11513,13 @@
         <v>85</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>85</v>
+        <v>612</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>85</v>
+        <v>613</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>85</v>
@@ -11509,7 +11537,7 @@
         <v>85</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>83</v>
@@ -11536,13 +11564,13 @@
         <v>85</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>85</v>
+        <v>614</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>85</v>
+        <v>615</v>
       </c>
       <c r="AQ70" t="s" s="2">
-        <v>621</v>
+        <v>524</v>
       </c>
       <c r="AR70" t="s" s="2">
         <v>85</v>
@@ -11553,10 +11581,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11567,7 +11595,7 @@
         <v>83</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>85</v>
@@ -11579,16 +11607,20 @@
         <v>85</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
+        <v>618</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>620</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>85</v>
       </c>
@@ -11612,13 +11644,13 @@
         <v>85</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>85</v>
+        <v>541</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>85</v>
+        <v>621</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>85</v>
+        <v>622</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>85</v>
@@ -11636,13 +11668,13 @@
         <v>85</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>85</v>
@@ -11663,13 +11695,13 @@
         <v>85</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>85</v>
+        <v>614</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>593</v>
+        <v>615</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>625</v>
+        <v>524</v>
       </c>
       <c r="AR71" t="s" s="2">
         <v>85</v>
@@ -11680,10 +11712,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11694,7 +11726,7 @@
         <v>83</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>85</v>
@@ -11703,21 +11735,21 @@
         <v>85</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="L72" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>85</v>
       </c>
@@ -11765,13 +11797,13 @@
         <v>85</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>85</v>
@@ -11795,10 +11827,10 @@
         <v>85</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>631</v>
+        <v>85</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="AR72" t="s" s="2">
         <v>85</v>
@@ -11809,10 +11841,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11823,7 +11855,7 @@
         <v>83</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>85</v>
@@ -11832,20 +11864,18 @@
         <v>85</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>634</v>
+        <v>162</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>637</v>
-      </c>
+        <v>631</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>85</v>
@@ -11894,13 +11924,13 @@
         <v>85</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>85</v>
@@ -11924,10 +11954,10 @@
         <v>85</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>631</v>
+        <v>600</v>
       </c>
       <c r="AQ73" t="s" s="2">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="AR73" t="s" s="2">
         <v>85</v>
@@ -11938,10 +11968,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11964,20 +11994,18 @@
         <v>96</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>572</v>
+        <v>634</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>643</v>
-      </c>
+        <v>637</v>
+      </c>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>85</v>
       </c>
@@ -12025,7 +12053,7 @@
         <v>85</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>83</v>
@@ -12055,10 +12083,10 @@
         <v>85</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="AQ74" t="s" s="2">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="AR74" t="s" s="2">
         <v>85</v>
@@ -12069,10 +12097,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12083,7 +12111,7 @@
         <v>83</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>85</v>
@@ -12092,18 +12120,20 @@
         <v>85</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>162</v>
+        <v>641</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>163</v>
+        <v>642</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>643</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>644</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>85</v>
@@ -12152,19 +12182,19 @@
         <v>85</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>165</v>
+        <v>640</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>85</v>
@@ -12182,10 +12212,10 @@
         <v>85</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>85</v>
+        <v>638</v>
       </c>
       <c r="AQ75" t="s" s="2">
-        <v>166</v>
+        <v>645</v>
       </c>
       <c r="AR75" t="s" s="2">
         <v>85</v>
@@ -12196,14 +12226,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -12219,21 +12249,23 @@
         <v>85</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>141</v>
+        <v>579</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>142</v>
+        <v>647</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>168</v>
+        <v>648</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O76" s="2"/>
+        <v>649</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>650</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>85</v>
       </c>
@@ -12281,7 +12313,7 @@
         <v>85</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>172</v>
+        <v>646</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>83</v>
@@ -12293,7 +12325,7 @@
         <v>85</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>85</v>
@@ -12311,10 +12343,10 @@
         <v>85</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>85</v>
+        <v>651</v>
       </c>
       <c r="AQ76" t="s" s="2">
-        <v>166</v>
+        <v>652</v>
       </c>
       <c r="AR76" t="s" s="2">
         <v>85</v>
@@ -12325,46 +12357,42 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>583</v>
+        <v>85</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>584</v>
+        <v>163</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>85</v>
       </c>
@@ -12412,19 +12440,19 @@
         <v>85</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>586</v>
+        <v>165</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>85</v>
@@ -12445,7 +12473,7 @@
         <v>85</v>
       </c>
       <c r="AQ77" t="s" s="2">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="AR77" t="s" s="2">
         <v>85</v>
@@ -12456,21 +12484,21 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>85</v>
@@ -12479,23 +12507,21 @@
         <v>85</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>184</v>
+        <v>141</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>650</v>
+        <v>142</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>651</v>
+        <v>168</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>278</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>85</v>
       </c>
@@ -12519,13 +12545,13 @@
         <v>85</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>534</v>
+        <v>85</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>653</v>
+        <v>85</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>280</v>
+        <v>85</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>85</v>
@@ -12543,19 +12569,19 @@
         <v>85</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>649</v>
+        <v>172</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>85</v>
@@ -12570,16 +12596,16 @@
         <v>85</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>654</v>
+        <v>85</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>283</v>
+        <v>85</v>
       </c>
       <c r="AQ78" t="s" s="2">
-        <v>284</v>
+        <v>166</v>
       </c>
       <c r="AR78" t="s" s="2">
-        <v>285</v>
+        <v>85</v>
       </c>
       <c r="AS78" t="s" s="2">
         <v>85</v>
@@ -12594,38 +12620,38 @@
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>85</v>
+        <v>590</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J79" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>433</v>
+        <v>141</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>656</v>
+        <v>591</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>657</v>
+        <v>592</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>658</v>
+        <v>144</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>437</v>
+        <v>150</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>85</v>
@@ -12674,19 +12700,19 @@
         <v>85</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>655</v>
+        <v>593</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>85</v>
@@ -12701,27 +12727,27 @@
         <v>85</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>659</v>
+        <v>85</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>441</v>
+        <v>85</v>
       </c>
       <c r="AQ79" t="s" s="2">
-        <v>442</v>
+        <v>138</v>
       </c>
       <c r="AR79" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS79" t="s" s="2">
-        <v>443</v>
+        <v>85</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12729,7 +12755,7 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>95</v>
@@ -12741,22 +12767,22 @@
         <v>85</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K80" t="s" s="2">
         <v>184</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>502</v>
+        <v>278</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>85</v>
@@ -12781,13 +12807,13 @@
         <v>85</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>189</v>
+        <v>541</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>503</v>
+        <v>280</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>85</v>
@@ -12805,16 +12831,16 @@
         <v>85</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>665</v>
+        <v>85</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>107</v>
@@ -12832,16 +12858,16 @@
         <v>85</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>85</v>
+        <v>661</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>138</v>
+        <v>283</v>
       </c>
       <c r="AQ80" t="s" s="2">
-        <v>506</v>
+        <v>284</v>
       </c>
       <c r="AR80" t="s" s="2">
-        <v>85</v>
+        <v>285</v>
       </c>
       <c r="AS80" t="s" s="2">
         <v>85</v>
@@ -12849,21 +12875,21 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>508</v>
+        <v>85</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>85</v>
@@ -12872,22 +12898,22 @@
         <v>85</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>184</v>
+        <v>434</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>509</v>
+        <v>663</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>510</v>
+        <v>664</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>511</v>
+        <v>665</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>512</v>
+        <v>438</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>85</v>
@@ -12912,13 +12938,13 @@
         <v>85</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>189</v>
+        <v>85</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>667</v>
+        <v>85</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>668</v>
+        <v>85</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>85</v>
@@ -12936,13 +12962,13 @@
         <v>85</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>85</v>
@@ -12963,27 +12989,27 @@
         <v>85</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>515</v>
+        <v>666</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>516</v>
+        <v>442</v>
       </c>
       <c r="AQ81" t="s" s="2">
-        <v>517</v>
+        <v>443</v>
       </c>
       <c r="AR81" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS81" t="s" s="2">
-        <v>518</v>
+        <v>444</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12994,7 +13020,7 @@
         <v>83</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>85</v>
@@ -13006,19 +13032,19 @@
         <v>85</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>86</v>
+        <v>184</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="N82" t="s" s="2">
         <v>670</v>
       </c>
-      <c r="M82" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>575</v>
-      </c>
       <c r="O82" t="s" s="2">
-        <v>576</v>
+        <v>509</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>85</v>
@@ -13043,13 +13069,13 @@
         <v>85</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>85</v>
+        <v>671</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>85</v>
+        <v>510</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>85</v>
@@ -13067,16 +13093,16 @@
         <v>85</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>85</v>
+        <v>672</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>107</v>
@@ -13097,20 +13123,282 @@
         <v>85</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>578</v>
+        <v>138</v>
       </c>
       <c r="AQ82" t="s" s="2">
-        <v>579</v>
+        <v>513</v>
       </c>
       <c r="AR82" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS82" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="83" hidden="true">
+      <c r="A83" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="P83" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO83" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AP83" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AQ83" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AR83" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS83" t="s" s="2">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="84" hidden="true">
+      <c r="A84" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="P84" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO84" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP84" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AQ84" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AR84" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS84" t="s" s="2">
         <v>85</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS82">
+  <autoFilter ref="A1:AS84">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -13120,7 +13408,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI81">
+  <conditionalFormatting sqref="A2:AI83">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -671,7 +671,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>851: source value from CHEM, HEM, TOX, RIA, SER, etc. - IEN (63.04-.001)</t>
+    <t>851: source value based on CHEM, HEM, TOX, RIA, SER, etc. - IEN (63.04-.001)</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
@@ -940,7 +940,7 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
-    <t>853: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-)</t>
+    <t>853: source value based on CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-)</t>
   </si>
   <si>
     <t>C*E.1-8, C*E.10-22</t>
@@ -1021,7 +1021,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>853-2: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC - CODE (63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-.01)</t>
+    <t>853-2: source value based on CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC - CODE (63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-.01)</t>
   </si>
   <si>
     <t>C*E.1</t>
@@ -1045,7 +1045,7 @@
     <t>Coding.display</t>
   </si>
   <si>
-    <t>853-3: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC - COMPONENT (63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-1)</t>
+    <t>853-3: source value based on CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC - COMPONENT (63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-1)</t>
   </si>
   <si>
     <t>C*E.2 - but note this is not well followed</t>
@@ -1125,7 +1125,7 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
-    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
+    <t>844: reference based on PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
@@ -1257,7 +1257,7 @@
 </t>
   </si>
   <si>
-    <t>845: source value from CHEM, HEM, TOX, RIA, SER, etc. - DATE/TIME SPECIMEN TAKEN (63.04-.01)</t>
+    <t>845: source value based on CHEM, HEM, TOX, RIA, SER, etc. - DATE/TIME SPECIMEN TAKEN (63.04-.01)</t>
   </si>
   <si>
     <t>Chem.LabChem.LabChemSpecimenDateTime,Chem.LabPanel.LabChemSpecimenDateTime,Chem.OrderedLabPanel.LabChemSpecimenDateTime,Chem.PatientLabChem.LabChemSpecimenDateTime</t>
@@ -1282,7 +1282,7 @@
     <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
-    <t>858: source value from CHEM, HEM, TOX, RIA, SER, etc. - DATE REPORT COMPLETED (63.04-.03)</t>
+    <t>858: source value based on CHEM, HEM, TOX, RIA, SER, etc. - DATE REPORT COMPLETED (63.04-.03)</t>
   </si>
   <si>
     <t>Chem.LabChem.LabChemCompleteDateTime,Chem.LabPanel.LabChemCompleteDateTime,Chem.OrderedLabPanel.LabChemCompleteDateTime,Chem.PatientLabChem.LabChemCompleteDateTime</t>
@@ -1342,7 +1342,7 @@
 </t>
   </si>
   <si>
-    <t>847: reference from CHEM, HEM, TOX, RIA, SER, etc. - ACCESSIONING INSTITUTION (63.04-.112)</t>
+    <t>847: reference based on CHEM, HEM, TOX, RIA, SER, etc. - ACCESSIONING INSTITUTION (63.04-.112)</t>
   </si>
   <si>
     <t>Chem.LabChem.AccessionInstitutionIEN,Chem.PatientLabChem.AccessionInstitutionIEN</t>
@@ -1361,7 +1361,7 @@
 </t>
   </si>
   <si>
-    <t>1676: reference from CHEM, HEM, TOX, RIA, SER, etc. - VERIFY PERSON (63.04-.04)</t>
+    <t>1676: reference based on CHEM, HEM, TOX, RIA, SER, etc. - VERIFY PERSON (63.04-.04)</t>
   </si>
   <si>
     <t>LabOrder.Result.VerifiedBy</t>
@@ -1453,7 +1453,7 @@
     <t>Quantity.value</t>
   </si>
   <si>
-    <t>857: source value from CHEM, HEM, TOX, RIA, SER, etc. - testnames (63.04-2+through+862)</t>
+    <t>857: source value based on CHEM, HEM, TOX, RIA, SER, etc. - testnames (63.04-2+through+862)</t>
   </si>
   <si>
     <t>SN.2  / CQ - N/A</t>
@@ -1513,7 +1513,7 @@
     <t>Quantity.unit</t>
   </si>
   <si>
-    <t>864: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - UNITS (63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-6)</t>
+    <t>864: source value based on CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - UNITS (63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-6)</t>
   </si>
   <si>
     <t>(see OBX.6 etc.) / CQ.2</t>
@@ -1674,7 +1674,7 @@
     <t>Need to be able to provide free text additional information.</t>
   </si>
   <si>
-    <t>846: source value from CHEM, HEM, TOX, RIA, SER, etc. - COMMENT &gt; COMMENT - COMMENT (63.04-.99 &gt; 63.041-.01)</t>
+    <t>846: source value based on CHEM, HEM, TOX, RIA, SER, etc. - COMMENT &gt; COMMENT - COMMENT (63.04-.99 &gt; 63.041-.01)</t>
   </si>
   <si>
     <t>Chem.LabPanel.LabPanelComment</t>
@@ -1766,7 +1766,7 @@
     <t>Should only be used if not implicit in code found in `Observation.code`.  Observations are not made on specimens themselves; they are made on a subject, but in many cases by the means of a specimen. Note that although specimens are often involved, they are not always tracked and reported explicitly. Also note that observation resources may be used in contexts that track the specimen explicitly (e.g. Diagnostic Report).</t>
   </si>
   <si>
-    <t>1656: reference from CHEM, HEM, TOX, RIA, SER, etc. - ACCESSION (63.04-.06)</t>
+    <t>1656: reference based on CHEM, HEM, TOX, RIA, SER, etc. - ACCESSION (63.04-.06)</t>
   </si>
   <si>
     <t>Chem.LabChem.ShortAccessionNumber,Chem.PatientLabChem.ShortAccessionNumber</t>
@@ -1884,7 +1884,7 @@
 </t>
   </si>
   <si>
-    <t>854: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - REFERENCE LOW (63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-1)</t>
+    <t>854: source value based on CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - REFERENCE LOW (63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-1)</t>
   </si>
   <si>
     <t>OBX-7</t>
@@ -1902,7 +1902,7 @@
     <t>The value of the high bound of the reference range.  The high bound of the reference range endpoint is inclusive of the value (e.g.  reference range is &gt;=5 - &lt;=9). If the high bound is omitted,  it is assumed to be meaningless (e.g. reference range is &gt;= 2.3).</t>
   </si>
   <si>
-    <t>850: source value from CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - REFERENCE HIGH (63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-2)</t>
+    <t>850: source value based on CHEM, HEM, TOX, RIA, SER, etc. - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - REFERENCE HIGH (63.04-.35 &gt; 63.07-13 &gt; 60-100 &gt; 60.01-2)</t>
   </si>
   <si>
     <t>value:IVL_PQ.high</t>
@@ -2488,7 +2488,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="251.90234375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="255.0" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="103.25" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3512" uniqueCount="679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3514" uniqueCount="681">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -798,6 +798,9 @@
   </si>
   <si>
     <t>Need to track the status of individual results. Some results are finalized before the whole report is finalized.</t>
+  </si>
+  <si>
+    <t>see mapping [VF_LabObservationStatus](ConceptMap-VF-LabObservationStatus.html)</t>
   </si>
   <si>
     <t>http://va.gov/fhir/ValueSet/LabObservationStatus</t>
@@ -1635,6 +1638,9 @@
   </si>
   <si>
     <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
+  </si>
+  <si>
+    <t>see mapping [VF_LabInterpretation](ConceptMap-VF-LabInterpretation.html)</t>
   </si>
   <si>
     <t>http://va.gov/fhir/ValueSet/LabInterpretation</t>
@@ -5285,9 +5291,11 @@
       <c r="X22" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="Y22" s="2"/>
+      <c r="Y22" t="s" s="2">
+        <v>252</v>
+      </c>
       <c r="Z22" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>85</v>
@@ -5320,7 +5328,7 @@
         <v>107</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>85</v>
@@ -5329,19 +5337,19 @@
         <v>85</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AS22" t="s" s="2">
         <v>85</v>
@@ -5349,10 +5357,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5378,16 +5386,16 @@
         <v>184</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>85</v>
@@ -5397,7 +5405,7 @@
         <v>85</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>85</v>
@@ -5415,16 +5423,16 @@
         <v>119</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -5434,7 +5442,7 @@
         <v>171</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>83</v>
@@ -5449,7 +5457,7 @@
         <v>107</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>85</v>
@@ -5467,10 +5475,10 @@
         <v>85</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AS23" t="s" s="2">
         <v>85</v>
@@ -5478,13 +5486,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>85</v>
@@ -5509,16 +5517,16 @@
         <v>184</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>85</v>
@@ -5528,7 +5536,7 @@
         <v>85</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>85</v>
@@ -5546,10 +5554,10 @@
         <v>119</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>85</v>
@@ -5567,7 +5575,7 @@
         <v>85</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>83</v>
@@ -5600,10 +5608,10 @@
         <v>85</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AS24" t="s" s="2">
         <v>85</v>
@@ -5611,14 +5619,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5640,16 +5648,16 @@
         <v>184</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>85</v>
@@ -5677,10 +5685,10 @@
         <v>189</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>85</v>
@@ -5698,7 +5706,7 @@
         <v>85</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>95</v>
@@ -5722,30 +5730,30 @@
         <v>85</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AS25" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5869,10 +5877,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5998,10 +6006,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6024,19 +6032,19 @@
         <v>96</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>85</v>
@@ -6085,7 +6093,7 @@
         <v>85</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>83</v>
@@ -6100,7 +6108,7 @@
         <v>107</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>85</v>
@@ -6115,10 +6123,10 @@
         <v>85</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>85</v>
@@ -6129,10 +6137,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6256,10 +6264,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6385,10 +6393,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6414,16 +6422,16 @@
         <v>109</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>85</v>
@@ -6433,7 +6441,7 @@
         <v>85</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="T31" t="s" s="2">
         <v>85</v>
@@ -6472,7 +6480,7 @@
         <v>85</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>83</v>
@@ -6487,7 +6495,7 @@
         <v>107</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>85</v>
@@ -6502,10 +6510,10 @@
         <v>85</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>85</v>
@@ -6516,10 +6524,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6545,13 +6553,13 @@
         <v>162</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6601,7 +6609,7 @@
         <v>85</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>83</v>
@@ -6631,10 +6639,10 @@
         <v>85</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>85</v>
@@ -6645,10 +6653,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6674,14 +6682,14 @@
         <v>115</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>85</v>
@@ -6730,7 +6738,7 @@
         <v>85</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>83</v>
@@ -6745,7 +6753,7 @@
         <v>107</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>85</v>
@@ -6760,10 +6768,10 @@
         <v>85</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>85</v>
@@ -6774,10 +6782,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6803,14 +6811,14 @@
         <v>162</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>85</v>
@@ -6859,7 +6867,7 @@
         <v>85</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>83</v>
@@ -6874,7 +6882,7 @@
         <v>107</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>85</v>
@@ -6889,10 +6897,10 @@
         <v>85</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>85</v>
@@ -6903,10 +6911,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6929,19 +6937,19 @@
         <v>96</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>85</v>
@@ -6990,7 +6998,7 @@
         <v>85</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>83</v>
@@ -7020,10 +7028,10 @@
         <v>85</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>85</v>
@@ -7034,10 +7042,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7063,16 +7071,16 @@
         <v>162</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>85</v>
@@ -7121,7 +7129,7 @@
         <v>85</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>83</v>
@@ -7151,10 +7159,10 @@
         <v>85</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>85</v>
@@ -7165,10 +7173,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7191,19 +7199,19 @@
         <v>96</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>85</v>
@@ -7252,7 +7260,7 @@
         <v>85</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>83</v>
@@ -7267,28 +7275,28 @@
         <v>107</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AS37" t="s" s="2">
         <v>85</v>
@@ -7296,10 +7304,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7322,16 +7330,16 @@
         <v>96</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7381,7 +7389,7 @@
         <v>85</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>83</v>
@@ -7411,13 +7419,13 @@
         <v>85</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AS38" t="s" s="2">
         <v>85</v>
@@ -7425,14 +7433,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7451,19 +7459,19 @@
         <v>96</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>85</v>
@@ -7512,7 +7520,7 @@
         <v>85</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>83</v>
@@ -7536,19 +7544,19 @@
         <v>85</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AS39" t="s" s="2">
         <v>85</v>
@@ -7556,14 +7564,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7582,19 +7590,19 @@
         <v>96</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>85</v>
@@ -7631,7 +7639,7 @@
         <v>85</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
@@ -7641,7 +7649,7 @@
         <v>171</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>83</v>
@@ -7650,10 +7658,10 @@
         <v>95</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>85</v>
@@ -7665,19 +7673,19 @@
         <v>85</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AS40" t="s" s="2">
         <v>85</v>
@@ -7685,16 +7693,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7713,19 +7721,19 @@
         <v>96</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>85</v>
@@ -7774,7 +7782,7 @@
         <v>85</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>83</v>
@@ -7783,34 +7791,34 @@
         <v>95</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AS41" t="s" s="2">
         <v>85</v>
@@ -7818,10 +7826,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7844,16 +7852,16 @@
         <v>96</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7903,7 +7911,7 @@
         <v>85</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>83</v>
@@ -7918,13 +7926,13 @@
         <v>107</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>85</v>
@@ -7933,13 +7941,13 @@
         <v>85</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AS42" t="s" s="2">
         <v>85</v>
@@ -7947,10 +7955,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7973,17 +7981,17 @@
         <v>96</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>85</v>
@@ -8020,7 +8028,7 @@
         <v>85</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
@@ -8030,7 +8038,7 @@
         <v>171</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>83</v>
@@ -8054,19 +8062,19 @@
         <v>85</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AS43" t="s" s="2">
         <v>85</v>
@@ -8074,13 +8082,13 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>85</v>
@@ -8102,17 +8110,17 @@
         <v>96</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>85</v>
@@ -8161,7 +8169,7 @@
         <v>85</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>83</v>
@@ -8176,28 +8184,28 @@
         <v>107</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AS44" t="s" s="2">
         <v>85</v>
@@ -8205,13 +8213,13 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>85</v>
@@ -8233,17 +8241,17 @@
         <v>96</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>85</v>
@@ -8292,7 +8300,7 @@
         <v>85</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
@@ -8307,28 +8315,28 @@
         <v>107</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AS45" t="s" s="2">
         <v>85</v>
@@ -8336,10 +8344,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8362,19 +8370,19 @@
         <v>96</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>85</v>
@@ -8411,7 +8419,7 @@
         <v>85</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AC46" s="2"/>
       <c r="AD46" t="s" s="2">
@@ -8421,7 +8429,7 @@
         <v>171</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>83</v>
@@ -8430,10 +8438,10 @@
         <v>95</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>85</v>
@@ -8448,30 +8456,30 @@
         <v>85</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS46" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>85</v>
@@ -8493,19 +8501,19 @@
         <v>96</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>85</v>
@@ -8554,7 +8562,7 @@
         <v>85</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
@@ -8563,10 +8571,10 @@
         <v>95</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>85</v>
@@ -8581,27 +8589,27 @@
         <v>85</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS47" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8725,10 +8733,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8854,10 +8862,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8880,19 +8888,19 @@
         <v>96</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>85</v>
@@ -8941,7 +8949,7 @@
         <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -8956,7 +8964,7 @@
         <v>107</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>85</v>
@@ -8971,10 +8979,10 @@
         <v>85</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>85</v>
@@ -8985,10 +8993,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9014,20 +9022,20 @@
         <v>115</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>85</v>
       </c>
       <c r="Q51" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="R51" t="s" s="2">
         <v>85</v>
@@ -9051,10 +9059,10 @@
         <v>178</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>85</v>
@@ -9072,7 +9080,7 @@
         <v>85</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -9102,10 +9110,10 @@
         <v>85</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>85</v>
@@ -9116,10 +9124,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9145,14 +9153,14 @@
         <v>162</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>85</v>
@@ -9201,7 +9209,7 @@
         <v>85</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
@@ -9216,7 +9224,7 @@
         <v>107</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>85</v>
@@ -9231,10 +9239,10 @@
         <v>85</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>85</v>
@@ -9245,10 +9253,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9274,14 +9282,14 @@
         <v>109</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>85</v>
@@ -9330,7 +9338,7 @@
         <v>85</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -9339,7 +9347,7 @@
         <v>95</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>107</v>
@@ -9360,10 +9368,10 @@
         <v>85</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>85</v>
@@ -9374,10 +9382,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9403,16 +9411,16 @@
         <v>115</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>85</v>
@@ -9461,7 +9469,7 @@
         <v>85</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -9491,10 +9499,10 @@
         <v>85</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>85</v>
@@ -9505,13 +9513,13 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>85</v>
@@ -9536,16 +9544,16 @@
         <v>184</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>85</v>
@@ -9594,7 +9602,7 @@
         <v>85</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -9603,13 +9611,13 @@
         <v>95</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>85</v>
@@ -9621,30 +9629,30 @@
         <v>85</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS55" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>85</v>
@@ -9669,16 +9677,16 @@
         <v>162</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>85</v>
@@ -9727,7 +9735,7 @@
         <v>85</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
@@ -9736,13 +9744,13 @@
         <v>95</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>85</v>
@@ -9754,27 +9762,27 @@
         <v>85</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS56" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9800,16 +9808,16 @@
         <v>184</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>85</v>
@@ -9838,7 +9846,7 @@
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>85</v>
@@ -9856,7 +9864,7 @@
         <v>85</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
@@ -9865,13 +9873,13 @@
         <v>95</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>85</v>
@@ -9889,7 +9897,7 @@
         <v>138</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>85</v>
@@ -9900,14 +9908,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9929,16 +9937,16 @@
         <v>184</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>85</v>
@@ -9965,9 +9973,11 @@
       <c r="X58" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="Y58" s="2"/>
+      <c r="Y58" t="s" s="2">
+        <v>521</v>
+      </c>
       <c r="Z58" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>85</v>
@@ -9985,7 +9995,7 @@
         <v>85</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
@@ -10000,7 +10010,7 @@
         <v>107</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>85</v>
@@ -10012,27 +10022,27 @@
         <v>85</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS58" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10055,19 +10065,19 @@
         <v>85</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>85</v>
@@ -10116,7 +10126,7 @@
         <v>85</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
@@ -10131,13 +10141,13 @@
         <v>107</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>85</v>
@@ -10146,10 +10156,10 @@
         <v>85</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>85</v>
@@ -10160,10 +10170,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10189,13 +10199,13 @@
         <v>184</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -10221,13 +10231,13 @@
         <v>85</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>85</v>
@@ -10245,7 +10255,7 @@
         <v>85</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
@@ -10272,27 +10282,27 @@
         <v>85</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS60" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10318,16 +10328,16 @@
         <v>184</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>85</v>
@@ -10352,13 +10362,13 @@
         <v>85</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>85</v>
@@ -10376,7 +10386,7 @@
         <v>85</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
@@ -10406,10 +10416,10 @@
         <v>85</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>85</v>
@@ -10420,10 +10430,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10446,16 +10456,16 @@
         <v>85</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -10505,7 +10515,7 @@
         <v>85</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
@@ -10520,39 +10530,39 @@
         <v>107</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS62" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10575,16 +10585,16 @@
         <v>85</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10634,7 +10644,7 @@
         <v>85</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -10661,27 +10671,27 @@
         <v>85</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS63" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10704,19 +10714,19 @@
         <v>85</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>85</v>
@@ -10765,7 +10775,7 @@
         <v>85</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
@@ -10777,7 +10787,7 @@
         <v>85</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>85</v>
@@ -10795,10 +10805,10 @@
         <v>85</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>85</v>
@@ -10809,10 +10819,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10936,10 +10946,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11065,14 +11075,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -11094,10 +11104,10 @@
         <v>141</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>144</v>
@@ -11152,7 +11162,7 @@
         <v>85</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>83</v>
@@ -11196,10 +11206,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11222,13 +11232,13 @@
         <v>85</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -11279,7 +11289,7 @@
         <v>85</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>83</v>
@@ -11288,13 +11298,13 @@
         <v>95</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>85</v>
@@ -11309,10 +11319,10 @@
         <v>85</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>85</v>
@@ -11323,10 +11333,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11349,13 +11359,13 @@
         <v>85</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -11406,7 +11416,7 @@
         <v>85</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
@@ -11415,13 +11425,13 @@
         <v>95</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>85</v>
@@ -11436,10 +11446,10 @@
         <v>85</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>85</v>
@@ -11450,10 +11460,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11479,16 +11489,16 @@
         <v>184</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>85</v>
@@ -11516,10 +11526,10 @@
         <v>119</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>85</v>
@@ -11537,7 +11547,7 @@
         <v>85</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>83</v>
@@ -11564,13 +11574,13 @@
         <v>85</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="AQ70" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AR70" t="s" s="2">
         <v>85</v>
@@ -11581,10 +11591,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11610,16 +11620,16 @@
         <v>184</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>85</v>
@@ -11644,13 +11654,13 @@
         <v>85</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>85</v>
@@ -11668,7 +11678,7 @@
         <v>85</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>83</v>
@@ -11695,13 +11705,13 @@
         <v>85</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AR71" t="s" s="2">
         <v>85</v>
@@ -11712,10 +11722,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11738,17 +11748,17 @@
         <v>85</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>85</v>
@@ -11797,7 +11807,7 @@
         <v>85</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>83</v>
@@ -11830,7 +11840,7 @@
         <v>85</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AR72" t="s" s="2">
         <v>85</v>
@@ -11841,10 +11851,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11870,10 +11880,10 @@
         <v>162</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -11924,7 +11934,7 @@
         <v>85</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>83</v>
@@ -11954,10 +11964,10 @@
         <v>85</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="AQ73" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="AR73" t="s" s="2">
         <v>85</v>
@@ -11968,10 +11978,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11994,16 +12004,16 @@
         <v>96</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -12053,7 +12063,7 @@
         <v>85</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>83</v>
@@ -12083,10 +12093,10 @@
         <v>85</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="AQ74" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="AR74" t="s" s="2">
         <v>85</v>
@@ -12097,10 +12107,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12123,16 +12133,16 @@
         <v>96</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -12182,7 +12192,7 @@
         <v>85</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>83</v>
@@ -12212,10 +12222,10 @@
         <v>85</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="AQ75" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="AR75" t="s" s="2">
         <v>85</v>
@@ -12226,10 +12236,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12252,19 +12262,19 @@
         <v>96</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>85</v>
@@ -12313,7 +12323,7 @@
         <v>85</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>83</v>
@@ -12343,10 +12353,10 @@
         <v>85</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="AQ76" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="AR76" t="s" s="2">
         <v>85</v>
@@ -12357,10 +12367,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12484,10 +12494,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12613,14 +12623,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -12642,10 +12652,10 @@
         <v>141</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="N79" t="s" s="2">
         <v>144</v>
@@ -12700,7 +12710,7 @@
         <v>85</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>83</v>
@@ -12744,10 +12754,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12773,16 +12783,16 @@
         <v>184</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>85</v>
@@ -12807,13 +12817,13 @@
         <v>85</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>85</v>
@@ -12831,7 +12841,7 @@
         <v>85</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>95</v>
@@ -12858,16 +12868,16 @@
         <v>85</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AQ80" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AR80" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AS80" t="s" s="2">
         <v>85</v>
@@ -12875,10 +12885,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12901,19 +12911,19 @@
         <v>96</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>85</v>
@@ -12962,7 +12972,7 @@
         <v>85</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>83</v>
@@ -12989,27 +12999,27 @@
         <v>85</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AQ81" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AR81" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS81" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13035,16 +13045,16 @@
         <v>184</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>85</v>
@@ -13072,10 +13082,10 @@
         <v>189</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>85</v>
@@ -13093,7 +13103,7 @@
         <v>85</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>83</v>
@@ -13102,7 +13112,7 @@
         <v>95</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>107</v>
@@ -13126,7 +13136,7 @@
         <v>138</v>
       </c>
       <c r="AQ82" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AR82" t="s" s="2">
         <v>85</v>
@@ -13137,14 +13147,14 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -13166,16 +13176,16 @@
         <v>184</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>85</v>
@@ -13203,28 +13213,28 @@
         <v>189</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="Z83" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF83" t="s" s="2">
         <v>675</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>673</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>83</v>
@@ -13251,27 +13261,27 @@
         <v>85</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AQ83" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AR83" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS83" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13297,16 +13307,16 @@
         <v>86</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>85</v>
@@ -13355,7 +13365,7 @@
         <v>85</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>83</v>
@@ -13385,10 +13395,10 @@
         <v>85</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="AQ84" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="AR84" t="s" s="2">
         <v>85</v>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$82</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3514" uniqueCount="681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3428" uniqueCount="675">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -837,6 +837,28 @@
   </si>
   <si>
     <t>Used for filtering what observations are retrieved and displayed.</t>
+  </si>
+  <si>
+    <t>Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category:Laboratory</t>
+  </si>
+  <si>
+    <t>Laboratory</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -847,29 +869,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>Codes for high level observation categories.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
     <t>843: fixed value = http://terminology.hl7.org/CodeSystem/observation-category#laboratory</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.category:Laboratory</t>
-  </si>
-  <si>
-    <t>Laboratory</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -1572,24 +1572,6 @@
   </si>
   <si>
     <t>PQ.code, MO.currency, PQ.translation.code</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>2054: target not supported</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueString</t>
-  </si>
-  <si>
-    <t>valueString</t>
-  </si>
-  <si>
-    <t>2055: target not supported</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -2456,12 +2438,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AS84"/>
+  <dimension ref="A1:AS82"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.1171875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="17.96484375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -5405,7 +5387,7 @@
         <v>85</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>265</v>
+        <v>85</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>85</v>
@@ -5423,16 +5405,16 @@
         <v>119</v>
       </c>
       <c r="Y23" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="Z23" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="Z23" t="s" s="2">
+      <c r="AA23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB23" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -5457,28 +5439,28 @@
         <v>107</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AQ23" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AR23" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AQ23" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="AR23" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="AS23" t="s" s="2">
         <v>85</v>
@@ -5486,13 +5468,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>260</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>85</v>
@@ -5536,7 +5518,7 @@
         <v>85</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>85</v>
@@ -5554,10 +5536,10 @@
         <v>119</v>
       </c>
       <c r="Y24" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="Z24" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="Z24" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>85</v>
@@ -5590,7 +5572,7 @@
         <v>107</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>85</v>
+        <v>273</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>85</v>
@@ -5608,10 +5590,10 @@
         <v>85</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AS24" t="s" s="2">
         <v>85</v>
@@ -9516,11 +9498,9 @@
         <v>500</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="C55" t="s" s="2">
-        <v>501</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
         <v>85</v>
       </c>
@@ -9538,22 +9518,22 @@
         <v>85</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K55" t="s" s="2">
         <v>184</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>436</v>
+        <v>501</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>437</v>
+        <v>502</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>438</v>
+        <v>503</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>439</v>
+        <v>504</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>85</v>
@@ -9578,13 +9558,11 @@
         <v>85</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>85</v>
+        <v>505</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>85</v>
@@ -9602,7 +9580,7 @@
         <v>85</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>434</v>
+        <v>500</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -9611,13 +9589,13 @@
         <v>95</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>440</v>
+        <v>506</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>441</v>
+        <v>107</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>85</v>
@@ -9629,40 +9607,38 @@
         <v>85</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>442</v>
+        <v>85</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>443</v>
+        <v>138</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>444</v>
+        <v>508</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS55" t="s" s="2">
-        <v>445</v>
+        <v>85</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="C56" t="s" s="2">
-        <v>504</v>
-      </c>
+        <v>509</v>
+      </c>
+      <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>85</v>
+        <v>510</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>96</v>
@@ -9671,22 +9647,22 @@
         <v>85</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>436</v>
+        <v>511</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>437</v>
+        <v>512</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>438</v>
+        <v>513</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>439</v>
+        <v>514</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>85</v>
@@ -9711,13 +9687,13 @@
         <v>85</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>85</v>
+        <v>178</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>85</v>
+        <v>515</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>85</v>
+        <v>516</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>85</v>
@@ -9735,22 +9711,22 @@
         <v>85</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>434</v>
+        <v>509</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>440</v>
+        <v>85</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>441</v>
+        <v>107</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>85</v>
@@ -9762,27 +9738,27 @@
         <v>85</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>442</v>
+        <v>518</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>443</v>
+        <v>519</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>444</v>
+        <v>520</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS56" t="s" s="2">
-        <v>445</v>
+        <v>521</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>506</v>
+        <v>522</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>506</v>
+        <v>522</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9793,7 +9769,7 @@
         <v>83</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>96</v>
@@ -9805,19 +9781,19 @@
         <v>85</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>184</v>
+        <v>523</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>508</v>
+        <v>525</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>509</v>
+        <v>526</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>510</v>
+        <v>527</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>85</v>
@@ -9842,11 +9818,13 @@
         <v>85</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="Y57" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="Z57" t="s" s="2">
-        <v>511</v>
+        <v>85</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>85</v>
@@ -9864,28 +9842,28 @@
         <v>85</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>506</v>
+        <v>522</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>512</v>
+        <v>85</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>513</v>
+        <v>528</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>85</v>
+        <v>529</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>85</v>
+        <v>530</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>85</v>
@@ -9894,10 +9872,10 @@
         <v>85</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>138</v>
+        <v>531</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>514</v>
+        <v>532</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>85</v>
@@ -9908,24 +9886,24 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>515</v>
+        <v>533</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>515</v>
+        <v>533</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>516</v>
+        <v>85</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>85</v>
@@ -9937,17 +9915,15 @@
         <v>184</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>517</v>
+        <v>534</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>518</v>
+        <v>535</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>520</v>
-      </c>
+        <v>536</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>85</v>
       </c>
@@ -9971,13 +9947,13 @@
         <v>85</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>178</v>
+        <v>537</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>521</v>
+        <v>538</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>522</v>
+        <v>539</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>85</v>
@@ -9995,13 +9971,13 @@
         <v>85</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>515</v>
+        <v>533</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>85</v>
@@ -10010,7 +9986,7 @@
         <v>107</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>523</v>
+        <v>85</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>85</v>
@@ -10022,27 +9998,27 @@
         <v>85</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>524</v>
+        <v>540</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>525</v>
+        <v>541</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>526</v>
+        <v>542</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS58" t="s" s="2">
-        <v>527</v>
+        <v>543</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>528</v>
+        <v>544</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>528</v>
+        <v>544</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10053,10 +10029,10 @@
         <v>83</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>85</v>
@@ -10065,19 +10041,19 @@
         <v>85</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>529</v>
+        <v>184</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>530</v>
+        <v>545</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>531</v>
+        <v>546</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>532</v>
+        <v>547</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>533</v>
+        <v>548</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>85</v>
@@ -10102,13 +10078,13 @@
         <v>85</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>85</v>
+        <v>537</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>85</v>
+        <v>549</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>85</v>
+        <v>550</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>85</v>
@@ -10126,13 +10102,13 @@
         <v>85</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>528</v>
+        <v>544</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>85</v>
@@ -10141,13 +10117,13 @@
         <v>107</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>534</v>
+        <v>85</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>535</v>
+        <v>85</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>536</v>
+        <v>85</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>85</v>
@@ -10156,10 +10132,10 @@
         <v>85</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>537</v>
+        <v>551</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>538</v>
+        <v>552</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>85</v>
@@ -10170,10 +10146,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>539</v>
+        <v>553</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>539</v>
+        <v>553</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10187,7 +10163,7 @@
         <v>95</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>85</v>
@@ -10196,16 +10172,16 @@
         <v>85</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>184</v>
+        <v>554</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>540</v>
+        <v>555</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>541</v>
+        <v>556</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>542</v>
+        <v>557</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -10231,13 +10207,13 @@
         <v>85</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>543</v>
+        <v>85</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>544</v>
+        <v>85</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>545</v>
+        <v>85</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>85</v>
@@ -10255,7 +10231,7 @@
         <v>85</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>539</v>
+        <v>553</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
@@ -10270,39 +10246,39 @@
         <v>107</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>85</v>
+        <v>558</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>85</v>
+        <v>559</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>85</v>
+        <v>560</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>546</v>
+        <v>561</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>547</v>
+        <v>562</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>548</v>
+        <v>563</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS60" t="s" s="2">
-        <v>549</v>
+        <v>564</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>550</v>
+        <v>565</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>550</v>
+        <v>565</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10325,20 +10301,18 @@
         <v>85</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>184</v>
+        <v>566</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>551</v>
+        <v>567</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>552</v>
+        <v>568</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>554</v>
-      </c>
+        <v>569</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>85</v>
       </c>
@@ -10362,13 +10336,13 @@
         <v>85</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>543</v>
+        <v>85</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>555</v>
+        <v>85</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>556</v>
+        <v>85</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>85</v>
@@ -10386,7 +10360,7 @@
         <v>85</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>550</v>
+        <v>565</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
@@ -10413,27 +10387,27 @@
         <v>85</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>85</v>
+        <v>570</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>557</v>
+        <v>571</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>558</v>
+        <v>572</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS61" t="s" s="2">
-        <v>85</v>
+        <v>573</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>559</v>
+        <v>574</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>559</v>
+        <v>574</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10444,10 +10418,10 @@
         <v>83</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>85</v>
@@ -10456,18 +10430,20 @@
         <v>85</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>560</v>
+        <v>575</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>561</v>
+        <v>576</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>562</v>
+        <v>577</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>578</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>579</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>85</v>
       </c>
@@ -10515,54 +10491,54 @@
         <v>85</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>559</v>
+        <v>574</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>107</v>
+        <v>580</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>564</v>
+        <v>85</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>565</v>
+        <v>85</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>566</v>
+        <v>85</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>567</v>
+        <v>85</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>568</v>
+        <v>581</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>569</v>
+        <v>582</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS62" t="s" s="2">
-        <v>570</v>
+        <v>85</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10585,17 +10561,15 @@
         <v>85</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>572</v>
+        <v>162</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>573</v>
+        <v>163</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>575</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>85</v>
@@ -10644,7 +10618,7 @@
         <v>85</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>571</v>
+        <v>165</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -10656,7 +10630,7 @@
         <v>85</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>85</v>
@@ -10671,31 +10645,31 @@
         <v>85</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>576</v>
+        <v>85</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>577</v>
+        <v>85</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>578</v>
+        <v>166</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS63" t="s" s="2">
-        <v>579</v>
+        <v>85</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -10714,20 +10688,18 @@
         <v>85</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>581</v>
+        <v>141</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>582</v>
+        <v>142</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>583</v>
+        <v>168</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>585</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>85</v>
       </c>
@@ -10775,7 +10747,7 @@
         <v>85</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>580</v>
+        <v>172</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
@@ -10787,7 +10759,7 @@
         <v>85</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>586</v>
+        <v>146</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>85</v>
@@ -10805,10 +10777,10 @@
         <v>85</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>587</v>
+        <v>85</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>588</v>
+        <v>166</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>85</v>
@@ -10819,42 +10791,46 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>85</v>
+        <v>586</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>163</v>
+        <v>587</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
+        <v>588</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>85</v>
       </c>
@@ -10902,19 +10878,19 @@
         <v>85</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>165</v>
+        <v>589</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>85</v>
@@ -10935,7 +10911,7 @@
         <v>85</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="AR65" t="s" s="2">
         <v>85</v>
@@ -10953,17 +10929,17 @@
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>85</v>
@@ -10972,17 +10948,15 @@
         <v>85</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>141</v>
+        <v>591</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>142</v>
+        <v>592</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>85</v>
@@ -11031,22 +11005,22 @@
         <v>85</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>172</v>
+        <v>590</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>85</v>
+        <v>594</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>85</v>
+        <v>595</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>85</v>
@@ -11061,10 +11035,10 @@
         <v>85</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>85</v>
+        <v>596</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>166</v>
+        <v>597</v>
       </c>
       <c r="AR66" t="s" s="2">
         <v>85</v>
@@ -11075,46 +11049,42 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>592</v>
+        <v>85</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>141</v>
+        <v>591</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>600</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>85</v>
       </c>
@@ -11162,22 +11132,22 @@
         <v>85</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>85</v>
+        <v>594</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>85</v>
+        <v>601</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>85</v>
@@ -11192,10 +11162,10 @@
         <v>85</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>85</v>
+        <v>596</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>138</v>
+        <v>602</v>
       </c>
       <c r="AR67" t="s" s="2">
         <v>85</v>
@@ -11206,10 +11176,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11223,7 +11193,7 @@
         <v>95</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>85</v>
@@ -11232,16 +11202,20 @@
         <v>85</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>597</v>
+        <v>184</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
+        <v>605</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>607</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>85</v>
       </c>
@@ -11265,13 +11239,13 @@
         <v>85</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>85</v>
+        <v>608</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>85</v>
+        <v>609</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>85</v>
@@ -11289,7 +11263,7 @@
         <v>85</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>83</v>
@@ -11298,13 +11272,13 @@
         <v>95</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>600</v>
+        <v>85</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>601</v>
+        <v>85</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>85</v>
@@ -11316,13 +11290,13 @@
         <v>85</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>85</v>
+        <v>610</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>602</v>
+        <v>611</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>603</v>
+        <v>520</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>85</v>
@@ -11333,10 +11307,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11347,10 +11321,10 @@
         <v>83</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>85</v>
@@ -11359,16 +11333,20 @@
         <v>85</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>597</v>
+        <v>184</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
+        <v>614</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>616</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>85</v>
       </c>
@@ -11392,13 +11370,13 @@
         <v>85</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>85</v>
+        <v>537</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>85</v>
+        <v>617</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>85</v>
+        <v>618</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>85</v>
@@ -11416,22 +11394,22 @@
         <v>85</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>600</v>
+        <v>85</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>607</v>
+        <v>85</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>85</v>
@@ -11443,13 +11421,13 @@
         <v>85</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>85</v>
+        <v>610</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>602</v>
+        <v>611</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>608</v>
+        <v>520</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>85</v>
@@ -11460,10 +11438,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>609</v>
+        <v>619</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>609</v>
+        <v>619</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11486,19 +11464,17 @@
         <v>85</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>184</v>
+        <v>620</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>610</v>
+        <v>621</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>612</v>
-      </c>
+        <v>622</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>613</v>
+        <v>623</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>85</v>
@@ -11523,13 +11499,13 @@
         <v>85</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>614</v>
+        <v>85</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>615</v>
+        <v>85</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>85</v>
@@ -11547,7 +11523,7 @@
         <v>85</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>609</v>
+        <v>619</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>83</v>
@@ -11574,13 +11550,13 @@
         <v>85</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>616</v>
+        <v>85</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>617</v>
+        <v>85</v>
       </c>
       <c r="AQ70" t="s" s="2">
-        <v>526</v>
+        <v>624</v>
       </c>
       <c r="AR70" t="s" s="2">
         <v>85</v>
@@ -11591,10 +11567,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11605,7 +11581,7 @@
         <v>83</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>85</v>
@@ -11617,20 +11593,16 @@
         <v>85</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>622</v>
-      </c>
+        <v>627</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>85</v>
       </c>
@@ -11654,13 +11626,13 @@
         <v>85</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>543</v>
+        <v>85</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>623</v>
+        <v>85</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>624</v>
+        <v>85</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>85</v>
@@ -11678,13 +11650,13 @@
         <v>85</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>85</v>
@@ -11705,13 +11677,13 @@
         <v>85</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>616</v>
+        <v>85</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>617</v>
+        <v>596</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>526</v>
+        <v>628</v>
       </c>
       <c r="AR71" t="s" s="2">
         <v>85</v>
@@ -11722,10 +11694,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11736,7 +11708,7 @@
         <v>83</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>85</v>
@@ -11745,21 +11717,21 @@
         <v>85</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="N72" s="2"/>
-      <c r="O72" t="s" s="2">
-        <v>629</v>
-      </c>
+        <v>632</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>85</v>
       </c>
@@ -11807,13 +11779,13 @@
         <v>85</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>85</v>
@@ -11837,10 +11809,10 @@
         <v>85</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>85</v>
+        <v>634</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="AR72" t="s" s="2">
         <v>85</v>
@@ -11851,10 +11823,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11865,7 +11837,7 @@
         <v>83</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>85</v>
@@ -11874,18 +11846,20 @@
         <v>85</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>162</v>
+        <v>637</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>639</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>640</v>
+      </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>85</v>
@@ -11934,13 +11908,13 @@
         <v>85</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>85</v>
@@ -11964,10 +11938,10 @@
         <v>85</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>602</v>
+        <v>634</v>
       </c>
       <c r="AQ73" t="s" s="2">
-        <v>634</v>
+        <v>641</v>
       </c>
       <c r="AR73" t="s" s="2">
         <v>85</v>
@@ -11978,10 +11952,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12004,18 +11978,20 @@
         <v>96</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>636</v>
+        <v>575</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="O74" s="2"/>
+        <v>645</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>646</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>85</v>
       </c>
@@ -12063,7 +12039,7 @@
         <v>85</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>83</v>
@@ -12093,10 +12069,10 @@
         <v>85</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="AQ74" t="s" s="2">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="AR74" t="s" s="2">
         <v>85</v>
@@ -12107,10 +12083,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12121,7 +12097,7 @@
         <v>83</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>85</v>
@@ -12130,20 +12106,18 @@
         <v>85</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>643</v>
+        <v>162</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>644</v>
+        <v>163</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>646</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>85</v>
@@ -12192,19 +12166,19 @@
         <v>85</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>642</v>
+        <v>165</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>85</v>
@@ -12222,10 +12196,10 @@
         <v>85</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>640</v>
+        <v>85</v>
       </c>
       <c r="AQ75" t="s" s="2">
-        <v>647</v>
+        <v>166</v>
       </c>
       <c r="AR75" t="s" s="2">
         <v>85</v>
@@ -12236,14 +12210,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -12259,23 +12233,21 @@
         <v>85</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>581</v>
+        <v>141</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>649</v>
+        <v>142</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>650</v>
+        <v>168</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>652</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>85</v>
       </c>
@@ -12323,7 +12295,7 @@
         <v>85</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>648</v>
+        <v>172</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>83</v>
@@ -12335,7 +12307,7 @@
         <v>85</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>85</v>
@@ -12353,10 +12325,10 @@
         <v>85</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>653</v>
+        <v>85</v>
       </c>
       <c r="AQ76" t="s" s="2">
-        <v>654</v>
+        <v>166</v>
       </c>
       <c r="AR76" t="s" s="2">
         <v>85</v>
@@ -12367,42 +12339,46 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>85</v>
+        <v>586</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>163</v>
+        <v>587</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
+        <v>588</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>85</v>
       </c>
@@ -12450,19 +12426,19 @@
         <v>85</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>165</v>
+        <v>589</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>85</v>
@@ -12483,7 +12459,7 @@
         <v>85</v>
       </c>
       <c r="AQ77" t="s" s="2">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="AR77" t="s" s="2">
         <v>85</v>
@@ -12494,21 +12470,21 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>85</v>
@@ -12517,21 +12493,23 @@
         <v>85</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>142</v>
+        <v>653</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>168</v>
+        <v>654</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O78" s="2"/>
+        <v>655</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>85</v>
       </c>
@@ -12555,13 +12533,13 @@
         <v>85</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>85</v>
+        <v>537</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>85</v>
+        <v>656</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>85</v>
+        <v>281</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>85</v>
@@ -12579,19 +12557,19 @@
         <v>85</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>172</v>
+        <v>652</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>85</v>
@@ -12606,16 +12584,16 @@
         <v>85</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>85</v>
+        <v>657</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>85</v>
+        <v>284</v>
       </c>
       <c r="AQ78" t="s" s="2">
-        <v>166</v>
+        <v>285</v>
       </c>
       <c r="AR78" t="s" s="2">
-        <v>85</v>
+        <v>286</v>
       </c>
       <c r="AS78" t="s" s="2">
         <v>85</v>
@@ -12623,45 +12601,45 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>592</v>
+        <v>85</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J79" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>141</v>
+        <v>435</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>593</v>
+        <v>659</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>594</v>
+        <v>660</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>144</v>
+        <v>661</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>150</v>
+        <v>439</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>85</v>
@@ -12710,19 +12688,19 @@
         <v>85</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>595</v>
+        <v>658</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>85</v>
@@ -12737,27 +12715,27 @@
         <v>85</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>85</v>
+        <v>662</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>85</v>
+        <v>443</v>
       </c>
       <c r="AQ79" t="s" s="2">
-        <v>138</v>
+        <v>444</v>
       </c>
       <c r="AR79" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS79" t="s" s="2">
-        <v>85</v>
+        <v>445</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12765,7 +12743,7 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>95</v>
@@ -12777,22 +12755,22 @@
         <v>85</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K80" t="s" s="2">
         <v>184</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>279</v>
+        <v>504</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>85</v>
@@ -12817,13 +12795,13 @@
         <v>85</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>543</v>
+        <v>189</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>281</v>
+        <v>505</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>85</v>
@@ -12841,16 +12819,16 @@
         <v>85</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>95</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>85</v>
+        <v>668</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>107</v>
@@ -12868,16 +12846,16 @@
         <v>85</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>663</v>
+        <v>85</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>284</v>
+        <v>138</v>
       </c>
       <c r="AQ80" t="s" s="2">
-        <v>285</v>
+        <v>508</v>
       </c>
       <c r="AR80" t="s" s="2">
-        <v>286</v>
+        <v>85</v>
       </c>
       <c r="AS80" t="s" s="2">
         <v>85</v>
@@ -12885,21 +12863,21 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>85</v>
+        <v>510</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>85</v>
@@ -12908,22 +12886,22 @@
         <v>85</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>435</v>
+        <v>184</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>665</v>
+        <v>511</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>666</v>
+        <v>512</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>667</v>
+        <v>513</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>439</v>
+        <v>514</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>85</v>
@@ -12948,13 +12926,13 @@
         <v>85</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>85</v>
+        <v>670</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>85</v>
+        <v>671</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>85</v>
@@ -12972,13 +12950,13 @@
         <v>85</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>85</v>
@@ -12999,27 +12977,27 @@
         <v>85</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>668</v>
+        <v>518</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>443</v>
+        <v>519</v>
       </c>
       <c r="AQ81" t="s" s="2">
-        <v>444</v>
+        <v>520</v>
       </c>
       <c r="AR81" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS81" t="s" s="2">
-        <v>445</v>
+        <v>521</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13030,7 +13008,7 @@
         <v>83</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>85</v>
@@ -13042,19 +13020,19 @@
         <v>85</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>184</v>
+        <v>86</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>672</v>
+        <v>578</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>510</v>
+        <v>579</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>85</v>
@@ -13079,13 +13057,13 @@
         <v>85</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>189</v>
+        <v>85</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>673</v>
+        <v>85</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>511</v>
+        <v>85</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>85</v>
@@ -13103,16 +13081,16 @@
         <v>85</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>674</v>
+        <v>85</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>107</v>
@@ -13133,282 +13111,20 @@
         <v>85</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>138</v>
+        <v>581</v>
       </c>
       <c r="AQ82" t="s" s="2">
-        <v>514</v>
+        <v>582</v>
       </c>
       <c r="AR82" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS82" t="s" s="2">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="83" hidden="true">
-      <c r="A83" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="C83" s="2"/>
-      <c r="D83" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="E83" s="2"/>
-      <c r="F83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G83" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H83" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J83" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K83" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="P83" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q83" s="2"/>
-      <c r="R83" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S83" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T83" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI83" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ83" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK83" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="AP83" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="AQ83" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="AR83" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS83" t="s" s="2">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="84" hidden="true">
-      <c r="A84" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="C84" s="2"/>
-      <c r="D84" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="E84" s="2"/>
-      <c r="F84" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G84" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H84" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I84" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J84" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K84" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L84" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="P84" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q84" s="2"/>
-      <c r="R84" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S84" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T84" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="AG84" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP84" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="AQ84" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="AR84" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS84" t="s" s="2">
         <v>85</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS84">
+  <autoFilter ref="A1:AS82">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -13418,7 +13134,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI83">
+  <conditionalFormatting sqref="A2:AI81">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationChemhemtoxriaserObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
